--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="811">
   <si>
     <t>S.No.</t>
   </si>
@@ -356,12 +356,6 @@
   </si>
   <si>
     <t>PASS. Searching 'zzz-no-such-class-9999' returned 0 classes and displayed the no-results state with no error. CAPTURED COPY: 'No classes that match your search zzz-no-such-class-9999' - the searched term is echoed back in bold.</t>
-  </si>
-  <si>
-    <t>Flaky</t>
-  </si>
-  <si>
-    <t>Suite: adminClassesTab | 2026-09-16: Flaky across 2 runs | Error: Class list did not update after searching 'zzz-no-such-class-9999' [expected false == true]</t>
   </si>
   <si>
     <t>11</t>
@@ -3366,7 +3360,7 @@
         <v>114</v>
       </c>
       <c r="M11" t="s">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
@@ -3375,21 +3369,21 @@
         <v>30</v>
       </c>
       <c r="P11" t="s">
-        <v>116</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" t="s">
         <v>117</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
         <v>118</v>
-      </c>
-      <c r="C12" t="s">
-        <v>119</v>
-      </c>
-      <c r="D12" t="s">
-        <v>120</v>
       </c>
       <c r="E12" t="s">
         <v>20</v>
@@ -3398,19 +3392,19 @@
         <v>54</v>
       </c>
       <c r="G12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I12" t="s">
         <v>24</v>
       </c>
       <c r="J12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M12" t="s">
         <v>28</v>
@@ -3427,16 +3421,16 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" t="s">
         <v>125</v>
       </c>
-      <c r="B13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" t="s">
-        <v>127</v>
-      </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E13" t="s">
         <v>20</v>
@@ -3445,22 +3439,22 @@
         <v>54</v>
       </c>
       <c r="G13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H13" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I13" t="s">
         <v>24</v>
       </c>
       <c r="J13" t="s">
+        <v>127</v>
+      </c>
+      <c r="K13" t="s">
+        <v>128</v>
+      </c>
+      <c r="L13" t="s">
         <v>129</v>
-      </c>
-      <c r="K13" t="s">
-        <v>130</v>
-      </c>
-      <c r="L13" t="s">
-        <v>131</v>
       </c>
       <c r="M13" t="s">
         <v>28</v>
@@ -3477,16 +3471,16 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" t="s">
         <v>132</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
         <v>133</v>
-      </c>
-      <c r="C14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D14" t="s">
-        <v>135</v>
       </c>
       <c r="E14" t="s">
         <v>20</v>
@@ -3495,19 +3489,19 @@
         <v>54</v>
       </c>
       <c r="G14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H14" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I14" t="s">
         <v>24</v>
       </c>
       <c r="J14" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L14" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M14" t="s">
         <v>28</v>
@@ -3524,16 +3518,16 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" t="s">
         <v>140</v>
       </c>
-      <c r="B15" t="s">
-        <v>141</v>
-      </c>
-      <c r="C15" t="s">
-        <v>142</v>
-      </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E15" t="s">
         <v>20</v>
@@ -3542,19 +3536,19 @@
         <v>65</v>
       </c>
       <c r="G15" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H15" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I15" t="s">
         <v>24</v>
       </c>
       <c r="J15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M15" t="s">
         <v>28</v>
@@ -3571,16 +3565,16 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B16" t="s">
+        <v>146</v>
+      </c>
+      <c r="C16" t="s">
         <v>147</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" t="s">
         <v>148</v>
-      </c>
-      <c r="C16" t="s">
-        <v>149</v>
-      </c>
-      <c r="D16" t="s">
-        <v>150</v>
       </c>
       <c r="E16" t="s">
         <v>20</v>
@@ -3589,19 +3583,19 @@
         <v>65</v>
       </c>
       <c r="G16" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I16" t="s">
         <v>24</v>
       </c>
       <c r="J16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L16" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="M16" t="s">
         <v>28</v>
@@ -3618,16 +3612,16 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>153</v>
+      </c>
+      <c r="B17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" t="s">
         <v>155</v>
       </c>
-      <c r="B17" t="s">
-        <v>156</v>
-      </c>
-      <c r="C17" t="s">
-        <v>157</v>
-      </c>
       <c r="D17" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E17" t="s">
         <v>20</v>
@@ -3636,19 +3630,19 @@
         <v>65</v>
       </c>
       <c r="G17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I17" t="s">
         <v>24</v>
       </c>
       <c r="J17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M17" t="s">
         <v>28</v>
@@ -3665,16 +3659,16 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>160</v>
+      </c>
+      <c r="B18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" t="s">
         <v>162</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
         <v>163</v>
-      </c>
-      <c r="C18" t="s">
-        <v>164</v>
-      </c>
-      <c r="D18" t="s">
-        <v>165</v>
       </c>
       <c r="E18" t="s">
         <v>20</v>
@@ -3683,22 +3677,22 @@
         <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H18" t="s">
+        <v>164</v>
+      </c>
+      <c r="I18" t="s">
+        <v>165</v>
+      </c>
+      <c r="J18" t="s">
         <v>166</v>
       </c>
-      <c r="I18" t="s">
+      <c r="K18" t="s">
         <v>167</v>
       </c>
-      <c r="J18" t="s">
+      <c r="L18" t="s">
         <v>168</v>
-      </c>
-      <c r="K18" t="s">
-        <v>169</v>
-      </c>
-      <c r="L18" t="s">
-        <v>170</v>
       </c>
       <c r="M18" t="s">
         <v>28</v>
@@ -3715,16 +3709,16 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>169</v>
+      </c>
+      <c r="B19" t="s">
+        <v>170</v>
+      </c>
+      <c r="C19" t="s">
         <v>171</v>
       </c>
-      <c r="B19" t="s">
+      <c r="D19" t="s">
         <v>172</v>
-      </c>
-      <c r="C19" t="s">
-        <v>173</v>
-      </c>
-      <c r="D19" t="s">
-        <v>174</v>
       </c>
       <c r="E19" t="s">
         <v>20</v>
@@ -3733,22 +3727,22 @@
         <v>54</v>
       </c>
       <c r="G19" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H19" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I19" t="s">
         <v>24</v>
       </c>
       <c r="J19" t="s">
+        <v>175</v>
+      </c>
+      <c r="K19" t="s">
+        <v>176</v>
+      </c>
+      <c r="L19" t="s">
         <v>177</v>
-      </c>
-      <c r="K19" t="s">
-        <v>178</v>
-      </c>
-      <c r="L19" t="s">
-        <v>179</v>
       </c>
       <c r="M19" t="s">
         <v>28</v>
@@ -3765,16 +3759,16 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>178</v>
+      </c>
+      <c r="B20" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" t="s">
         <v>180</v>
       </c>
-      <c r="B20" t="s">
-        <v>181</v>
-      </c>
-      <c r="C20" t="s">
-        <v>182</v>
-      </c>
       <c r="D20" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E20" t="s">
         <v>20</v>
@@ -3783,19 +3777,19 @@
         <v>54</v>
       </c>
       <c r="G20" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H20" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I20" t="s">
         <v>24</v>
       </c>
       <c r="J20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L20" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M20" t="s">
         <v>28</v>
@@ -3812,16 +3806,16 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>185</v>
+      </c>
+      <c r="B21" t="s">
+        <v>186</v>
+      </c>
+      <c r="C21" t="s">
         <v>187</v>
       </c>
-      <c r="B21" t="s">
+      <c r="D21" t="s">
         <v>188</v>
-      </c>
-      <c r="C21" t="s">
-        <v>189</v>
-      </c>
-      <c r="D21" t="s">
-        <v>190</v>
       </c>
       <c r="E21" t="s">
         <v>20</v>
@@ -3830,22 +3824,22 @@
         <v>54</v>
       </c>
       <c r="G21" t="s">
+        <v>189</v>
+      </c>
+      <c r="H21" t="s">
+        <v>190</v>
+      </c>
+      <c r="I21" t="s">
         <v>191</v>
       </c>
-      <c r="H21" t="s">
+      <c r="J21" t="s">
         <v>192</v>
       </c>
-      <c r="I21" t="s">
+      <c r="K21" t="s">
         <v>193</v>
       </c>
-      <c r="J21" t="s">
+      <c r="L21" t="s">
         <v>194</v>
-      </c>
-      <c r="K21" t="s">
-        <v>195</v>
-      </c>
-      <c r="L21" t="s">
-        <v>196</v>
       </c>
       <c r="M21" t="s">
         <v>28</v>
@@ -3862,16 +3856,16 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>195</v>
+      </c>
+      <c r="B22" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" t="s">
         <v>197</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D22" t="s">
         <v>198</v>
-      </c>
-      <c r="C22" t="s">
-        <v>199</v>
-      </c>
-      <c r="D22" t="s">
-        <v>200</v>
       </c>
       <c r="E22" t="s">
         <v>20</v>
@@ -3880,22 +3874,22 @@
         <v>54</v>
       </c>
       <c r="G22" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H22" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I22" t="s">
         <v>24</v>
       </c>
       <c r="J22" t="s">
+        <v>201</v>
+      </c>
+      <c r="K22" t="s">
+        <v>202</v>
+      </c>
+      <c r="L22" t="s">
         <v>203</v>
-      </c>
-      <c r="K22" t="s">
-        <v>204</v>
-      </c>
-      <c r="L22" t="s">
-        <v>205</v>
       </c>
       <c r="M22" t="s">
         <v>28</v>
@@ -3912,16 +3906,16 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>204</v>
+      </c>
+      <c r="B23" t="s">
+        <v>205</v>
+      </c>
+      <c r="C23" t="s">
         <v>206</v>
       </c>
-      <c r="B23" t="s">
-        <v>207</v>
-      </c>
-      <c r="C23" t="s">
-        <v>208</v>
-      </c>
       <c r="D23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E23" t="s">
         <v>64</v>
@@ -3930,22 +3924,22 @@
         <v>65</v>
       </c>
       <c r="G23" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H23" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I23" t="s">
         <v>24</v>
       </c>
       <c r="J23" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>69</v>
       </c>
       <c r="L23" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="M23" t="s">
         <v>28</v>
@@ -3962,16 +3956,16 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>211</v>
+      </c>
+      <c r="B24" t="s">
+        <v>212</v>
+      </c>
+      <c r="C24" t="s">
         <v>213</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D24" t="s">
         <v>214</v>
-      </c>
-      <c r="C24" t="s">
-        <v>215</v>
-      </c>
-      <c r="D24" t="s">
-        <v>216</v>
       </c>
       <c r="E24" t="s">
         <v>20</v>
@@ -3980,22 +3974,22 @@
         <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H24" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I24" t="s">
         <v>24</v>
       </c>
       <c r="J24" t="s">
+        <v>217</v>
+      </c>
+      <c r="K24" t="s">
+        <v>218</v>
+      </c>
+      <c r="L24" t="s">
         <v>219</v>
-      </c>
-      <c r="K24" t="s">
-        <v>220</v>
-      </c>
-      <c r="L24" t="s">
-        <v>221</v>
       </c>
       <c r="M24" t="s">
         <v>28</v>
@@ -4004,21 +3998,21 @@
         <v>30</v>
       </c>
       <c r="P24" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>221</v>
+      </c>
+      <c r="B25" t="s">
+        <v>222</v>
+      </c>
+      <c r="C25" t="s">
         <v>223</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="s">
         <v>224</v>
-      </c>
-      <c r="C25" t="s">
-        <v>225</v>
-      </c>
-      <c r="D25" t="s">
-        <v>226</v>
       </c>
       <c r="E25" t="s">
         <v>20</v>
@@ -4027,48 +4021,48 @@
         <v>21</v>
       </c>
       <c r="G25" t="s">
+        <v>225</v>
+      </c>
+      <c r="H25" t="s">
+        <v>226</v>
+      </c>
+      <c r="I25" t="s">
         <v>227</v>
       </c>
-      <c r="H25" t="s">
+      <c r="J25" t="s">
         <v>228</v>
       </c>
-      <c r="I25" t="s">
+      <c r="K25" t="s">
         <v>229</v>
       </c>
-      <c r="J25" t="s">
+      <c r="L25" t="s">
         <v>230</v>
-      </c>
-      <c r="K25" t="s">
-        <v>231</v>
-      </c>
-      <c r="L25" t="s">
-        <v>232</v>
       </c>
       <c r="M25" t="s">
         <v>28</v>
       </c>
       <c r="N25" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O25" t="s">
         <v>30</v>
       </c>
       <c r="P25" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>232</v>
+      </c>
+      <c r="B26" t="s">
+        <v>233</v>
+      </c>
+      <c r="C26" t="s">
         <v>234</v>
       </c>
-      <c r="B26" t="s">
-        <v>235</v>
-      </c>
-      <c r="C26" t="s">
-        <v>236</v>
-      </c>
       <c r="D26" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E26" t="s">
         <v>64</v>
@@ -4077,48 +4071,48 @@
         <v>65</v>
       </c>
       <c r="G26" t="s">
+        <v>235</v>
+      </c>
+      <c r="H26" t="s">
+        <v>236</v>
+      </c>
+      <c r="I26" t="s">
         <v>237</v>
       </c>
-      <c r="H26" t="s">
+      <c r="J26" t="s">
         <v>238</v>
       </c>
-      <c r="I26" t="s">
+      <c r="K26" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="J26" t="s">
+      <c r="L26" t="s">
         <v>240</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="L26" t="s">
-        <v>242</v>
       </c>
       <c r="M26" t="s">
         <v>28</v>
       </c>
       <c r="N26" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O26" t="s">
         <v>30</v>
       </c>
       <c r="P26" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>241</v>
+      </c>
+      <c r="B27" t="s">
+        <v>242</v>
+      </c>
+      <c r="C27" t="s">
         <v>243</v>
       </c>
-      <c r="B27" t="s">
-        <v>244</v>
-      </c>
-      <c r="C27" t="s">
-        <v>245</v>
-      </c>
       <c r="D27" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E27" t="s">
         <v>64</v>
@@ -4127,48 +4121,48 @@
         <v>54</v>
       </c>
       <c r="G27" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I27" t="s">
         <v>24</v>
       </c>
       <c r="J27" t="s">
+        <v>246</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="L27" t="s">
         <v>248</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="M27" t="s">
         <v>249</v>
       </c>
-      <c r="L27" t="s">
+      <c r="N27" t="s">
         <v>250</v>
       </c>
-      <c r="M27" t="s">
+      <c r="O27" t="s">
+        <v>249</v>
+      </c>
+      <c r="P27" t="s">
         <v>251</v>
-      </c>
-      <c r="N27" t="s">
-        <v>252</v>
-      </c>
-      <c r="O27" t="s">
-        <v>251</v>
-      </c>
-      <c r="P27" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>252</v>
+      </c>
+      <c r="B28" t="s">
+        <v>253</v>
+      </c>
+      <c r="C28" t="s">
         <v>254</v>
       </c>
-      <c r="B28" t="s">
-        <v>255</v>
-      </c>
-      <c r="C28" t="s">
-        <v>256</v>
-      </c>
       <c r="D28" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E28" t="s">
         <v>74</v>
@@ -4177,48 +4171,48 @@
         <v>54</v>
       </c>
       <c r="G28" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H28" t="s">
+        <v>255</v>
+      </c>
+      <c r="I28" t="s">
+        <v>256</v>
+      </c>
+      <c r="J28" t="s">
         <v>257</v>
       </c>
-      <c r="I28" t="s">
+      <c r="K28" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="J28" t="s">
+      <c r="L28" t="s">
         <v>259</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="L28" t="s">
-        <v>261</v>
       </c>
       <c r="M28" t="s">
         <v>28</v>
       </c>
       <c r="N28" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O28" t="s">
         <v>30</v>
       </c>
       <c r="P28" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>260</v>
+      </c>
+      <c r="B29" t="s">
+        <v>261</v>
+      </c>
+      <c r="C29" t="s">
         <v>262</v>
       </c>
-      <c r="B29" t="s">
+      <c r="D29" t="s">
         <v>263</v>
-      </c>
-      <c r="C29" t="s">
-        <v>264</v>
-      </c>
-      <c r="D29" t="s">
-        <v>265</v>
       </c>
       <c r="E29" t="s">
         <v>20</v>
@@ -4227,22 +4221,22 @@
         <v>54</v>
       </c>
       <c r="G29" t="s">
+        <v>264</v>
+      </c>
+      <c r="H29" t="s">
+        <v>265</v>
+      </c>
+      <c r="I29" t="s">
         <v>266</v>
       </c>
-      <c r="H29" t="s">
+      <c r="J29" t="s">
         <v>267</v>
       </c>
-      <c r="I29" t="s">
+      <c r="K29" t="s">
         <v>268</v>
       </c>
-      <c r="J29" t="s">
+      <c r="L29" t="s">
         <v>269</v>
-      </c>
-      <c r="K29" t="s">
-        <v>270</v>
-      </c>
-      <c r="L29" t="s">
-        <v>271</v>
       </c>
       <c r="M29" t="s">
         <v>28</v>
@@ -4251,21 +4245,21 @@
         <v>30</v>
       </c>
       <c r="P29" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>270</v>
+      </c>
+      <c r="B30" t="s">
+        <v>271</v>
+      </c>
+      <c r="C30" t="s">
         <v>272</v>
       </c>
-      <c r="B30" t="s">
+      <c r="D30" t="s">
         <v>273</v>
-      </c>
-      <c r="C30" t="s">
-        <v>274</v>
-      </c>
-      <c r="D30" t="s">
-        <v>275</v>
       </c>
       <c r="E30" t="s">
         <v>20</v>
@@ -4274,22 +4268,22 @@
         <v>54</v>
       </c>
       <c r="G30" t="s">
+        <v>274</v>
+      </c>
+      <c r="H30" t="s">
+        <v>275</v>
+      </c>
+      <c r="I30" t="s">
         <v>276</v>
       </c>
-      <c r="H30" t="s">
+      <c r="J30" t="s">
         <v>277</v>
       </c>
-      <c r="I30" t="s">
+      <c r="K30" t="s">
         <v>278</v>
       </c>
-      <c r="J30" t="s">
+      <c r="L30" t="s">
         <v>279</v>
-      </c>
-      <c r="K30" t="s">
-        <v>280</v>
-      </c>
-      <c r="L30" t="s">
-        <v>281</v>
       </c>
       <c r="M30" t="s">
         <v>28</v>
@@ -4298,21 +4292,21 @@
         <v>30</v>
       </c>
       <c r="P30" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>281</v>
+      </c>
+      <c r="B31" t="s">
+        <v>282</v>
+      </c>
+      <c r="C31" t="s">
         <v>283</v>
       </c>
-      <c r="B31" t="s">
+      <c r="D31" t="s">
         <v>284</v>
-      </c>
-      <c r="C31" t="s">
-        <v>285</v>
-      </c>
-      <c r="D31" t="s">
-        <v>286</v>
       </c>
       <c r="E31" t="s">
         <v>20</v>
@@ -4321,48 +4315,48 @@
         <v>21</v>
       </c>
       <c r="G31" t="s">
+        <v>285</v>
+      </c>
+      <c r="H31" t="s">
+        <v>286</v>
+      </c>
+      <c r="I31" t="s">
+        <v>266</v>
+      </c>
+      <c r="J31" t="s">
         <v>287</v>
       </c>
-      <c r="H31" t="s">
+      <c r="K31" t="s">
         <v>288</v>
       </c>
-      <c r="I31" t="s">
-        <v>268</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="L31" t="s">
         <v>289</v>
-      </c>
-      <c r="K31" t="s">
-        <v>290</v>
-      </c>
-      <c r="L31" t="s">
-        <v>291</v>
       </c>
       <c r="M31" t="s">
         <v>28</v>
       </c>
       <c r="N31" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O31" t="s">
         <v>30</v>
       </c>
       <c r="P31" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>290</v>
+      </c>
+      <c r="B32" t="s">
+        <v>291</v>
+      </c>
+      <c r="C32" t="s">
         <v>292</v>
       </c>
-      <c r="B32" t="s">
-        <v>293</v>
-      </c>
-      <c r="C32" t="s">
-        <v>294</v>
-      </c>
       <c r="D32" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E32" t="s">
         <v>64</v>
@@ -4371,48 +4365,48 @@
         <v>65</v>
       </c>
       <c r="G32" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H32" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I32" t="s">
         <v>24</v>
       </c>
       <c r="J32" t="s">
+        <v>294</v>
+      </c>
+      <c r="K32" t="s">
+        <v>295</v>
+      </c>
+      <c r="L32" t="s">
         <v>296</v>
-      </c>
-      <c r="K32" t="s">
-        <v>297</v>
-      </c>
-      <c r="L32" t="s">
-        <v>298</v>
       </c>
       <c r="M32" t="s">
         <v>28</v>
       </c>
       <c r="N32" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O32" t="s">
         <v>30</v>
       </c>
       <c r="P32" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>297</v>
+      </c>
+      <c r="B33" t="s">
+        <v>298</v>
+      </c>
+      <c r="C33" t="s">
         <v>299</v>
       </c>
-      <c r="B33" t="s">
+      <c r="D33" t="s">
         <v>300</v>
-      </c>
-      <c r="C33" t="s">
-        <v>301</v>
-      </c>
-      <c r="D33" t="s">
-        <v>302</v>
       </c>
       <c r="E33" t="s">
         <v>20</v>
@@ -4424,45 +4418,45 @@
         <v>36</v>
       </c>
       <c r="H33" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I33" t="s">
         <v>24</v>
       </c>
       <c r="J33" t="s">
+        <v>302</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="L33" t="s">
         <v>304</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="L33" t="s">
-        <v>306</v>
       </c>
       <c r="M33" t="s">
         <v>28</v>
       </c>
       <c r="N33" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="O33" t="s">
         <v>30</v>
       </c>
       <c r="P33" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>307</v>
+      </c>
+      <c r="B34" t="s">
+        <v>308</v>
+      </c>
+      <c r="C34" t="s">
         <v>309</v>
       </c>
-      <c r="B34" t="s">
-        <v>310</v>
-      </c>
-      <c r="C34" t="s">
-        <v>311</v>
-      </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E34" t="s">
         <v>20</v>
@@ -4471,48 +4465,48 @@
         <v>21</v>
       </c>
       <c r="G34" t="s">
+        <v>310</v>
+      </c>
+      <c r="H34" t="s">
+        <v>311</v>
+      </c>
+      <c r="I34" t="s">
         <v>312</v>
       </c>
-      <c r="H34" t="s">
+      <c r="J34" t="s">
         <v>313</v>
       </c>
-      <c r="I34" t="s">
+      <c r="K34" t="s">
         <v>314</v>
       </c>
-      <c r="J34" t="s">
+      <c r="L34" t="s">
         <v>315</v>
-      </c>
-      <c r="K34" t="s">
-        <v>316</v>
-      </c>
-      <c r="L34" t="s">
-        <v>317</v>
       </c>
       <c r="M34" t="s">
         <v>28</v>
       </c>
       <c r="N34" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="O34" t="s">
         <v>30</v>
       </c>
       <c r="P34" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>318</v>
+      </c>
+      <c r="B35" t="s">
+        <v>319</v>
+      </c>
+      <c r="C35" t="s">
         <v>320</v>
       </c>
-      <c r="B35" t="s">
-        <v>321</v>
-      </c>
-      <c r="C35" t="s">
-        <v>322</v>
-      </c>
       <c r="D35" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E35" t="s">
         <v>20</v>
@@ -4521,48 +4515,48 @@
         <v>54</v>
       </c>
       <c r="G35" t="s">
+        <v>321</v>
+      </c>
+      <c r="H35" t="s">
+        <v>322</v>
+      </c>
+      <c r="I35" t="s">
         <v>323</v>
       </c>
-      <c r="H35" t="s">
+      <c r="J35" t="s">
         <v>324</v>
       </c>
-      <c r="I35" t="s">
+      <c r="K35" t="s">
         <v>325</v>
       </c>
-      <c r="J35" t="s">
+      <c r="L35" t="s">
         <v>326</v>
-      </c>
-      <c r="K35" t="s">
-        <v>327</v>
-      </c>
-      <c r="L35" t="s">
-        <v>328</v>
       </c>
       <c r="M35" t="s">
         <v>28</v>
       </c>
       <c r="N35" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="O35" t="s">
         <v>30</v>
       </c>
       <c r="P35" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>329</v>
+      </c>
+      <c r="B36" t="s">
+        <v>330</v>
+      </c>
+      <c r="C36" t="s">
         <v>331</v>
       </c>
-      <c r="B36" t="s">
-        <v>332</v>
-      </c>
-      <c r="C36" t="s">
-        <v>333</v>
-      </c>
       <c r="D36" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E36" t="s">
         <v>20</v>
@@ -4571,48 +4565,48 @@
         <v>54</v>
       </c>
       <c r="G36" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H36" t="s">
+        <v>332</v>
+      </c>
+      <c r="I36" t="s">
+        <v>333</v>
+      </c>
+      <c r="J36" t="s">
         <v>334</v>
       </c>
-      <c r="I36" t="s">
+      <c r="K36" t="s">
         <v>335</v>
       </c>
-      <c r="J36" t="s">
+      <c r="L36" t="s">
         <v>336</v>
-      </c>
-      <c r="K36" t="s">
-        <v>337</v>
-      </c>
-      <c r="L36" t="s">
-        <v>338</v>
       </c>
       <c r="M36" t="s">
         <v>28</v>
       </c>
       <c r="N36" t="s">
+        <v>337</v>
+      </c>
+      <c r="O36" t="s">
+        <v>338</v>
+      </c>
+      <c r="P36" t="s">
         <v>339</v>
-      </c>
-      <c r="O36" t="s">
-        <v>340</v>
-      </c>
-      <c r="P36" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>340</v>
+      </c>
+      <c r="B37" t="s">
+        <v>341</v>
+      </c>
+      <c r="C37" t="s">
         <v>342</v>
       </c>
-      <c r="B37" t="s">
-        <v>343</v>
-      </c>
-      <c r="C37" t="s">
-        <v>344</v>
-      </c>
       <c r="D37" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E37" t="s">
         <v>20</v>
@@ -4621,45 +4615,45 @@
         <v>54</v>
       </c>
       <c r="G37" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H37" t="s">
+        <v>343</v>
+      </c>
+      <c r="I37" t="s">
+        <v>344</v>
+      </c>
+      <c r="J37" t="s">
         <v>345</v>
       </c>
-      <c r="I37" t="s">
+      <c r="L37" t="s">
         <v>346</v>
-      </c>
-      <c r="J37" t="s">
-        <v>347</v>
-      </c>
-      <c r="L37" t="s">
-        <v>348</v>
       </c>
       <c r="M37" t="s">
         <v>28</v>
       </c>
       <c r="N37" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="O37" t="s">
         <v>30</v>
       </c>
       <c r="P37" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>349</v>
+      </c>
+      <c r="B38" t="s">
+        <v>350</v>
+      </c>
+      <c r="C38" t="s">
         <v>351</v>
       </c>
-      <c r="B38" t="s">
-        <v>352</v>
-      </c>
-      <c r="C38" t="s">
-        <v>353</v>
-      </c>
       <c r="D38" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E38" t="s">
         <v>20</v>
@@ -4668,45 +4662,45 @@
         <v>21</v>
       </c>
       <c r="G38" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H38" t="s">
+        <v>352</v>
+      </c>
+      <c r="I38" t="s">
+        <v>353</v>
+      </c>
+      <c r="J38" t="s">
         <v>354</v>
       </c>
-      <c r="I38" t="s">
+      <c r="L38" t="s">
         <v>355</v>
-      </c>
-      <c r="J38" t="s">
-        <v>356</v>
-      </c>
-      <c r="L38" t="s">
-        <v>357</v>
       </c>
       <c r="M38" t="s">
         <v>28</v>
       </c>
       <c r="N38" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="O38" t="s">
         <v>30</v>
       </c>
       <c r="P38" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>358</v>
+      </c>
+      <c r="B39" t="s">
+        <v>359</v>
+      </c>
+      <c r="C39" t="s">
         <v>360</v>
       </c>
-      <c r="B39" t="s">
-        <v>361</v>
-      </c>
-      <c r="C39" t="s">
-        <v>362</v>
-      </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E39" t="s">
         <v>20</v>
@@ -4715,48 +4709,48 @@
         <v>54</v>
       </c>
       <c r="G39" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H39" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="I39" t="s">
         <v>24</v>
       </c>
       <c r="J39" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="K39" s="3" t="s">
         <v>69</v>
       </c>
       <c r="L39" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="M39" t="s">
         <v>28</v>
       </c>
       <c r="N39" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="O39" t="s">
         <v>30</v>
       </c>
       <c r="P39" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>367</v>
+      </c>
+      <c r="B40" t="s">
+        <v>368</v>
+      </c>
+      <c r="C40" t="s">
         <v>369</v>
       </c>
-      <c r="B40" t="s">
-        <v>370</v>
-      </c>
-      <c r="C40" t="s">
-        <v>371</v>
-      </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E40" t="s">
         <v>20</v>
@@ -4765,48 +4759,48 @@
         <v>54</v>
       </c>
       <c r="G40" t="s">
+        <v>370</v>
+      </c>
+      <c r="H40" t="s">
+        <v>371</v>
+      </c>
+      <c r="I40" t="s">
         <v>372</v>
       </c>
-      <c r="H40" t="s">
+      <c r="J40" t="s">
         <v>373</v>
       </c>
-      <c r="I40" t="s">
+      <c r="K40" t="s">
         <v>374</v>
       </c>
-      <c r="J40" t="s">
+      <c r="L40" t="s">
         <v>375</v>
-      </c>
-      <c r="K40" t="s">
-        <v>376</v>
-      </c>
-      <c r="L40" t="s">
-        <v>377</v>
       </c>
       <c r="M40" t="s">
         <v>28</v>
       </c>
       <c r="N40" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="O40" t="s">
         <v>30</v>
       </c>
       <c r="P40" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>378</v>
+      </c>
+      <c r="B41" t="s">
+        <v>379</v>
+      </c>
+      <c r="C41" t="s">
         <v>380</v>
       </c>
-      <c r="B41" t="s">
-        <v>381</v>
-      </c>
-      <c r="C41" t="s">
-        <v>382</v>
-      </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E41" t="s">
         <v>20</v>
@@ -4815,48 +4809,48 @@
         <v>54</v>
       </c>
       <c r="G41" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="H41" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I41" t="s">
         <v>24</v>
       </c>
       <c r="J41" t="s">
+        <v>383</v>
+      </c>
+      <c r="K41" t="s">
+        <v>384</v>
+      </c>
+      <c r="L41" t="s">
         <v>385</v>
-      </c>
-      <c r="K41" t="s">
-        <v>386</v>
-      </c>
-      <c r="L41" t="s">
-        <v>387</v>
       </c>
       <c r="M41" t="s">
         <v>28</v>
       </c>
       <c r="N41" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="O41" t="s">
         <v>30</v>
       </c>
       <c r="P41" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>388</v>
+      </c>
+      <c r="B42" t="s">
+        <v>389</v>
+      </c>
+      <c r="C42" t="s">
         <v>390</v>
       </c>
-      <c r="B42" t="s">
-        <v>391</v>
-      </c>
-      <c r="C42" t="s">
-        <v>392</v>
-      </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E42" t="s">
         <v>20</v>
@@ -4865,45 +4859,45 @@
         <v>65</v>
       </c>
       <c r="G42" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H42" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="I42" t="s">
         <v>24</v>
       </c>
       <c r="J42" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="L42" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="M42" t="s">
         <v>28</v>
       </c>
       <c r="N42" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="O42" t="s">
         <v>30</v>
       </c>
       <c r="P42" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>396</v>
+      </c>
+      <c r="B43" t="s">
+        <v>397</v>
+      </c>
+      <c r="C43" t="s">
         <v>398</v>
       </c>
-      <c r="B43" t="s">
-        <v>399</v>
-      </c>
-      <c r="C43" t="s">
-        <v>400</v>
-      </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E43" t="s">
         <v>20</v>
@@ -4912,45 +4906,45 @@
         <v>54</v>
       </c>
       <c r="G43" t="s">
+        <v>399</v>
+      </c>
+      <c r="H43" t="s">
+        <v>400</v>
+      </c>
+      <c r="I43" t="s">
         <v>401</v>
       </c>
-      <c r="H43" t="s">
+      <c r="J43" t="s">
         <v>402</v>
       </c>
-      <c r="I43" t="s">
+      <c r="L43" t="s">
         <v>403</v>
-      </c>
-      <c r="J43" t="s">
-        <v>404</v>
-      </c>
-      <c r="L43" t="s">
-        <v>405</v>
       </c>
       <c r="M43" t="s">
         <v>28</v>
       </c>
       <c r="N43" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="O43" t="s">
         <v>30</v>
       </c>
       <c r="P43" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>406</v>
+      </c>
+      <c r="B44" t="s">
+        <v>407</v>
+      </c>
+      <c r="C44" t="s">
         <v>408</v>
       </c>
-      <c r="B44" t="s">
-        <v>409</v>
-      </c>
-      <c r="C44" t="s">
-        <v>410</v>
-      </c>
       <c r="D44" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E44" t="s">
         <v>20</v>
@@ -4959,48 +4953,48 @@
         <v>54</v>
       </c>
       <c r="G44" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H44" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I44" t="s">
         <v>24</v>
       </c>
       <c r="J44" t="s">
+        <v>411</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="L44" t="s">
         <v>413</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="L44" t="s">
-        <v>415</v>
       </c>
       <c r="M44" t="s">
         <v>28</v>
       </c>
       <c r="N44" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="O44" t="s">
         <v>30</v>
       </c>
       <c r="P44" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>416</v>
+      </c>
+      <c r="B45" t="s">
+        <v>417</v>
+      </c>
+      <c r="C45" t="s">
         <v>418</v>
       </c>
-      <c r="B45" t="s">
-        <v>419</v>
-      </c>
-      <c r="C45" t="s">
-        <v>420</v>
-      </c>
       <c r="D45" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E45" t="s">
         <v>64</v>
@@ -5009,48 +5003,48 @@
         <v>65</v>
       </c>
       <c r="G45" t="s">
+        <v>419</v>
+      </c>
+      <c r="H45" t="s">
+        <v>420</v>
+      </c>
+      <c r="I45" t="s">
+        <v>237</v>
+      </c>
+      <c r="J45" t="s">
         <v>421</v>
-      </c>
-      <c r="H45" t="s">
-        <v>422</v>
-      </c>
-      <c r="I45" t="s">
-        <v>239</v>
-      </c>
-      <c r="J45" t="s">
-        <v>423</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>69</v>
       </c>
       <c r="L45" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="M45" t="s">
         <v>28</v>
       </c>
       <c r="N45" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="O45" t="s">
         <v>30</v>
       </c>
       <c r="P45" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>425</v>
+      </c>
+      <c r="B46" t="s">
+        <v>426</v>
+      </c>
+      <c r="C46" t="s">
         <v>427</v>
       </c>
-      <c r="B46" t="s">
-        <v>428</v>
-      </c>
-      <c r="C46" t="s">
-        <v>429</v>
-      </c>
       <c r="D46" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E46" t="s">
         <v>64</v>
@@ -5059,48 +5053,48 @@
         <v>54</v>
       </c>
       <c r="G46" t="s">
+        <v>428</v>
+      </c>
+      <c r="H46" t="s">
+        <v>429</v>
+      </c>
+      <c r="I46" t="s">
         <v>430</v>
       </c>
-      <c r="H46" t="s">
+      <c r="J46" t="s">
         <v>431</v>
       </c>
-      <c r="I46" t="s">
+      <c r="K46" t="s">
         <v>432</v>
       </c>
-      <c r="J46" t="s">
+      <c r="L46" t="s">
         <v>433</v>
-      </c>
-      <c r="K46" t="s">
-        <v>434</v>
-      </c>
-      <c r="L46" t="s">
-        <v>435</v>
       </c>
       <c r="M46" t="s">
         <v>28</v>
       </c>
       <c r="N46" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="O46" t="s">
         <v>30</v>
       </c>
       <c r="P46" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>436</v>
+      </c>
+      <c r="B47" t="s">
+        <v>437</v>
+      </c>
+      <c r="C47" t="s">
         <v>438</v>
       </c>
-      <c r="B47" t="s">
-        <v>439</v>
-      </c>
-      <c r="C47" t="s">
-        <v>440</v>
-      </c>
       <c r="D47" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E47" t="s">
         <v>74</v>
@@ -5109,48 +5103,48 @@
         <v>21</v>
       </c>
       <c r="G47" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H47" t="s">
+        <v>439</v>
+      </c>
+      <c r="I47" t="s">
+        <v>440</v>
+      </c>
+      <c r="J47" t="s">
         <v>441</v>
-      </c>
-      <c r="I47" t="s">
-        <v>442</v>
-      </c>
-      <c r="J47" t="s">
-        <v>443</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>69</v>
       </c>
       <c r="L47" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="M47" t="s">
         <v>28</v>
       </c>
       <c r="N47" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="O47" t="s">
         <v>30</v>
       </c>
       <c r="P47" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>445</v>
+      </c>
+      <c r="B48" t="s">
+        <v>446</v>
+      </c>
+      <c r="C48" t="s">
         <v>447</v>
       </c>
-      <c r="B48" t="s">
-        <v>448</v>
-      </c>
-      <c r="C48" t="s">
-        <v>449</v>
-      </c>
       <c r="D48" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E48" t="s">
         <v>74</v>
@@ -5159,48 +5153,48 @@
         <v>54</v>
       </c>
       <c r="G48" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H48" t="s">
+        <v>448</v>
+      </c>
+      <c r="I48" t="s">
+        <v>449</v>
+      </c>
+      <c r="J48" t="s">
         <v>450</v>
-      </c>
-      <c r="I48" t="s">
-        <v>451</v>
-      </c>
-      <c r="J48" t="s">
-        <v>452</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>69</v>
       </c>
       <c r="L48" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="M48" t="s">
         <v>28</v>
       </c>
       <c r="N48" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="O48" t="s">
         <v>30</v>
       </c>
       <c r="P48" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>454</v>
+      </c>
+      <c r="B49" t="s">
+        <v>455</v>
+      </c>
+      <c r="C49" t="s">
         <v>456</v>
       </c>
-      <c r="B49" t="s">
+      <c r="D49" t="s">
         <v>457</v>
-      </c>
-      <c r="C49" t="s">
-        <v>458</v>
-      </c>
-      <c r="D49" t="s">
-        <v>459</v>
       </c>
       <c r="E49" t="s">
         <v>20</v>
@@ -5209,22 +5203,22 @@
         <v>21</v>
       </c>
       <c r="G49" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H49" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="I49" t="s">
         <v>24</v>
       </c>
       <c r="J49" t="s">
+        <v>459</v>
+      </c>
+      <c r="K49" t="s">
+        <v>460</v>
+      </c>
+      <c r="L49" t="s">
         <v>461</v>
-      </c>
-      <c r="K49" t="s">
-        <v>462</v>
-      </c>
-      <c r="L49" t="s">
-        <v>463</v>
       </c>
       <c r="M49" t="s">
         <v>28</v>
@@ -5233,21 +5227,21 @@
         <v>30</v>
       </c>
       <c r="P49" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>463</v>
+      </c>
+      <c r="B50" t="s">
+        <v>464</v>
+      </c>
+      <c r="C50" t="s">
         <v>465</v>
       </c>
-      <c r="B50" t="s">
+      <c r="D50" t="s">
         <v>466</v>
-      </c>
-      <c r="C50" t="s">
-        <v>467</v>
-      </c>
-      <c r="D50" t="s">
-        <v>468</v>
       </c>
       <c r="E50" t="s">
         <v>20</v>
@@ -5256,22 +5250,22 @@
         <v>21</v>
       </c>
       <c r="G50" t="s">
+        <v>467</v>
+      </c>
+      <c r="H50" t="s">
+        <v>468</v>
+      </c>
+      <c r="I50" t="s">
         <v>469</v>
       </c>
-      <c r="H50" t="s">
+      <c r="J50" t="s">
         <v>470</v>
       </c>
-      <c r="I50" t="s">
+      <c r="K50" t="s">
         <v>471</v>
       </c>
-      <c r="J50" t="s">
+      <c r="L50" t="s">
         <v>472</v>
-      </c>
-      <c r="K50" t="s">
-        <v>473</v>
-      </c>
-      <c r="L50" t="s">
-        <v>474</v>
       </c>
       <c r="M50" t="s">
         <v>28</v>
@@ -5280,21 +5274,21 @@
         <v>30</v>
       </c>
       <c r="P50" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>473</v>
+      </c>
+      <c r="B51" t="s">
+        <v>474</v>
+      </c>
+      <c r="C51" t="s">
         <v>475</v>
       </c>
-      <c r="B51" t="s">
-        <v>476</v>
-      </c>
-      <c r="C51" t="s">
-        <v>477</v>
-      </c>
       <c r="D51" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E51" t="s">
         <v>20</v>
@@ -5303,22 +5297,22 @@
         <v>54</v>
       </c>
       <c r="G51" t="s">
+        <v>476</v>
+      </c>
+      <c r="H51" t="s">
+        <v>477</v>
+      </c>
+      <c r="I51" t="s">
         <v>478</v>
       </c>
-      <c r="H51" t="s">
+      <c r="J51" t="s">
         <v>479</v>
       </c>
-      <c r="I51" t="s">
+      <c r="K51" t="s">
         <v>480</v>
       </c>
-      <c r="J51" t="s">
+      <c r="L51" t="s">
         <v>481</v>
-      </c>
-      <c r="K51" t="s">
-        <v>482</v>
-      </c>
-      <c r="L51" t="s">
-        <v>483</v>
       </c>
       <c r="M51" t="s">
         <v>28</v>
@@ -5327,21 +5321,21 @@
         <v>30</v>
       </c>
       <c r="P51" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>482</v>
+      </c>
+      <c r="B52" t="s">
+        <v>483</v>
+      </c>
+      <c r="C52" t="s">
         <v>484</v>
       </c>
-      <c r="B52" t="s">
-        <v>485</v>
-      </c>
-      <c r="C52" t="s">
-        <v>486</v>
-      </c>
       <c r="D52" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E52" t="s">
         <v>64</v>
@@ -5350,42 +5344,42 @@
         <v>54</v>
       </c>
       <c r="G52" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H52" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="I52" t="s">
         <v>24</v>
       </c>
       <c r="J52" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="M52" t="s">
+        <v>249</v>
+      </c>
+      <c r="O52" t="s">
+        <v>249</v>
+      </c>
+      <c r="P52" t="s">
         <v>251</v>
-      </c>
-      <c r="O52" t="s">
-        <v>251</v>
-      </c>
-      <c r="P52" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>489</v>
+      </c>
+      <c r="B53" t="s">
+        <v>490</v>
+      </c>
+      <c r="C53" t="s">
         <v>491</v>
       </c>
-      <c r="B53" t="s">
-        <v>492</v>
-      </c>
-      <c r="C53" t="s">
-        <v>493</v>
-      </c>
       <c r="D53" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E53" t="s">
         <v>74</v>
@@ -5394,19 +5388,19 @@
         <v>21</v>
       </c>
       <c r="G53" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H53" t="s">
+        <v>492</v>
+      </c>
+      <c r="I53" t="s">
+        <v>493</v>
+      </c>
+      <c r="J53" t="s">
         <v>494</v>
       </c>
-      <c r="I53" t="s">
+      <c r="L53" t="s">
         <v>495</v>
-      </c>
-      <c r="J53" t="s">
-        <v>496</v>
-      </c>
-      <c r="L53" t="s">
-        <v>497</v>
       </c>
       <c r="M53" t="s">
         <v>28</v>
@@ -5415,21 +5409,21 @@
         <v>30</v>
       </c>
       <c r="P53" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>496</v>
+      </c>
+      <c r="B54" t="s">
+        <v>497</v>
+      </c>
+      <c r="C54" t="s">
         <v>498</v>
       </c>
-      <c r="B54" t="s">
+      <c r="D54" t="s">
         <v>499</v>
-      </c>
-      <c r="C54" t="s">
-        <v>500</v>
-      </c>
-      <c r="D54" t="s">
-        <v>501</v>
       </c>
       <c r="E54" t="s">
         <v>20</v>
@@ -5438,19 +5432,19 @@
         <v>54</v>
       </c>
       <c r="G54" t="s">
+        <v>500</v>
+      </c>
+      <c r="H54" t="s">
+        <v>501</v>
+      </c>
+      <c r="I54" t="s">
         <v>502</v>
       </c>
-      <c r="H54" t="s">
+      <c r="J54" t="s">
         <v>503</v>
       </c>
-      <c r="I54" t="s">
+      <c r="L54" t="s">
         <v>504</v>
-      </c>
-      <c r="J54" t="s">
-        <v>505</v>
-      </c>
-      <c r="L54" t="s">
-        <v>506</v>
       </c>
       <c r="M54" t="s">
         <v>28</v>
@@ -5459,21 +5453,21 @@
         <v>30</v>
       </c>
       <c r="P54" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>505</v>
+      </c>
+      <c r="B55" t="s">
+        <v>506</v>
+      </c>
+      <c r="C55" t="s">
         <v>507</v>
       </c>
-      <c r="B55" t="s">
+      <c r="D55" t="s">
         <v>508</v>
-      </c>
-      <c r="C55" t="s">
-        <v>509</v>
-      </c>
-      <c r="D55" t="s">
-        <v>510</v>
       </c>
       <c r="E55" t="s">
         <v>20</v>
@@ -5482,22 +5476,22 @@
         <v>54</v>
       </c>
       <c r="G55" t="s">
+        <v>509</v>
+      </c>
+      <c r="H55" t="s">
+        <v>510</v>
+      </c>
+      <c r="I55" t="s">
         <v>511</v>
       </c>
-      <c r="H55" t="s">
+      <c r="J55" t="s">
         <v>512</v>
       </c>
-      <c r="I55" t="s">
+      <c r="K55" t="s">
         <v>513</v>
       </c>
-      <c r="J55" t="s">
+      <c r="L55" t="s">
         <v>514</v>
-      </c>
-      <c r="K55" t="s">
-        <v>515</v>
-      </c>
-      <c r="L55" t="s">
-        <v>516</v>
       </c>
       <c r="M55" t="s">
         <v>28</v>
@@ -5506,21 +5500,21 @@
         <v>30</v>
       </c>
       <c r="P55" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>515</v>
+      </c>
+      <c r="B56" t="s">
+        <v>516</v>
+      </c>
+      <c r="C56" t="s">
         <v>517</v>
       </c>
-      <c r="B56" t="s">
+      <c r="D56" t="s">
         <v>518</v>
-      </c>
-      <c r="C56" t="s">
-        <v>519</v>
-      </c>
-      <c r="D56" t="s">
-        <v>520</v>
       </c>
       <c r="E56" t="s">
         <v>20</v>
@@ -5529,22 +5523,22 @@
         <v>21</v>
       </c>
       <c r="G56" t="s">
+        <v>519</v>
+      </c>
+      <c r="H56" t="s">
+        <v>520</v>
+      </c>
+      <c r="I56" t="s">
+        <v>502</v>
+      </c>
+      <c r="J56" t="s">
         <v>521</v>
       </c>
-      <c r="H56" t="s">
+      <c r="K56" t="s">
         <v>522</v>
       </c>
-      <c r="I56" t="s">
-        <v>504</v>
-      </c>
-      <c r="J56" t="s">
+      <c r="L56" t="s">
         <v>523</v>
-      </c>
-      <c r="K56" t="s">
-        <v>524</v>
-      </c>
-      <c r="L56" t="s">
-        <v>525</v>
       </c>
       <c r="M56" t="s">
         <v>28</v>
@@ -5553,21 +5547,21 @@
         <v>30</v>
       </c>
       <c r="P56" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>524</v>
+      </c>
+      <c r="B57" t="s">
+        <v>525</v>
+      </c>
+      <c r="C57" t="s">
         <v>526</v>
       </c>
-      <c r="B57" t="s">
+      <c r="D57" t="s">
         <v>527</v>
-      </c>
-      <c r="C57" t="s">
-        <v>528</v>
-      </c>
-      <c r="D57" t="s">
-        <v>529</v>
       </c>
       <c r="E57" t="s">
         <v>20</v>
@@ -5576,19 +5570,19 @@
         <v>21</v>
       </c>
       <c r="G57" t="s">
+        <v>528</v>
+      </c>
+      <c r="H57" t="s">
+        <v>529</v>
+      </c>
+      <c r="I57" t="s">
+        <v>502</v>
+      </c>
+      <c r="J57" t="s">
         <v>530</v>
       </c>
-      <c r="H57" t="s">
+      <c r="L57" t="s">
         <v>531</v>
-      </c>
-      <c r="I57" t="s">
-        <v>504</v>
-      </c>
-      <c r="J57" t="s">
-        <v>532</v>
-      </c>
-      <c r="L57" t="s">
-        <v>533</v>
       </c>
       <c r="M57" t="s">
         <v>28</v>
@@ -5597,21 +5591,21 @@
         <v>30</v>
       </c>
       <c r="P57" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>532</v>
+      </c>
+      <c r="B58" t="s">
+        <v>533</v>
+      </c>
+      <c r="C58" t="s">
         <v>534</v>
       </c>
-      <c r="B58" t="s">
-        <v>535</v>
-      </c>
-      <c r="C58" t="s">
-        <v>536</v>
-      </c>
       <c r="D58" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E58" t="s">
         <v>64</v>
@@ -5620,19 +5614,19 @@
         <v>65</v>
       </c>
       <c r="G58" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="H58" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="I58" t="s">
         <v>24</v>
       </c>
       <c r="J58" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="L58" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="M58" t="s">
         <v>28</v>
@@ -5641,21 +5635,21 @@
         <v>30</v>
       </c>
       <c r="P58" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>539</v>
+      </c>
+      <c r="B59" t="s">
+        <v>540</v>
+      </c>
+      <c r="C59" t="s">
         <v>541</v>
       </c>
-      <c r="B59" t="s">
-        <v>542</v>
-      </c>
-      <c r="C59" t="s">
-        <v>543</v>
-      </c>
       <c r="D59" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E59" t="s">
         <v>74</v>
@@ -5664,22 +5658,22 @@
         <v>54</v>
       </c>
       <c r="G59" t="s">
+        <v>542</v>
+      </c>
+      <c r="H59" t="s">
+        <v>543</v>
+      </c>
+      <c r="I59" t="s">
         <v>544</v>
       </c>
-      <c r="H59" t="s">
+      <c r="J59" t="s">
         <v>545</v>
       </c>
-      <c r="I59" t="s">
+      <c r="K59" t="s">
         <v>546</v>
       </c>
-      <c r="J59" t="s">
+      <c r="L59" t="s">
         <v>547</v>
-      </c>
-      <c r="K59" t="s">
-        <v>548</v>
-      </c>
-      <c r="L59" t="s">
-        <v>549</v>
       </c>
       <c r="M59" t="s">
         <v>28</v>
@@ -5688,21 +5682,21 @@
         <v>30</v>
       </c>
       <c r="P59" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>548</v>
+      </c>
+      <c r="B60" t="s">
+        <v>549</v>
+      </c>
+      <c r="C60" t="s">
         <v>550</v>
       </c>
-      <c r="B60" t="s">
+      <c r="D60" t="s">
         <v>551</v>
-      </c>
-      <c r="C60" t="s">
-        <v>552</v>
-      </c>
-      <c r="D60" t="s">
-        <v>553</v>
       </c>
       <c r="E60" t="s">
         <v>20</v>
@@ -5711,19 +5705,19 @@
         <v>54</v>
       </c>
       <c r="G60" t="s">
+        <v>552</v>
+      </c>
+      <c r="H60" t="s">
+        <v>553</v>
+      </c>
+      <c r="I60" t="s">
+        <v>502</v>
+      </c>
+      <c r="J60" t="s">
         <v>554</v>
       </c>
-      <c r="H60" t="s">
+      <c r="L60" t="s">
         <v>555</v>
-      </c>
-      <c r="I60" t="s">
-        <v>504</v>
-      </c>
-      <c r="J60" t="s">
-        <v>556</v>
-      </c>
-      <c r="L60" t="s">
-        <v>557</v>
       </c>
       <c r="M60" t="s">
         <v>28</v>
@@ -5732,21 +5726,21 @@
         <v>30</v>
       </c>
       <c r="P60" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>556</v>
+      </c>
+      <c r="B61" t="s">
+        <v>557</v>
+      </c>
+      <c r="C61" t="s">
         <v>558</v>
       </c>
-      <c r="B61" t="s">
+      <c r="D61" t="s">
         <v>559</v>
-      </c>
-      <c r="C61" t="s">
-        <v>560</v>
-      </c>
-      <c r="D61" t="s">
-        <v>561</v>
       </c>
       <c r="E61" t="s">
         <v>20</v>
@@ -5755,42 +5749,42 @@
         <v>54</v>
       </c>
       <c r="G61" t="s">
+        <v>560</v>
+      </c>
+      <c r="H61" t="s">
+        <v>561</v>
+      </c>
+      <c r="I61" t="s">
+        <v>344</v>
+      </c>
+      <c r="J61" t="s">
         <v>562</v>
       </c>
-      <c r="H61" t="s">
+      <c r="K61" t="s">
         <v>563</v>
       </c>
-      <c r="I61" t="s">
-        <v>346</v>
-      </c>
-      <c r="J61" t="s">
+      <c r="M61" t="s">
         <v>564</v>
       </c>
-      <c r="K61" t="s">
-        <v>565</v>
-      </c>
-      <c r="M61" t="s">
-        <v>566</v>
-      </c>
       <c r="O61" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P61" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>565</v>
+      </c>
+      <c r="B62" t="s">
+        <v>566</v>
+      </c>
+      <c r="C62" t="s">
         <v>567</v>
       </c>
-      <c r="B62" t="s">
-        <v>568</v>
-      </c>
-      <c r="C62" t="s">
-        <v>569</v>
-      </c>
       <c r="D62" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E62" t="s">
         <v>20</v>
@@ -5799,39 +5793,39 @@
         <v>65</v>
       </c>
       <c r="G62" t="s">
+        <v>568</v>
+      </c>
+      <c r="H62" t="s">
+        <v>569</v>
+      </c>
+      <c r="I62" t="s">
         <v>570</v>
       </c>
-      <c r="H62" t="s">
+      <c r="J62" t="s">
         <v>571</v>
       </c>
-      <c r="I62" t="s">
-        <v>572</v>
-      </c>
-      <c r="J62" t="s">
-        <v>573</v>
-      </c>
       <c r="M62" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="O62" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P62" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>572</v>
+      </c>
+      <c r="B63" t="s">
+        <v>573</v>
+      </c>
+      <c r="C63" t="s">
         <v>574</v>
       </c>
-      <c r="B63" t="s">
+      <c r="D63" t="s">
         <v>575</v>
-      </c>
-      <c r="C63" t="s">
-        <v>576</v>
-      </c>
-      <c r="D63" t="s">
-        <v>577</v>
       </c>
       <c r="E63" t="s">
         <v>20</v>
@@ -5840,42 +5834,42 @@
         <v>21</v>
       </c>
       <c r="G63" t="s">
+        <v>576</v>
+      </c>
+      <c r="H63" t="s">
+        <v>577</v>
+      </c>
+      <c r="I63" t="s">
         <v>578</v>
       </c>
-      <c r="H63" t="s">
+      <c r="J63" t="s">
         <v>579</v>
       </c>
-      <c r="I63" t="s">
+      <c r="K63" t="s">
         <v>580</v>
       </c>
-      <c r="J63" t="s">
-        <v>581</v>
-      </c>
-      <c r="K63" t="s">
-        <v>582</v>
-      </c>
       <c r="M63" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="O63" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P63" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>581</v>
+      </c>
+      <c r="B64" t="s">
+        <v>582</v>
+      </c>
+      <c r="C64" t="s">
         <v>583</v>
       </c>
-      <c r="B64" t="s">
-        <v>584</v>
-      </c>
-      <c r="C64" t="s">
-        <v>585</v>
-      </c>
       <c r="D64" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E64" t="s">
         <v>20</v>
@@ -5884,42 +5878,42 @@
         <v>21</v>
       </c>
       <c r="G64" t="s">
+        <v>584</v>
+      </c>
+      <c r="H64" t="s">
+        <v>585</v>
+      </c>
+      <c r="I64" t="s">
         <v>586</v>
       </c>
-      <c r="H64" t="s">
+      <c r="J64" t="s">
         <v>587</v>
-      </c>
-      <c r="I64" t="s">
-        <v>588</v>
-      </c>
-      <c r="J64" t="s">
-        <v>589</v>
       </c>
       <c r="K64" s="3" t="s">
         <v>69</v>
       </c>
       <c r="M64" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="O64" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="P64" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>590</v>
+      </c>
+      <c r="B65" t="s">
+        <v>591</v>
+      </c>
+      <c r="C65" t="s">
         <v>592</v>
       </c>
-      <c r="B65" t="s">
-        <v>593</v>
-      </c>
-      <c r="C65" t="s">
-        <v>594</v>
-      </c>
       <c r="D65" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E65" t="s">
         <v>20</v>
@@ -5928,42 +5922,42 @@
         <v>54</v>
       </c>
       <c r="G65" t="s">
+        <v>593</v>
+      </c>
+      <c r="H65" t="s">
+        <v>594</v>
+      </c>
+      <c r="I65" t="s">
         <v>595</v>
       </c>
-      <c r="H65" t="s">
+      <c r="J65" t="s">
         <v>596</v>
       </c>
-      <c r="I65" t="s">
+      <c r="K65" t="s">
         <v>597</v>
       </c>
-      <c r="J65" t="s">
-        <v>598</v>
-      </c>
-      <c r="K65" t="s">
-        <v>599</v>
-      </c>
       <c r="M65" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="O65" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P65" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>598</v>
+      </c>
+      <c r="B66" t="s">
+        <v>599</v>
+      </c>
+      <c r="C66" t="s">
         <v>600</v>
       </c>
-      <c r="B66" t="s">
-        <v>601</v>
-      </c>
-      <c r="C66" t="s">
-        <v>602</v>
-      </c>
       <c r="D66" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E66" t="s">
         <v>64</v>
@@ -5972,42 +5966,42 @@
         <v>54</v>
       </c>
       <c r="G66" t="s">
+        <v>601</v>
+      </c>
+      <c r="H66" t="s">
+        <v>602</v>
+      </c>
+      <c r="I66" t="s">
         <v>603</v>
       </c>
-      <c r="H66" t="s">
+      <c r="J66" t="s">
         <v>604</v>
       </c>
-      <c r="I66" t="s">
+      <c r="K66" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="J66" t="s">
-        <v>606</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>607</v>
-      </c>
       <c r="M66" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="O66" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="P66" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>606</v>
+      </c>
+      <c r="B67" t="s">
+        <v>607</v>
+      </c>
+      <c r="C67" t="s">
         <v>608</v>
       </c>
-      <c r="B67" t="s">
-        <v>609</v>
-      </c>
-      <c r="C67" t="s">
-        <v>610</v>
-      </c>
       <c r="D67" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E67" t="s">
         <v>64</v>
@@ -6016,39 +6010,39 @@
         <v>65</v>
       </c>
       <c r="G67" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="H67" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="I67" t="s">
         <v>24</v>
       </c>
       <c r="J67" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="M67" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="O67" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P67" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>612</v>
+      </c>
+      <c r="B68" t="s">
+        <v>613</v>
+      </c>
+      <c r="C68" t="s">
         <v>614</v>
       </c>
-      <c r="B68" t="s">
-        <v>615</v>
-      </c>
-      <c r="C68" t="s">
-        <v>616</v>
-      </c>
       <c r="D68" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E68" t="s">
         <v>74</v>
@@ -6057,39 +6051,39 @@
         <v>54</v>
       </c>
       <c r="G68" t="s">
+        <v>615</v>
+      </c>
+      <c r="H68" t="s">
+        <v>616</v>
+      </c>
+      <c r="I68" t="s">
         <v>617</v>
       </c>
-      <c r="H68" t="s">
+      <c r="J68" t="s">
         <v>618</v>
       </c>
-      <c r="I68" t="s">
-        <v>619</v>
-      </c>
-      <c r="J68" t="s">
-        <v>620</v>
-      </c>
       <c r="M68" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="O68" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P68" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>619</v>
+      </c>
+      <c r="B69" t="s">
+        <v>620</v>
+      </c>
+      <c r="C69" t="s">
         <v>621</v>
       </c>
-      <c r="B69" t="s">
+      <c r="D69" t="s">
         <v>622</v>
-      </c>
-      <c r="C69" t="s">
-        <v>623</v>
-      </c>
-      <c r="D69" t="s">
-        <v>624</v>
       </c>
       <c r="E69" t="s">
         <v>20</v>
@@ -6101,39 +6095,39 @@
         <v>36</v>
       </c>
       <c r="H69" t="s">
+        <v>623</v>
+      </c>
+      <c r="I69" t="s">
+        <v>624</v>
+      </c>
+      <c r="J69" t="s">
         <v>625</v>
       </c>
-      <c r="I69" t="s">
+      <c r="K69" t="s">
         <v>626</v>
       </c>
-      <c r="J69" t="s">
-        <v>627</v>
-      </c>
-      <c r="K69" t="s">
-        <v>628</v>
-      </c>
       <c r="M69" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="O69" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P69" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>627</v>
+      </c>
+      <c r="B70" t="s">
+        <v>628</v>
+      </c>
+      <c r="C70" t="s">
         <v>629</v>
       </c>
-      <c r="B70" t="s">
+      <c r="D70" t="s">
         <v>630</v>
-      </c>
-      <c r="C70" t="s">
-        <v>631</v>
-      </c>
-      <c r="D70" t="s">
-        <v>632</v>
       </c>
       <c r="E70" t="s">
         <v>20</v>
@@ -6142,19 +6136,19 @@
         <v>21</v>
       </c>
       <c r="G70" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="H70" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="I70" t="s">
         <v>24</v>
       </c>
       <c r="J70" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="K70" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="M70" t="s">
         <v>28</v>
@@ -6163,21 +6157,21 @@
         <v>30</v>
       </c>
       <c r="P70" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>635</v>
+      </c>
+      <c r="B71" t="s">
+        <v>636</v>
+      </c>
+      <c r="C71" t="s">
         <v>637</v>
       </c>
-      <c r="B71" t="s">
-        <v>638</v>
-      </c>
-      <c r="C71" t="s">
-        <v>639</v>
-      </c>
       <c r="D71" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E71" t="s">
         <v>20</v>
@@ -6186,19 +6180,19 @@
         <v>21</v>
       </c>
       <c r="G71" t="s">
+        <v>638</v>
+      </c>
+      <c r="H71" t="s">
+        <v>639</v>
+      </c>
+      <c r="I71" t="s">
         <v>640</v>
       </c>
-      <c r="H71" t="s">
+      <c r="J71" t="s">
         <v>641</v>
       </c>
-      <c r="I71" t="s">
+      <c r="K71" t="s">
         <v>642</v>
-      </c>
-      <c r="J71" t="s">
-        <v>643</v>
-      </c>
-      <c r="K71" t="s">
-        <v>644</v>
       </c>
       <c r="M71" t="s">
         <v>28</v>
@@ -6207,21 +6201,21 @@
         <v>30</v>
       </c>
       <c r="P71" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>643</v>
+      </c>
+      <c r="B72" t="s">
+        <v>644</v>
+      </c>
+      <c r="C72" t="s">
         <v>645</v>
       </c>
-      <c r="B72" t="s">
-        <v>646</v>
-      </c>
-      <c r="C72" t="s">
-        <v>647</v>
-      </c>
       <c r="D72" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E72" t="s">
         <v>20</v>
@@ -6230,19 +6224,19 @@
         <v>21</v>
       </c>
       <c r="G72" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="H72" t="s">
+        <v>646</v>
+      </c>
+      <c r="I72" t="s">
+        <v>647</v>
+      </c>
+      <c r="J72" t="s">
         <v>648</v>
       </c>
-      <c r="I72" t="s">
+      <c r="K72" t="s">
         <v>649</v>
-      </c>
-      <c r="J72" t="s">
-        <v>650</v>
-      </c>
-      <c r="K72" t="s">
-        <v>651</v>
       </c>
       <c r="M72" t="s">
         <v>28</v>
@@ -6251,21 +6245,21 @@
         <v>30</v>
       </c>
       <c r="P72" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>650</v>
+      </c>
+      <c r="B73" t="s">
+        <v>651</v>
+      </c>
+      <c r="C73" t="s">
         <v>652</v>
       </c>
-      <c r="B73" t="s">
-        <v>653</v>
-      </c>
-      <c r="C73" t="s">
-        <v>654</v>
-      </c>
       <c r="D73" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E73" t="s">
         <v>20</v>
@@ -6274,16 +6268,16 @@
         <v>54</v>
       </c>
       <c r="G73" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="H73" t="s">
+        <v>653</v>
+      </c>
+      <c r="I73" t="s">
+        <v>654</v>
+      </c>
+      <c r="J73" t="s">
         <v>655</v>
-      </c>
-      <c r="I73" t="s">
-        <v>656</v>
-      </c>
-      <c r="J73" t="s">
-        <v>657</v>
       </c>
       <c r="M73" t="s">
         <v>28</v>
@@ -6292,21 +6286,21 @@
         <v>30</v>
       </c>
       <c r="P73" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>656</v>
+      </c>
+      <c r="B74" t="s">
+        <v>657</v>
+      </c>
+      <c r="C74" t="s">
         <v>658</v>
       </c>
-      <c r="B74" t="s">
-        <v>659</v>
-      </c>
-      <c r="C74" t="s">
-        <v>660</v>
-      </c>
       <c r="D74" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E74" t="s">
         <v>20</v>
@@ -6315,16 +6309,16 @@
         <v>65</v>
       </c>
       <c r="G74" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="H74" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I74" t="s">
         <v>24</v>
       </c>
       <c r="J74" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="M74" t="s">
         <v>28</v>
@@ -6333,21 +6327,21 @@
         <v>30</v>
       </c>
       <c r="P74" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>661</v>
+      </c>
+      <c r="B75" t="s">
+        <v>662</v>
+      </c>
+      <c r="C75" t="s">
         <v>663</v>
       </c>
-      <c r="B75" t="s">
-        <v>664</v>
-      </c>
-      <c r="C75" t="s">
-        <v>665</v>
-      </c>
       <c r="D75" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E75" t="s">
         <v>64</v>
@@ -6356,19 +6350,19 @@
         <v>54</v>
       </c>
       <c r="G75" t="s">
+        <v>664</v>
+      </c>
+      <c r="H75" t="s">
+        <v>665</v>
+      </c>
+      <c r="I75" t="s">
         <v>666</v>
       </c>
-      <c r="H75" t="s">
+      <c r="J75" t="s">
         <v>667</v>
       </c>
-      <c r="I75" t="s">
+      <c r="K75" t="s">
         <v>668</v>
-      </c>
-      <c r="J75" t="s">
-        <v>669</v>
-      </c>
-      <c r="K75" t="s">
-        <v>670</v>
       </c>
       <c r="M75" t="s">
         <v>28</v>
@@ -6377,21 +6371,21 @@
         <v>30</v>
       </c>
       <c r="P75" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>669</v>
+      </c>
+      <c r="B76" t="s">
+        <v>670</v>
+      </c>
+      <c r="C76" t="s">
         <v>671</v>
       </c>
-      <c r="B76" t="s">
+      <c r="D76" t="s">
         <v>672</v>
-      </c>
-      <c r="C76" t="s">
-        <v>673</v>
-      </c>
-      <c r="D76" t="s">
-        <v>674</v>
       </c>
       <c r="E76" t="s">
         <v>20</v>
@@ -6400,42 +6394,42 @@
         <v>21</v>
       </c>
       <c r="G76" t="s">
+        <v>673</v>
+      </c>
+      <c r="H76" t="s">
+        <v>674</v>
+      </c>
+      <c r="I76" t="s">
         <v>675</v>
       </c>
-      <c r="H76" t="s">
+      <c r="J76" t="s">
         <v>676</v>
       </c>
-      <c r="I76" t="s">
+      <c r="K76" t="s">
         <v>677</v>
       </c>
-      <c r="J76" t="s">
-        <v>678</v>
-      </c>
-      <c r="K76" t="s">
-        <v>679</v>
-      </c>
       <c r="M76" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="O76" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P76" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>678</v>
+      </c>
+      <c r="B77" t="s">
+        <v>679</v>
+      </c>
+      <c r="C77" t="s">
         <v>680</v>
       </c>
-      <c r="B77" t="s">
-        <v>681</v>
-      </c>
-      <c r="C77" t="s">
-        <v>682</v>
-      </c>
       <c r="D77" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E77" t="s">
         <v>20</v>
@@ -6444,42 +6438,42 @@
         <v>21</v>
       </c>
       <c r="G77" t="s">
+        <v>681</v>
+      </c>
+      <c r="H77" t="s">
+        <v>682</v>
+      </c>
+      <c r="I77" t="s">
         <v>683</v>
       </c>
-      <c r="H77" t="s">
+      <c r="J77" t="s">
         <v>684</v>
       </c>
-      <c r="I77" t="s">
+      <c r="K77" t="s">
         <v>685</v>
       </c>
-      <c r="J77" t="s">
-        <v>686</v>
-      </c>
-      <c r="K77" t="s">
-        <v>687</v>
-      </c>
       <c r="M77" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="O77" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P77" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>686</v>
+      </c>
+      <c r="B78" t="s">
+        <v>687</v>
+      </c>
+      <c r="C78" t="s">
         <v>688</v>
       </c>
-      <c r="B78" t="s">
-        <v>689</v>
-      </c>
-      <c r="C78" t="s">
-        <v>690</v>
-      </c>
       <c r="D78" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E78" t="s">
         <v>64</v>
@@ -6488,42 +6482,42 @@
         <v>54</v>
       </c>
       <c r="G78" t="s">
+        <v>689</v>
+      </c>
+      <c r="H78" t="s">
+        <v>690</v>
+      </c>
+      <c r="I78" t="s">
         <v>691</v>
       </c>
-      <c r="H78" t="s">
+      <c r="J78" t="s">
         <v>692</v>
       </c>
-      <c r="I78" t="s">
+      <c r="K78" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="J78" t="s">
-        <v>694</v>
-      </c>
-      <c r="K78" s="3" t="s">
-        <v>695</v>
-      </c>
       <c r="M78" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="O78" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="P78" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>694</v>
+      </c>
+      <c r="B79" t="s">
+        <v>695</v>
+      </c>
+      <c r="C79" t="s">
         <v>696</v>
       </c>
-      <c r="B79" t="s">
+      <c r="D79" t="s">
         <v>697</v>
-      </c>
-      <c r="C79" t="s">
-        <v>698</v>
-      </c>
-      <c r="D79" t="s">
-        <v>699</v>
       </c>
       <c r="E79" t="s">
         <v>20</v>
@@ -6532,42 +6526,42 @@
         <v>54</v>
       </c>
       <c r="G79" t="s">
+        <v>698</v>
+      </c>
+      <c r="H79" t="s">
+        <v>699</v>
+      </c>
+      <c r="I79" t="s">
         <v>700</v>
       </c>
-      <c r="H79" t="s">
+      <c r="J79" t="s">
         <v>701</v>
       </c>
-      <c r="I79" t="s">
+      <c r="K79" t="s">
         <v>702</v>
       </c>
-      <c r="J79" t="s">
-        <v>703</v>
-      </c>
-      <c r="K79" t="s">
-        <v>704</v>
-      </c>
       <c r="M79" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="O79" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P79" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>703</v>
+      </c>
+      <c r="B80" t="s">
+        <v>704</v>
+      </c>
+      <c r="C80" t="s">
         <v>705</v>
       </c>
-      <c r="B80" t="s">
-        <v>706</v>
-      </c>
-      <c r="C80" t="s">
-        <v>707</v>
-      </c>
       <c r="D80" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E80" t="s">
         <v>20</v>
@@ -6576,42 +6570,42 @@
         <v>54</v>
       </c>
       <c r="G80" t="s">
+        <v>706</v>
+      </c>
+      <c r="H80" t="s">
+        <v>707</v>
+      </c>
+      <c r="I80" t="s">
         <v>708</v>
       </c>
-      <c r="H80" t="s">
+      <c r="J80" t="s">
         <v>709</v>
       </c>
-      <c r="I80" t="s">
+      <c r="K80" t="s">
         <v>710</v>
       </c>
-      <c r="J80" t="s">
-        <v>711</v>
-      </c>
-      <c r="K80" t="s">
-        <v>712</v>
-      </c>
       <c r="M80" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="O80" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P80" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>711</v>
+      </c>
+      <c r="B81" t="s">
+        <v>712</v>
+      </c>
+      <c r="C81" t="s">
         <v>713</v>
       </c>
-      <c r="B81" t="s">
-        <v>714</v>
-      </c>
-      <c r="C81" t="s">
-        <v>715</v>
-      </c>
       <c r="D81" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E81" t="s">
         <v>20</v>
@@ -6620,42 +6614,42 @@
         <v>54</v>
       </c>
       <c r="G81" t="s">
+        <v>714</v>
+      </c>
+      <c r="H81" t="s">
+        <v>715</v>
+      </c>
+      <c r="I81" t="s">
         <v>716</v>
       </c>
-      <c r="H81" t="s">
+      <c r="J81" t="s">
         <v>717</v>
       </c>
-      <c r="I81" t="s">
+      <c r="K81" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="J81" t="s">
-        <v>719</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>720</v>
-      </c>
       <c r="M81" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="O81" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="P81" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>719</v>
+      </c>
+      <c r="B82" t="s">
+        <v>720</v>
+      </c>
+      <c r="C82" t="s">
         <v>721</v>
       </c>
-      <c r="B82" t="s">
-        <v>722</v>
-      </c>
-      <c r="C82" t="s">
-        <v>723</v>
-      </c>
       <c r="D82" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E82" t="s">
         <v>20</v>
@@ -6664,39 +6658,39 @@
         <v>54</v>
       </c>
       <c r="G82" t="s">
+        <v>722</v>
+      </c>
+      <c r="H82" t="s">
+        <v>723</v>
+      </c>
+      <c r="I82" t="s">
         <v>724</v>
       </c>
-      <c r="H82" t="s">
+      <c r="J82" t="s">
         <v>725</v>
       </c>
-      <c r="I82" t="s">
-        <v>726</v>
-      </c>
-      <c r="J82" t="s">
-        <v>727</v>
-      </c>
       <c r="K82" s="3" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="M82" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="O82" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="P82" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>726</v>
+      </c>
+      <c r="B83" t="s">
+        <v>727</v>
+      </c>
+      <c r="C83" t="s">
         <v>728</v>
-      </c>
-      <c r="B83" t="s">
-        <v>729</v>
-      </c>
-      <c r="C83" t="s">
-        <v>730</v>
       </c>
       <c r="D83" t="s">
         <v>35</v>
@@ -6708,28 +6702,28 @@
         <v>54</v>
       </c>
       <c r="G83" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="H83" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="I83" t="s">
         <v>24</v>
       </c>
       <c r="J83" t="s">
+        <v>731</v>
+      </c>
+      <c r="K83" t="s">
+        <v>732</v>
+      </c>
+      <c r="L83" t="s">
         <v>733</v>
-      </c>
-      <c r="K83" t="s">
-        <v>734</v>
-      </c>
-      <c r="L83" t="s">
-        <v>735</v>
       </c>
       <c r="M83" t="s">
         <v>28</v>
       </c>
       <c r="N83" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="O83" t="s">
         <v>30</v>
@@ -6743,13 +6737,13 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>737</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>739</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>20</v>
@@ -6758,34 +6752,34 @@
         <v>54</v>
       </c>
       <c r="G84" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="I84" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="H84" s="3" t="s">
+      <c r="J84" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="I84" s="3" t="s">
+      <c r="K84" s="3" t="s">
         <v>742</v>
       </c>
-      <c r="J84" s="3" t="s">
+      <c r="L84" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="K84" s="3" t="s">
+      <c r="M84" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="N84" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="L84" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="M84" s="3" t="s">
+      <c r="O84" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="P84" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="N84" s="3" t="s">
-        <v>746</v>
-      </c>
-      <c r="O84" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="P84" s="3" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="85" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6793,13 +6787,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>747</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>749</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>74</v>
@@ -6808,34 +6802,34 @@
         <v>54</v>
       </c>
       <c r="G85" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="I85" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="H85" s="3" t="s">
+      <c r="J85" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="I85" s="3" t="s">
+      <c r="K85" s="3" t="s">
         <v>752</v>
       </c>
-      <c r="J85" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="K85" s="3" t="s">
-        <v>754</v>
-      </c>
       <c r="L85" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="O85" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="86" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6843,13 +6837,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>755</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>757</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>20</v>
@@ -6858,34 +6852,34 @@
         <v>65</v>
       </c>
       <c r="G86" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="I86" s="3" t="s">
         <v>758</v>
       </c>
-      <c r="H86" s="3" t="s">
+      <c r="J86" s="3" t="s">
         <v>759</v>
       </c>
-      <c r="I86" s="3" t="s">
+      <c r="K86" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="J86" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="K86" s="3" t="s">
-        <v>762</v>
-      </c>
       <c r="L86" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="O86" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P86" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="87" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6893,13 +6887,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>763</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>765</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>74</v>
@@ -6908,34 +6902,34 @@
         <v>54</v>
       </c>
       <c r="G87" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="I87" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="H87" s="3" t="s">
+      <c r="J87" s="3" t="s">
         <v>767</v>
       </c>
-      <c r="I87" s="3" t="s">
+      <c r="K87" s="3" t="s">
         <v>768</v>
       </c>
-      <c r="J87" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="K87" s="3" t="s">
-        <v>770</v>
-      </c>
       <c r="L87" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="N87" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="O87" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P87" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="88" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6943,13 +6937,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>771</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>773</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>20</v>
@@ -6958,34 +6952,34 @@
         <v>54</v>
       </c>
       <c r="G88" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="I88" s="3" t="s">
         <v>774</v>
       </c>
-      <c r="H88" s="3" t="s">
+      <c r="J88" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="I88" s="3" t="s">
+      <c r="K88" s="3" t="s">
         <v>776</v>
       </c>
-      <c r="J88" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="K88" s="3" t="s">
-        <v>778</v>
-      </c>
       <c r="L88" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="N88" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="O88" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P88" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="89" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6993,13 +6987,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>779</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>781</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>20</v>
@@ -7008,34 +7002,34 @@
         <v>54</v>
       </c>
       <c r="G89" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="I89" s="3" t="s">
         <v>782</v>
       </c>
-      <c r="H89" s="3" t="s">
+      <c r="J89" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="I89" s="3" t="s">
+      <c r="K89" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>785</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>786</v>
-      </c>
       <c r="L89" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P89" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="90" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7043,13 +7037,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>20</v>
@@ -7058,34 +7052,34 @@
         <v>54</v>
       </c>
       <c r="G90" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="I90" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="H90" s="3" t="s">
+      <c r="J90" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="I90" s="3" t="s">
+      <c r="K90" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="J90" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="K90" s="3" t="s">
-        <v>793</v>
-      </c>
       <c r="L90" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P90" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="91" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7093,13 +7087,13 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>20</v>
@@ -7108,34 +7102,34 @@
         <v>54</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="H91" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="J91" s="3" t="s">
         <v>796</v>
       </c>
-      <c r="I91" s="3" t="s">
+      <c r="K91" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>799</v>
-      </c>
       <c r="L91" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P91" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="92" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7143,13 +7137,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>20</v>
@@ -7158,34 +7152,34 @@
         <v>54</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="H92" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="J92" s="3" t="s">
         <v>802</v>
       </c>
-      <c r="I92" s="3" t="s">
+      <c r="K92" s="3" t="s">
         <v>803</v>
       </c>
-      <c r="J92" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="K92" s="3" t="s">
-        <v>805</v>
-      </c>
       <c r="L92" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P92" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="93" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7193,13 +7187,13 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>20</v>
@@ -7208,34 +7202,34 @@
         <v>54</v>
       </c>
       <c r="G93" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="I93" s="3" t="s">
         <v>808</v>
       </c>
-      <c r="H93" s="3" t="s">
+      <c r="J93" s="3" t="s">
         <v>809</v>
       </c>
-      <c r="I93" s="3" t="s">
+      <c r="K93" s="3" t="s">
         <v>810</v>
       </c>
-      <c r="J93" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="K93" s="3" t="s">
-        <v>812</v>
-      </c>
       <c r="L93" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P93" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="834">
   <si>
     <t>S.No.</t>
   </si>
@@ -2242,84 +2242,108 @@
     <t>Positive counterpart to TST_CLST_TC_22, which pairs a status and a label that match zero classes. TC_22 cannot distinguish AND from OR: if the filters were ORed, a zero-match pair would still return zero and TC_22 would still pass. This case is the only one that proves the AND. Added 2026-09-01 from the other team's TC_CLS_002, whose expected result states "Combined filters apply as an AND condition".</t>
   </si>
   <si>
+    <t>PASS. Combined filter (status Active + label A11y test) applied successfully; the page-level Clear link appeared, the 'Active classes (1)' heading updated, and exactly 1 matching class row (New Auto Test Class DND) was returned.</t>
+  </si>
+  <si>
+    <t>Automated — adminClassesTab.test.js (npm run P1AdminClassesTab_Thor, thor). Last run 2026-09-17: 24/24 passing.</t>
+  </si>
+  <si>
+    <t>Suite: adminClassesTab | 2026-09-17: Pass across 1 run</t>
+  </si>
+  <si>
+    <t>TST_GCAT_TC_11</t>
+  </si>
+  <si>
+    <t>Verify a grading category cannot be created with a name that already exists</t>
+  </si>
+  <si>
+    <t>#5 - Verify create grading category</t>
+  </si>
+  <si>
+    <t>On the Manage grading categories page, with at least one existing category whose name is known.</t>
+  </si>
+  <si>
+    <t>1. Note an existing category name and the current category count. 2. Click Create a grading category. 3. Enter the exact existing name. 4. Click Save. 5. Return to the list and re-count.</t>
+  </si>
+  <si>
+    <t>The name of a category already present in the school.</t>
+  </si>
+  <si>
+    <t>The duplicate name is not accepted: creation is blocked or warned per business rule, and the category count is unchanged. [ASSUMED] - the rule itself is unconfirmed; the other team's sheet also leaves it open ("handled per business rule").</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_CLS_005. We cover the empty name (TST_GCAT_TC_5) and the 50-character boundary (TST_GCAT_TC_3) but never re-use an existing name. Automation note: the GCAT suite deliberately generates names as AutoCat_create_&lt;epoch-ms&gt; to avoid collisions, so this case needs a fixed name plus a housekeeping step to remove it. Confirm the rule with the product owner before finalising the expected result - "blocked" and "warned but allowed" are different products.</t>
+  </si>
+  <si>
+    <t>PASS. Entering a duplicate category name disabled the Save button and displayed the inline validation message 'This name already exists'. The category count remained unchanged and the category name appeared exactly once in the list.</t>
+  </si>
+  <si>
+    <t>Automated as TST_GCAT_TC_11 in adminGradingCategories.test.js (npm run P1AdminGradingCategories_Thor). Verified live on thor (school FCN-CHZ-PDA). Resolved [ASSUMED] duplicate behavior.</t>
+  </si>
+  <si>
+    <t>Suite: adminGradingCategories | 2026-09-17: Pass across 2 runs</t>
+  </si>
+  <si>
+    <t>TST_GSCL_TC_15</t>
+  </si>
+  <si>
+    <t>Verify the Cambridge One default grading scale details page shows its classes list and notice but no bands section</t>
+  </si>
+  <si>
+    <t>#12 - Verify view details page of grading scale</t>
+  </si>
+  <si>
+    <t>On the Grading scales page. The system scale "Cambridge One grading scale" carries the default badge.</t>
+  </si>
+  <si>
+    <t>1. Open the Open drop down menu on "Cambridge One grading scale". 2. Click View details. 3. Read the page: heading, classes list, any notice, and whether a bands section is present.</t>
+  </si>
+  <si>
+    <t>The system scale "Cambridge One grading scale".</t>
+  </si>
+  <si>
+    <t>The details page shows the scale name, the linked Classes (n) list (or "No classes yet") and the pre-27-July-2023 notice. No "Grading scale bands" section is rendered, because the default scale's target varies by material. [ASSUMED] - the notice wording is not captured verbatim.</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_CLS_012, which opens both a custom scale and the default scale for comparison. Our TST_GSCL_TC_6 opens a custom scale only, and the default scale renders differently. The asymmetry is already recorded in this document's product reference and in TST_GSCL_TC_12's note - the case simply did not exist. Capture the notice text verbatim on the first live pass and clear the [ASSUMED].</t>
+  </si>
+  <si>
+    <t>PASS. The details page showed heading "Cambridge One grading scale", linked classes section heading "Classes (93)", and no "Grading scale bands" accordion section (element count 0).</t>
+  </si>
+  <si>
+    <t>Automated as TST_GSCL_TC_15 in adminGradingScales.test.js (npm run P1AdminGradingScales_Thor). Verified live on thor (school FCN-CHZ-PDA). Resolved [ASSUMED] notice/bands behavior.</t>
+  </si>
+  <si>
+    <t>Suite: adminGradingScales | 2026-09-17: Pass across 2 consecutive clean runs</t>
+  </si>
+  <si>
+    <t>TST_GSCL_TC_14</t>
+  </si>
+  <si>
+    <t>Verify a grading scale that is applied to a class cannot be deleted without warning</t>
+  </si>
+  <si>
+    <t>#15 - Verify deleting a grading scale</t>
+  </si>
+  <si>
+    <t>A non-default grading scale exists and is currently applied to at least one live class.</t>
+  </si>
+  <si>
+    <t>1. Apply a non-default scale to a class via Class grade settings. 2. Open the Grading scales page and that scale's Open drop down menu. 3. Click Delete. 4. Read the resulting dialog. 5. Cancel and confirm the scale is still listed and still applied to the class.</t>
+  </si>
+  <si>
+    <t>A non-default scale applied to &lt;CLASS_WITH_CUSTOM_SCALE&gt;.</t>
+  </si>
+  <si>
+    <t>Deletion of an in-use scale is prevented, or warns about the impact on the classes using it before proceeding, per business rule. The affected class(es) are identified to the admin. Cancelling leaves both the scale and the class assignment untouched. [ASSUMED] - behaviour and copy unconfirmed.</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_CLS_015_N1, which bundles two rules: the default scale and a scale in active use. Our TST_GSCL_TC_11 implements only the first. Suite placement: the precondition is a scale applied to a live class - the state the CGST suite already builds - so this case should run inside the CGST suite rather than the GSCL suite, exactly as TST_GSCL_TC_7 does.</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Blocked at design time (skill rule 4). TST_CLST_TC_4's Actual Result records that label VM1 matches no ACTIVE class on 3 July Test School 1. Unblock by applying an existing label to a known Active class on the target school, or by identifying a label/Active-class pair live; then ground the expected result and clear the [ASSUMED].</t>
-  </si>
-  <si>
-    <t>TST_GCAT_TC_10</t>
-  </si>
-  <si>
-    <t>Verify a grading category cannot be created with a name that already exists</t>
-  </si>
-  <si>
-    <t>#5 - Verify create grading category</t>
-  </si>
-  <si>
-    <t>On the Manage grading categories page, with at least one existing category whose name is known.</t>
-  </si>
-  <si>
-    <t>1. Note an existing category name and the current category count. 2. Click Create a grading category. 3. Enter the exact existing name. 4. Click Save. 5. Return to the list and re-count.</t>
-  </si>
-  <si>
-    <t>The name of a category already present in the school.</t>
-  </si>
-  <si>
-    <t>The duplicate name is not accepted: creation is blocked or warned per business rule, and the category count is unchanged. [ASSUMED] - the rule itself is unconfirmed; the other team's sheet also leaves it open ("handled per business rule").</t>
-  </si>
-  <si>
-    <t>Added 2026-09-01 from the other team's TC_CLS_005. We cover the empty name (TST_GCAT_TC_5) and the 50-character boundary (TST_GCAT_TC_3) but never re-use an existing name. Automation note: the GCAT suite deliberately generates names as AutoCat_create_&lt;epoch-ms&gt; to avoid collisions, so this case needs a fixed name plus a housekeeping step to remove it. Confirm the rule with the product owner before finalising the expected result - "blocked" and "warned but allowed" are different products.</t>
-  </si>
-  <si>
-    <t>TST_GSCL_TC_13</t>
-  </si>
-  <si>
-    <t>Verify the Cambridge One default grading scale details page shows its classes list and notice but no bands section</t>
-  </si>
-  <si>
-    <t>#12 - Verify view details page of grading scale</t>
-  </si>
-  <si>
-    <t>On the Grading scales page. The system scale "Cambridge One grading scale" carries the default badge.</t>
-  </si>
-  <si>
-    <t>1. Open the Open drop down menu on "Cambridge One grading scale". 2. Click View details. 3. Read the page: heading, classes list, any notice, and whether a bands section is present.</t>
-  </si>
-  <si>
-    <t>The system scale "Cambridge One grading scale".</t>
-  </si>
-  <si>
-    <t>The details page shows the scale name, the linked Classes (n) list (or "No classes yet") and the pre-27-July-2023 notice. No "Grading scale bands" section is rendered, because the default scale's target varies by material. [ASSUMED] - the notice wording is not captured verbatim.</t>
-  </si>
-  <si>
-    <t>Added 2026-09-01 from the other team's TC_CLS_012, which opens both a custom scale and the default scale for comparison. Our TST_GSCL_TC_6 opens a custom scale only, and the default scale renders differently. The asymmetry is already recorded in this document's product reference and in TST_GSCL_TC_12's note - the case simply did not exist. Capture the notice text verbatim on the first live pass and clear the [ASSUMED].</t>
-  </si>
-  <si>
-    <t>TST_GSCL_TC_14</t>
-  </si>
-  <si>
-    <t>Verify a grading scale that is applied to a class cannot be deleted without warning</t>
-  </si>
-  <si>
-    <t>#15 - Verify deleting a grading scale</t>
-  </si>
-  <si>
-    <t>A non-default grading scale exists and is currently applied to at least one live class.</t>
-  </si>
-  <si>
-    <t>1. Apply a non-default scale to a class via Class grade settings. 2. Open the Grading scales page and that scale's Open drop down menu. 3. Click Delete. 4. Read the resulting dialog. 5. Cancel and confirm the scale is still listed and still applied to the class.</t>
-  </si>
-  <si>
-    <t>A non-default scale applied to &lt;CLASS_WITH_CUSTOM_SCALE&gt;.</t>
-  </si>
-  <si>
-    <t>Deletion of an in-use scale is prevented, or warns about the impact on the classes using it before proceeding, per business rule. The affected class(es) are identified to the admin. Cancelling leaves both the scale and the class assignment untouched. [ASSUMED] - behaviour and copy unconfirmed.</t>
-  </si>
-  <si>
-    <t>Added 2026-09-01 from the other team's TC_CLS_015_N1, which bundles two rules: the default scale and a scale in active use. Our TST_GSCL_TC_11 implements only the first. Suite placement: the precondition is a scale applied to a live class - the state the CGST suite already builds - so this case should run inside the CGST suite rather than the GSCL suite, exactly as TST_GSCL_TC_7 does.</t>
-  </si>
-  <si>
     <t>TST_CGST_TC_7</t>
   </si>
   <si>
@@ -2344,7 +2368,7 @@
     <t>Added 2026-09-01 from the other team's TC_CLS_034, which covers weights, add and remove, and the 100% rule. Our TST_CGST_TC_3 only adds a category and TST_CGST_TC_6 only checks the 100% total, so removal was untested. Fits the existing CGST suite, which already creates and tears down its own class - no new fixture needed. Creates and mutates real data on that throwaway class.</t>
   </si>
   <si>
-    <t>TST_BCCF_TC_17</t>
+    <t>TST_CCLS_TC_24</t>
   </si>
   <si>
     <t>Verify the bulk Add teacher toolbar action applies the teacher to every selected class row</t>
@@ -2368,7 +2392,16 @@
     <t>Added 2026-09-01 from the other team's TC_CLS_036, which exercises the whole bulk toolbar. TST_BCCF_TC_9 covers bulk Start/End date only; its Remarks claim "the same pattern applies to bulk Add teacher / Add labels / Add Material" - a prose claim, not coverage. This case and TC_18-TC_21 turn that sentence into tests. Side-effect free - the form is not submitted.</t>
   </si>
   <si>
-    <t>TST_BCCF_TC_18</t>
+    <t>Teacher email applied to every selected row via bulk Add teacher toolbar action, and rows deselected after apply.</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_24 (bulk suite). [ASSUMED] deselect-after-apply verified live.</t>
+  </si>
+  <si>
+    <t>Automated as TST_CCLS_TC_24 | Suite: schoolAdminAddClassBulk | 2026-09-17: Pass</t>
+  </si>
+  <si>
+    <t>TST_CCLS_TC_25</t>
   </si>
   <si>
     <t>Verify the bulk Add Material toolbar action applies the material to every selected class row</t>
@@ -2389,7 +2422,16 @@
     <t>Added 2026-09-01 from TC_CLS_036 - see TST_BCCF_TC_17 Remarks. Side-effect free.</t>
   </si>
   <si>
-    <t>TST_BCCF_TC_19</t>
+    <t>Material applied to every selected row via bulk Add Material toolbar action, and rows deselected after apply.</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_25 (bulk suite). [ASSUMED] deselect-after-apply verified live.</t>
+  </si>
+  <si>
+    <t>Automated as TST_CCLS_TC_25 | Suite: schoolAdminAddClassBulk | 2026-09-17: Pass</t>
+  </si>
+  <si>
+    <t>TST_CCLS_TC_26</t>
   </si>
   <si>
     <t>Verify the bulk Add labels toolbar action applies the label to every selected class row</t>
@@ -2407,7 +2449,16 @@
     <t>Added 2026-09-01 from TC_CLS_036 - see TST_BCCF_TC_17 Remarks. Note TST_BCCF_TC_7 records that labels behave specially on Duplicate (an "Apply the labels to new classes too?" dialog); check whether the bulk label action raises anything similar. Side-effect free.</t>
   </si>
   <si>
-    <t>TST_BCCF_TC_20</t>
+    <t>Label applied to every selected row via bulk Add labels toolbar action, and rows deselected after apply.</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_26 (bulk suite). [ASSUMED] deselect-after-apply verified live.</t>
+  </si>
+  <si>
+    <t>Automated as TST_CCLS_TC_26 | Suite: schoolAdminAddClassBulk | 2026-09-17: Pass</t>
+  </si>
+  <si>
+    <t>TST_CCLS_TC_27</t>
   </si>
   <si>
     <t>Verify the bulk Show student progress toolbar action applies to every selected class row</t>
@@ -2425,7 +2476,16 @@
     <t>Added 2026-09-01 from TC_CLS_036. This is the toolbar control that produces a context class - the classes created this way are the subject of TST_CTXC_TC_1 and TST_CTXC_TC_2, so the two areas should be grounded in the same live pass. Side-effect free while the form is not submitted.</t>
   </si>
   <si>
-    <t>TST_BCCF_TC_21</t>
+    <t>Show student progress setting applied to selected rows via bulk toolbar action, confirming confirmation modal and applying setting across rows.</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_27 (bulk suite). [ASSUMED] resolved live.</t>
+  </si>
+  <si>
+    <t>Automated as TST_CCLS_TC_27 | Suite: schoolAdminAddClassBulk | 2026-09-17: Pass</t>
+  </si>
+  <si>
+    <t>TST_CCLS_TC_28</t>
   </si>
   <si>
     <t>Verify the bulk Remove toolbar action deletes exactly the selected class rows</t>
@@ -2444,6 +2504,15 @@
   </si>
   <si>
     <t>Added 2026-09-01 from TC_CLS_036. Deliberately leaves one row unselected: an action that removed all rows would still pass a case that only counted deletions. Side-effect free - the form is not submitted.</t>
+  </si>
+  <si>
+    <t>Exactly selected rows removed via bulk Remove toolbar action, confirmation dialog confirmed, Create N classes button count updated to remaining count, and unselected row survived.</t>
+  </si>
+  <si>
+    <t>Automated: TST_CCLS_TC_28 (bulk suite). [ASSUMED] confirmation dialog and surviving row verified live.</t>
+  </si>
+  <si>
+    <t>Automated as TST_CCLS_TC_28 | Suite: schoolAdminAddClassBulk | 2026-09-17: Pass</t>
   </si>
 </sst>
 </file>
@@ -6770,16 +6839,16 @@
         <v>743</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>249</v>
+        <v>28</v>
       </c>
       <c r="N84" s="3" t="s">
         <v>744</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>249</v>
+        <v>30</v>
       </c>
       <c r="P84" s="3" t="s">
-        <v>251</v>
+        <v>745</v>
       </c>
     </row>
     <row r="85" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6787,13 +6856,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>74</v>
@@ -6802,34 +6871,34 @@
         <v>54</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>564</v>
+        <v>28</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="O85" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>220</v>
+        <v>756</v>
       </c>
     </row>
     <row r="86" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6837,13 +6906,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>20</v>
@@ -6852,34 +6921,34 @@
         <v>65</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>743</v>
+        <v>765</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>564</v>
+        <v>28</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>743</v>
+        <v>766</v>
       </c>
       <c r="O86" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P86" s="3" t="s">
-        <v>462</v>
+        <v>767</v>
       </c>
     </row>
     <row r="87" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6887,13 +6956,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>74</v>
@@ -6902,28 +6971,28 @@
         <v>54</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>743</v>
+        <v>776</v>
       </c>
       <c r="M87" s="3" t="s">
         <v>564</v>
       </c>
       <c r="N87" s="3" t="s">
-        <v>743</v>
+        <v>776</v>
       </c>
       <c r="O87" s="3" t="s">
         <v>338</v>
@@ -6937,13 +7006,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>20</v>
@@ -6952,34 +7021,34 @@
         <v>54</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="K88" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="L88" s="3" t="s">
         <v>776</v>
-      </c>
-      <c r="L88" s="3" t="s">
-        <v>743</v>
       </c>
       <c r="M88" s="3" t="s">
         <v>564</v>
       </c>
       <c r="N88" s="3" t="s">
-        <v>743</v>
+        <v>776</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>30</v>
+        <v>338</v>
       </c>
       <c r="P88" s="3" t="s">
-        <v>280</v>
+        <v>339</v>
       </c>
     </row>
     <row r="89" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6987,13 +7056,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>20</v>
@@ -7002,34 +7071,34 @@
         <v>54</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>743</v>
+        <v>793</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>564</v>
+        <v>28</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>743</v>
+        <v>794</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>338</v>
+        <v>30</v>
       </c>
       <c r="P89" s="3" t="s">
-        <v>339</v>
+        <v>795</v>
       </c>
     </row>
     <row r="90" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7037,13 +7106,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>785</v>
+        <v>796</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>786</v>
+        <v>797</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>20</v>
@@ -7052,34 +7121,34 @@
         <v>54</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>787</v>
+        <v>798</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>788</v>
+        <v>799</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>789</v>
+        <v>800</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>790</v>
+        <v>801</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>791</v>
+        <v>802</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>743</v>
+        <v>803</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>564</v>
+        <v>28</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>743</v>
+        <v>804</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>338</v>
+        <v>30</v>
       </c>
       <c r="P90" s="3" t="s">
-        <v>339</v>
+        <v>805</v>
       </c>
     </row>
     <row r="91" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7087,13 +7156,13 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>792</v>
+        <v>806</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>793</v>
+        <v>807</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>20</v>
@@ -7102,34 +7171,34 @@
         <v>54</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>787</v>
+        <v>798</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>794</v>
+        <v>808</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>795</v>
+        <v>809</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>796</v>
+        <v>810</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>797</v>
+        <v>811</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>743</v>
+        <v>812</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>564</v>
+        <v>28</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>743</v>
+        <v>813</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>338</v>
+        <v>30</v>
       </c>
       <c r="P91" s="3" t="s">
-        <v>339</v>
+        <v>814</v>
       </c>
     </row>
     <row r="92" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7137,13 +7206,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>798</v>
+        <v>815</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>799</v>
+        <v>816</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>20</v>
@@ -7152,34 +7221,34 @@
         <v>54</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>787</v>
+        <v>798</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>800</v>
+        <v>817</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>801</v>
+        <v>818</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>802</v>
+        <v>819</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>803</v>
+        <v>820</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>743</v>
+        <v>821</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>564</v>
+        <v>28</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>743</v>
+        <v>822</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>338</v>
+        <v>30</v>
       </c>
       <c r="P92" s="3" t="s">
-        <v>339</v>
+        <v>823</v>
       </c>
     </row>
     <row r="93" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7187,13 +7256,13 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>804</v>
+        <v>824</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>805</v>
+        <v>825</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>20</v>
@@ -7202,34 +7271,34 @@
         <v>54</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>806</v>
+        <v>826</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>807</v>
+        <v>827</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>808</v>
+        <v>828</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>809</v>
+        <v>829</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>743</v>
+        <v>831</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>564</v>
+        <v>28</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>743</v>
+        <v>832</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>338</v>
+        <v>30</v>
       </c>
       <c r="P93" s="3" t="s">
-        <v>339</v>
+        <v>833</v>
       </c>
     </row>
   </sheetData>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="776">
   <si>
     <t>S.No.</t>
   </si>
@@ -736,39 +736,6 @@
     <t>PASS. A 50-character name was accepted and the category appeared in the list. Confirmed live that #gradingCategoryNameInput carries maxlength=50, so longer input cannot be typed - the [ASSUMED] on this TC is resolved.</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>TST_GCAT_TC_4</t>
-  </si>
-  <si>
-    <t>Verify the maximum-grading-categories limit is enforced</t>
-  </si>
-  <si>
-    <t>School already at the maximum number of grading categories.</t>
-  </si>
-  <si>
-    <t>1. Attempt to create another grading category.</t>
-  </si>
-  <si>
-    <t>Modal: You have reached the maximum number of grading categories for your school. Please remove at least one category to add a new one; no category created. [ASSUMED] exact max count.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. NOT AUTOMATED - BLOCKED. Deliberately absent from the test file, the TC repository and the execution file (not merely skipped), so it cannot run by accident.</t>
-  </si>
-  <si>
-    <t>- (not executed)</t>
-  </si>
-  <si>
-    <t>Blocked</t>
-  </si>
-  <si>
-    <t>BLOCKED (2026-08-18). The precondition is 'school is already at its maximum', so the test must first FILL the school with grading categories. Three problems: (1) the maximum is unknown, so the only way to find it is to keep creating until the app refuses; (2) 3 July Test School 1 (FCN-CHZ-PDA) is SHARED - while it sits at the cap, nobody else can create a grading category and other suites would fail with a misleading error (same cross-suite interference that broke two TST_CLST_TC_7 assertions on 2026-08-17); (3) if a run crashes before cleanup, the school stays full until cleared by hand. TO UNBLOCK, any one of: (a) a DEDICATED school used only by this test (recommended - cheapest and fully safe); (b) product/dev supply the exact maximum, plus agreement to accept the shared-school impact; (c) an environment where no other suite runs. The expected modal copy is already verified live (the modal is pre-rendered in the DOM), so once a school exists this is a short TC.</t>
-  </si>
-  <si>
-    <t>BLOCKED - see Comments for the blocker and its unblock route</t>
-  </si>
-  <si>
     <t>27</t>
   </si>
   <si>
@@ -1459,27 +1426,6 @@
     <t>As expected. '+ Add new grade' inserted a middle band between Highest and Lowest. Note the re-indexing: before the click rows are 0=Highest, 1=Lowest; after, 0=Highest, 1=new middle band, 2=Lowest. The middle band exposes BOTH From and To. Automation creates nothing here - it cancels out.</t>
   </si>
   <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>TST_GSCL_TC_4</t>
-  </si>
-  <si>
-    <t>Verify the maximum-grading-scales limit is enforced</t>
-  </si>
-  <si>
-    <t>School already at the maximum number of grading scales.</t>
-  </si>
-  <si>
-    <t>1. Attempt to create another grading scale.</t>
-  </si>
-  <si>
-    <t>Modal: You have reached the maximum number of grading scales for this school. Please remove at least one grading scale to add a new one; no scale created. [ASSUMED] exact maximum.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. The expected modal copy is now VERIFIED word for word - the modal is pre-rendered in the DOM, so it was captured without filling the school to its cap. Only triggering it is blocked (shared school).</t>
-  </si>
-  <si>
     <t>52</t>
   </si>
   <si>
@@ -1756,33 +1702,6 @@
     <t>Soft delete is restorable.</t>
   </si>
   <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>TST_CMGT_TC_4</t>
-  </si>
-  <si>
-    <t>Verify bulk-deleting multiple classes</t>
-  </si>
-  <si>
-    <t>On the Classes tab with &gt;=2 active classes.</t>
-  </si>
-  <si>
-    <t>1. Select multiple class checkboxes (or select-all). 2. Click Delete class. 3. Confirm Yes, delete N classes.</t>
-  </si>
-  <si>
-    <t>Multiple classes</t>
-  </si>
-  <si>
-    <t>Selected classes are soft-deleted together; confirmation reflects the count (Yes, delete N classes).</t>
-  </si>
-  <si>
-    <t>Excluded - Phase 1</t>
-  </si>
-  <si>
-    <t>Out of Phase 1 automation scope.</t>
-  </si>
-  <si>
     <t>64</t>
   </si>
   <si>
@@ -1807,30 +1726,6 @@
     <t>The 7 conditions (per AdminApp.xlsx) must all be satisfied.</t>
   </si>
   <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>TST_CMGT_TC_6</t>
-  </si>
-  <si>
-    <t>Verify bulk delete supports up to 50 classes</t>
-  </si>
-  <si>
-    <t>On the Classes tab with many classes.</t>
-  </si>
-  <si>
-    <t>1. Select up to 50 classes. 2. Click Delete class and confirm.</t>
-  </si>
-  <si>
-    <t>50 classes</t>
-  </si>
-  <si>
-    <t>Up to 50 classes can be selected and deleted in one action. [ASSUMED] confirm the 50-class maximum.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Scenario title references 50 classes.</t>
-  </si>
-  <si>
     <t>66</t>
   </si>
   <si>
@@ -2071,30 +1966,6 @@
     <t>Requires a seeded source class.</t>
   </si>
   <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>TST_CLON_TC_3</t>
-  </si>
-  <si>
-    <t>Verify components with no items are not selectable when copying</t>
-  </si>
-  <si>
-    <t>A source class that has 0 of one or more components.</t>
-  </si>
-  <si>
-    <t>1. Copy an Existing Class -&gt; select a source with empty components -&gt; Continue.</t>
-  </si>
-  <si>
-    <t>Source: SarthakTestClass1 (0 teachers/materials/assignments/rules)</t>
-  </si>
-  <si>
-    <t>Components with a count of 0 are disabled/unselectable (e.g. Teachers [0] disabled; Class grade settings - Not available).</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Observed live.</t>
-  </si>
-  <si>
     <t>78</t>
   </si>
   <si>
@@ -2144,51 +2015,6 @@
   </si>
   <si>
     <t>Expected result strengthened 2026-09-01 from the other team's TC_CLS_030, which gives the concrete assertion this case previously lacked - ours read only "behaves as expected", which nothing could fail. Allow a few minutes after creation: class creation is asynchronous. Depends on TST_BCCF_TC_20 (the bulk Show student progress toolbar action) for the class that produces this state.</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>TST_CTXC_TC_3</t>
-  </si>
-  <si>
-    <t>Verify the context class appears/behaves correctly in the teacher login</t>
-  </si>
-  <si>
-    <t>A context class exists; a teacher account associated with it.</t>
-  </si>
-  <si>
-    <t>1. Log in as the teacher. 2. Locate/open the context class.</t>
-  </si>
-  <si>
-    <t>Teacher account [ASSUMED]</t>
-  </si>
-  <si>
-    <t>The context class is visible and behaves correctly for the teacher role. [ASSUMED] needs a teacher test account.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Cross-role verification.</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>TST_CTXC_TC_4</t>
-  </si>
-  <si>
-    <t>Verify the context class appears/behaves correctly in the student login</t>
-  </si>
-  <si>
-    <t>A context class exists; a student account enrolled in it.</t>
-  </si>
-  <si>
-    <t>1. Log in as the student. 2. Locate/open the context class.</t>
-  </si>
-  <si>
-    <t>Student account [ASSUMED]</t>
-  </si>
-  <si>
-    <t>The context class is visible and behaves correctly for the student role. [ASSUMED] needs a student test account.</t>
   </si>
   <si>
     <t>82</t>
@@ -2873,7 +2699,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P93"/>
+  <dimension ref="A1:P86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -4184,19 +4010,19 @@
         <v>224</v>
       </c>
       <c r="E27" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F27" t="s">
         <v>54</v>
       </c>
       <c r="G27" t="s">
+        <v>235</v>
+      </c>
+      <c r="H27" t="s">
         <v>244</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>245</v>
-      </c>
-      <c r="I27" t="s">
-        <v>24</v>
       </c>
       <c r="J27" t="s">
         <v>246</v>
@@ -4208,60 +4034,57 @@
         <v>248</v>
       </c>
       <c r="M27" t="s">
-        <v>249</v>
+        <v>28</v>
       </c>
       <c r="N27" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="O27" t="s">
-        <v>249</v>
+        <v>30</v>
       </c>
       <c r="P27" t="s">
-        <v>251</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>249</v>
+      </c>
+      <c r="B28" t="s">
+        <v>250</v>
+      </c>
+      <c r="C28" t="s">
+        <v>251</v>
+      </c>
+      <c r="D28" t="s">
         <v>252</v>
       </c>
-      <c r="B28" t="s">
-        <v>253</v>
-      </c>
-      <c r="C28" t="s">
-        <v>254</v>
-      </c>
-      <c r="D28" t="s">
-        <v>224</v>
-      </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="F28" t="s">
         <v>54</v>
       </c>
       <c r="G28" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="H28" t="s">
+        <v>254</v>
+      </c>
+      <c r="I28" t="s">
         <v>255</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>256</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>257</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="L28" t="s">
         <v>258</v>
       </c>
-      <c r="L28" t="s">
-        <v>259</v>
-      </c>
       <c r="M28" t="s">
         <v>28</v>
-      </c>
-      <c r="N28" t="s">
-        <v>231</v>
       </c>
       <c r="O28" t="s">
         <v>30</v>
@@ -4272,16 +4095,16 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>259</v>
+      </c>
+      <c r="B29" t="s">
         <v>260</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>261</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>262</v>
-      </c>
-      <c r="D29" t="s">
-        <v>263</v>
       </c>
       <c r="E29" t="s">
         <v>20</v>
@@ -4290,31 +4113,31 @@
         <v>54</v>
       </c>
       <c r="G29" t="s">
+        <v>263</v>
+      </c>
+      <c r="H29" t="s">
         <v>264</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>265</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>266</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>267</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L29" t="s">
         <v>268</v>
       </c>
-      <c r="L29" t="s">
+      <c r="M29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O29" t="s">
+        <v>30</v>
+      </c>
+      <c r="P29" t="s">
         <v>269</v>
-      </c>
-      <c r="M29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O29" t="s">
-        <v>30</v>
-      </c>
-      <c r="P29" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -4334,7 +4157,7 @@
         <v>20</v>
       </c>
       <c r="F30" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G30" t="s">
         <v>274</v>
@@ -4343,63 +4166,66 @@
         <v>275</v>
       </c>
       <c r="I30" t="s">
+        <v>255</v>
+      </c>
+      <c r="J30" t="s">
         <v>276</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>277</v>
       </c>
-      <c r="K30" t="s">
+      <c r="L30" t="s">
         <v>278</v>
       </c>
-      <c r="L30" t="s">
-        <v>279</v>
-      </c>
       <c r="M30" t="s">
         <v>28</v>
       </c>
+      <c r="N30" t="s">
+        <v>231</v>
+      </c>
       <c r="O30" t="s">
         <v>30</v>
       </c>
       <c r="P30" t="s">
-        <v>280</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>279</v>
+      </c>
+      <c r="B31" t="s">
+        <v>280</v>
+      </c>
+      <c r="C31" t="s">
         <v>281</v>
       </c>
-      <c r="B31" t="s">
+      <c r="D31" t="s">
+        <v>273</v>
+      </c>
+      <c r="E31" t="s">
+        <v>64</v>
+      </c>
+      <c r="F31" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" t="s">
+        <v>253</v>
+      </c>
+      <c r="H31" t="s">
         <v>282</v>
       </c>
-      <c r="C31" t="s">
+      <c r="I31" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" t="s">
         <v>283</v>
       </c>
-      <c r="D31" t="s">
+      <c r="K31" t="s">
         <v>284</v>
       </c>
-      <c r="E31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F31" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="L31" t="s">
         <v>285</v>
-      </c>
-      <c r="H31" t="s">
-        <v>286</v>
-      </c>
-      <c r="I31" t="s">
-        <v>266</v>
-      </c>
-      <c r="J31" t="s">
-        <v>287</v>
-      </c>
-      <c r="K31" t="s">
-        <v>288</v>
-      </c>
-      <c r="L31" t="s">
-        <v>289</v>
       </c>
       <c r="M31" t="s">
         <v>28</v>
@@ -4416,66 +4242,66 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>286</v>
+      </c>
+      <c r="B32" t="s">
+        <v>287</v>
+      </c>
+      <c r="C32" t="s">
+        <v>288</v>
+      </c>
+      <c r="D32" t="s">
+        <v>289</v>
+      </c>
+      <c r="E32" t="s">
+        <v>20</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" t="s">
+        <v>36</v>
+      </c>
+      <c r="H32" t="s">
         <v>290</v>
-      </c>
-      <c r="B32" t="s">
-        <v>291</v>
-      </c>
-      <c r="C32" t="s">
-        <v>292</v>
-      </c>
-      <c r="D32" t="s">
-        <v>284</v>
-      </c>
-      <c r="E32" t="s">
-        <v>64</v>
-      </c>
-      <c r="F32" t="s">
-        <v>65</v>
-      </c>
-      <c r="G32" t="s">
-        <v>264</v>
-      </c>
-      <c r="H32" t="s">
-        <v>293</v>
       </c>
       <c r="I32" t="s">
         <v>24</v>
       </c>
       <c r="J32" t="s">
+        <v>291</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="L32" t="s">
+        <v>293</v>
+      </c>
+      <c r="M32" t="s">
+        <v>28</v>
+      </c>
+      <c r="N32" t="s">
         <v>294</v>
       </c>
-      <c r="K32" t="s">
+      <c r="O32" t="s">
+        <v>30</v>
+      </c>
+      <c r="P32" t="s">
         <v>295</v>
-      </c>
-      <c r="L32" t="s">
-        <v>296</v>
-      </c>
-      <c r="M32" t="s">
-        <v>28</v>
-      </c>
-      <c r="N32" t="s">
-        <v>231</v>
-      </c>
-      <c r="O32" t="s">
-        <v>30</v>
-      </c>
-      <c r="P32" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>296</v>
+      </c>
+      <c r="B33" t="s">
         <v>297</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>298</v>
       </c>
-      <c r="C33" t="s">
-        <v>299</v>
-      </c>
       <c r="D33" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E33" t="s">
         <v>20</v>
@@ -4484,18 +4310,18 @@
         <v>21</v>
       </c>
       <c r="G33" t="s">
-        <v>36</v>
+        <v>299</v>
       </c>
       <c r="H33" t="s">
+        <v>300</v>
+      </c>
+      <c r="I33" t="s">
         <v>301</v>
-      </c>
-      <c r="I33" t="s">
-        <v>24</v>
       </c>
       <c r="J33" t="s">
         <v>302</v>
       </c>
-      <c r="K33" s="3" t="s">
+      <c r="K33" t="s">
         <v>303</v>
       </c>
       <c r="L33" t="s">
@@ -4525,13 +4351,13 @@
         <v>309</v>
       </c>
       <c r="D34" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E34" t="s">
         <v>20</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G34" t="s">
         <v>310</v>
@@ -4575,7 +4401,7 @@
         <v>320</v>
       </c>
       <c r="D35" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E35" t="s">
         <v>20</v>
@@ -4584,31 +4410,31 @@
         <v>54</v>
       </c>
       <c r="G35" t="s">
+        <v>310</v>
+      </c>
+      <c r="H35" t="s">
         <v>321</v>
       </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
         <v>322</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>323</v>
       </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>324</v>
       </c>
-      <c r="K35" t="s">
+      <c r="L35" t="s">
         <v>325</v>
       </c>
-      <c r="L35" t="s">
+      <c r="M35" t="s">
+        <v>28</v>
+      </c>
+      <c r="N35" t="s">
         <v>326</v>
       </c>
-      <c r="M35" t="s">
-        <v>28</v>
-      </c>
-      <c r="N35" t="s">
+      <c r="O35" t="s">
         <v>327</v>
-      </c>
-      <c r="O35" t="s">
-        <v>30</v>
       </c>
       <c r="P35" t="s">
         <v>328</v>
@@ -4625,7 +4451,7 @@
         <v>331</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E36" t="s">
         <v>20</v>
@@ -4634,7 +4460,7 @@
         <v>54</v>
       </c>
       <c r="G36" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="H36" t="s">
         <v>332</v>
@@ -4645,131 +4471,131 @@
       <c r="J36" t="s">
         <v>334</v>
       </c>
-      <c r="K36" t="s">
+      <c r="L36" t="s">
         <v>335</v>
       </c>
-      <c r="L36" t="s">
+      <c r="M36" t="s">
+        <v>28</v>
+      </c>
+      <c r="N36" t="s">
         <v>336</v>
       </c>
-      <c r="M36" t="s">
-        <v>28</v>
-      </c>
-      <c r="N36" t="s">
+      <c r="O36" t="s">
+        <v>30</v>
+      </c>
+      <c r="P36" t="s">
         <v>337</v>
-      </c>
-      <c r="O36" t="s">
-        <v>338</v>
-      </c>
-      <c r="P36" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>338</v>
+      </c>
+      <c r="B37" t="s">
+        <v>339</v>
+      </c>
+      <c r="C37" t="s">
         <v>340</v>
       </c>
-      <c r="B37" t="s">
-        <v>341</v>
-      </c>
-      <c r="C37" t="s">
-        <v>342</v>
-      </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E37" t="s">
         <v>20</v>
       </c>
       <c r="F37" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G37" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="H37" t="s">
+        <v>341</v>
+      </c>
+      <c r="I37" t="s">
+        <v>342</v>
+      </c>
+      <c r="J37" t="s">
         <v>343</v>
       </c>
-      <c r="I37" t="s">
+      <c r="L37" t="s">
         <v>344</v>
       </c>
-      <c r="J37" t="s">
+      <c r="M37" t="s">
+        <v>28</v>
+      </c>
+      <c r="N37" t="s">
         <v>345</v>
       </c>
-      <c r="L37" t="s">
+      <c r="O37" t="s">
+        <v>30</v>
+      </c>
+      <c r="P37" t="s">
         <v>346</v>
-      </c>
-      <c r="M37" t="s">
-        <v>28</v>
-      </c>
-      <c r="N37" t="s">
-        <v>347</v>
-      </c>
-      <c r="O37" t="s">
-        <v>30</v>
-      </c>
-      <c r="P37" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>347</v>
+      </c>
+      <c r="B38" t="s">
+        <v>348</v>
+      </c>
+      <c r="C38" t="s">
         <v>349</v>
       </c>
-      <c r="B38" t="s">
-        <v>350</v>
-      </c>
-      <c r="C38" t="s">
-        <v>351</v>
-      </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E38" t="s">
         <v>20</v>
       </c>
       <c r="F38" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G38" t="s">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="H38" t="s">
+        <v>351</v>
+      </c>
+      <c r="I38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J38" t="s">
         <v>352</v>
       </c>
-      <c r="I38" t="s">
+      <c r="K38" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L38" t="s">
         <v>353</v>
       </c>
-      <c r="J38" t="s">
+      <c r="M38" t="s">
+        <v>28</v>
+      </c>
+      <c r="N38" t="s">
         <v>354</v>
       </c>
-      <c r="L38" t="s">
+      <c r="O38" t="s">
+        <v>30</v>
+      </c>
+      <c r="P38" t="s">
         <v>355</v>
-      </c>
-      <c r="M38" t="s">
-        <v>28</v>
-      </c>
-      <c r="N38" t="s">
-        <v>356</v>
-      </c>
-      <c r="O38" t="s">
-        <v>30</v>
-      </c>
-      <c r="P38" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>356</v>
+      </c>
+      <c r="B39" t="s">
+        <v>357</v>
+      </c>
+      <c r="C39" t="s">
         <v>358</v>
       </c>
-      <c r="B39" t="s">
-        <v>359</v>
-      </c>
-      <c r="C39" t="s">
-        <v>360</v>
-      </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E39" t="s">
         <v>20</v>
@@ -4778,19 +4604,19 @@
         <v>54</v>
       </c>
       <c r="G39" t="s">
+        <v>359</v>
+      </c>
+      <c r="H39" t="s">
+        <v>360</v>
+      </c>
+      <c r="I39" t="s">
         <v>361</v>
       </c>
-      <c r="H39" t="s">
+      <c r="J39" t="s">
         <v>362</v>
       </c>
-      <c r="I39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>363</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="L39" t="s">
         <v>364</v>
@@ -4819,7 +4645,7 @@
         <v>369</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E40" t="s">
         <v>20</v>
@@ -4834,139 +4660,136 @@
         <v>371</v>
       </c>
       <c r="I40" t="s">
+        <v>24</v>
+      </c>
+      <c r="J40" t="s">
         <v>372</v>
       </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
         <v>373</v>
       </c>
-      <c r="K40" t="s">
+      <c r="L40" t="s">
         <v>374</v>
       </c>
-      <c r="L40" t="s">
+      <c r="M40" t="s">
+        <v>28</v>
+      </c>
+      <c r="N40" t="s">
         <v>375</v>
       </c>
-      <c r="M40" t="s">
-        <v>28</v>
-      </c>
-      <c r="N40" t="s">
+      <c r="O40" t="s">
+        <v>30</v>
+      </c>
+      <c r="P40" t="s">
         <v>376</v>
-      </c>
-      <c r="O40" t="s">
-        <v>30</v>
-      </c>
-      <c r="P40" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>377</v>
+      </c>
+      <c r="B41" t="s">
         <v>378</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>379</v>
       </c>
-      <c r="C41" t="s">
-        <v>380</v>
-      </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E41" t="s">
         <v>20</v>
       </c>
       <c r="F41" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="G41" t="s">
-        <v>381</v>
+        <v>299</v>
       </c>
       <c r="H41" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I41" t="s">
         <v>24</v>
       </c>
       <c r="J41" t="s">
+        <v>381</v>
+      </c>
+      <c r="L41" t="s">
+        <v>382</v>
+      </c>
+      <c r="M41" t="s">
+        <v>28</v>
+      </c>
+      <c r="N41" t="s">
         <v>383</v>
       </c>
-      <c r="K41" t="s">
+      <c r="O41" t="s">
+        <v>30</v>
+      </c>
+      <c r="P41" t="s">
         <v>384</v>
-      </c>
-      <c r="L41" t="s">
-        <v>385</v>
-      </c>
-      <c r="M41" t="s">
-        <v>28</v>
-      </c>
-      <c r="N41" t="s">
-        <v>386</v>
-      </c>
-      <c r="O41" t="s">
-        <v>30</v>
-      </c>
-      <c r="P41" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B42" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C42" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D42" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E42" t="s">
         <v>20</v>
       </c>
       <c r="F42" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G42" t="s">
-        <v>310</v>
+        <v>388</v>
       </c>
       <c r="H42" t="s">
+        <v>389</v>
+      </c>
+      <c r="I42" t="s">
+        <v>390</v>
+      </c>
+      <c r="J42" t="s">
         <v>391</v>
       </c>
-      <c r="I42" t="s">
-        <v>24</v>
-      </c>
-      <c r="J42" t="s">
+      <c r="L42" t="s">
         <v>392</v>
       </c>
-      <c r="L42" t="s">
+      <c r="M42" t="s">
+        <v>28</v>
+      </c>
+      <c r="N42" t="s">
         <v>393</v>
       </c>
-      <c r="M42" t="s">
-        <v>28</v>
-      </c>
-      <c r="N42" t="s">
+      <c r="O42" t="s">
+        <v>30</v>
+      </c>
+      <c r="P42" t="s">
         <v>394</v>
-      </c>
-      <c r="O42" t="s">
-        <v>30</v>
-      </c>
-      <c r="P42" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>395</v>
+      </c>
+      <c r="B43" t="s">
         <v>396</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>397</v>
       </c>
-      <c r="C43" t="s">
-        <v>398</v>
-      </c>
       <c r="D43" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E43" t="s">
         <v>20</v>
@@ -4975,116 +4798,119 @@
         <v>54</v>
       </c>
       <c r="G43" t="s">
+        <v>398</v>
+      </c>
+      <c r="H43" t="s">
         <v>399</v>
       </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
+        <v>24</v>
+      </c>
+      <c r="J43" t="s">
         <v>400</v>
       </c>
-      <c r="I43" t="s">
+      <c r="K43" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="J43" t="s">
+      <c r="L43" t="s">
         <v>402</v>
       </c>
-      <c r="L43" t="s">
+      <c r="M43" t="s">
+        <v>28</v>
+      </c>
+      <c r="N43" t="s">
         <v>403</v>
       </c>
-      <c r="M43" t="s">
-        <v>28</v>
-      </c>
-      <c r="N43" t="s">
+      <c r="O43" t="s">
+        <v>30</v>
+      </c>
+      <c r="P43" t="s">
         <v>404</v>
-      </c>
-      <c r="O43" t="s">
-        <v>30</v>
-      </c>
-      <c r="P43" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>405</v>
+      </c>
+      <c r="B44" t="s">
         <v>406</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>407</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
+        <v>289</v>
+      </c>
+      <c r="E44" t="s">
+        <v>64</v>
+      </c>
+      <c r="F44" t="s">
+        <v>65</v>
+      </c>
+      <c r="G44" t="s">
         <v>408</v>
       </c>
-      <c r="D44" t="s">
-        <v>300</v>
-      </c>
-      <c r="E44" t="s">
-        <v>20</v>
-      </c>
-      <c r="F44" t="s">
-        <v>54</v>
-      </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>409</v>
       </c>
-      <c r="H44" t="s">
+      <c r="I44" t="s">
+        <v>237</v>
+      </c>
+      <c r="J44" t="s">
         <v>410</v>
       </c>
-      <c r="I44" t="s">
-        <v>24</v>
-      </c>
-      <c r="J44" t="s">
+      <c r="K44" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L44" t="s">
         <v>411</v>
       </c>
-      <c r="K44" s="3" t="s">
+      <c r="M44" t="s">
+        <v>28</v>
+      </c>
+      <c r="N44" t="s">
         <v>412</v>
       </c>
-      <c r="L44" t="s">
+      <c r="O44" t="s">
+        <v>30</v>
+      </c>
+      <c r="P44" t="s">
         <v>413</v>
-      </c>
-      <c r="M44" t="s">
-        <v>28</v>
-      </c>
-      <c r="N44" t="s">
-        <v>414</v>
-      </c>
-      <c r="O44" t="s">
-        <v>30</v>
-      </c>
-      <c r="P44" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>414</v>
+      </c>
+      <c r="B45" t="s">
+        <v>415</v>
+      </c>
+      <c r="C45" t="s">
         <v>416</v>
       </c>
-      <c r="B45" t="s">
-        <v>417</v>
-      </c>
-      <c r="C45" t="s">
-        <v>418</v>
-      </c>
       <c r="D45" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E45" t="s">
         <v>64</v>
       </c>
       <c r="F45" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G45" t="s">
+        <v>417</v>
+      </c>
+      <c r="H45" t="s">
+        <v>418</v>
+      </c>
+      <c r="I45" t="s">
         <v>419</v>
       </c>
-      <c r="H45" t="s">
+      <c r="J45" t="s">
         <v>420</v>
       </c>
-      <c r="I45" t="s">
-        <v>237</v>
-      </c>
-      <c r="J45" t="s">
+      <c r="K45" t="s">
         <v>421</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="L45" t="s">
         <v>422</v>
@@ -5113,157 +4939,154 @@
         <v>427</v>
       </c>
       <c r="D46" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E46" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F46" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G46" t="s">
+        <v>299</v>
+      </c>
+      <c r="H46" t="s">
         <v>428</v>
       </c>
-      <c r="H46" t="s">
+      <c r="I46" t="s">
         <v>429</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>430</v>
       </c>
-      <c r="J46" t="s">
+      <c r="K46" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L46" t="s">
         <v>431</v>
       </c>
-      <c r="K46" t="s">
+      <c r="M46" t="s">
+        <v>28</v>
+      </c>
+      <c r="N46" t="s">
         <v>432</v>
       </c>
-      <c r="L46" t="s">
+      <c r="O46" t="s">
+        <v>30</v>
+      </c>
+      <c r="P46" t="s">
         <v>433</v>
-      </c>
-      <c r="M46" t="s">
-        <v>28</v>
-      </c>
-      <c r="N46" t="s">
-        <v>434</v>
-      </c>
-      <c r="O46" t="s">
-        <v>30</v>
-      </c>
-      <c r="P46" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>434</v>
+      </c>
+      <c r="B47" t="s">
+        <v>435</v>
+      </c>
+      <c r="C47" t="s">
         <v>436</v>
       </c>
-      <c r="B47" t="s">
-        <v>437</v>
-      </c>
-      <c r="C47" t="s">
-        <v>438</v>
-      </c>
       <c r="D47" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E47" t="s">
         <v>74</v>
       </c>
       <c r="F47" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G47" t="s">
-        <v>310</v>
+        <v>408</v>
       </c>
       <c r="H47" t="s">
+        <v>437</v>
+      </c>
+      <c r="I47" t="s">
+        <v>438</v>
+      </c>
+      <c r="J47" t="s">
         <v>439</v>
-      </c>
-      <c r="I47" t="s">
-        <v>440</v>
-      </c>
-      <c r="J47" t="s">
-        <v>441</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>69</v>
       </c>
       <c r="L47" t="s">
+        <v>440</v>
+      </c>
+      <c r="M47" t="s">
+        <v>28</v>
+      </c>
+      <c r="N47" t="s">
+        <v>441</v>
+      </c>
+      <c r="O47" t="s">
+        <v>30</v>
+      </c>
+      <c r="P47" t="s">
         <v>442</v>
-      </c>
-      <c r="M47" t="s">
-        <v>28</v>
-      </c>
-      <c r="N47" t="s">
-        <v>443</v>
-      </c>
-      <c r="O47" t="s">
-        <v>30</v>
-      </c>
-      <c r="P47" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>443</v>
+      </c>
+      <c r="B48" t="s">
+        <v>444</v>
+      </c>
+      <c r="C48" t="s">
         <v>445</v>
       </c>
-      <c r="B48" t="s">
+      <c r="D48" t="s">
         <v>446</v>
       </c>
-      <c r="C48" t="s">
+      <c r="E48" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48" t="s">
+        <v>215</v>
+      </c>
+      <c r="H48" t="s">
         <v>447</v>
       </c>
-      <c r="D48" t="s">
-        <v>300</v>
-      </c>
-      <c r="E48" t="s">
-        <v>74</v>
-      </c>
-      <c r="F48" t="s">
-        <v>54</v>
-      </c>
-      <c r="G48" t="s">
-        <v>419</v>
-      </c>
-      <c r="H48" t="s">
+      <c r="I48" t="s">
+        <v>24</v>
+      </c>
+      <c r="J48" t="s">
         <v>448</v>
       </c>
-      <c r="I48" t="s">
+      <c r="K48" t="s">
         <v>449</v>
       </c>
-      <c r="J48" t="s">
+      <c r="L48" t="s">
         <v>450</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L48" t="s">
+      <c r="M48" t="s">
+        <v>28</v>
+      </c>
+      <c r="O48" t="s">
+        <v>30</v>
+      </c>
+      <c r="P48" t="s">
         <v>451</v>
-      </c>
-      <c r="M48" t="s">
-        <v>28</v>
-      </c>
-      <c r="N48" t="s">
-        <v>452</v>
-      </c>
-      <c r="O48" t="s">
-        <v>30</v>
-      </c>
-      <c r="P48" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>452</v>
+      </c>
+      <c r="B49" t="s">
+        <v>453</v>
+      </c>
+      <c r="C49" t="s">
         <v>454</v>
       </c>
-      <c r="B49" t="s">
+      <c r="D49" t="s">
         <v>455</v>
-      </c>
-      <c r="C49" t="s">
-        <v>456</v>
-      </c>
-      <c r="D49" t="s">
-        <v>457</v>
       </c>
       <c r="E49" t="s">
         <v>20</v>
@@ -5272,13 +5095,13 @@
         <v>21</v>
       </c>
       <c r="G49" t="s">
-        <v>215</v>
+        <v>456</v>
       </c>
       <c r="H49" t="s">
+        <v>457</v>
+      </c>
+      <c r="I49" t="s">
         <v>458</v>
-      </c>
-      <c r="I49" t="s">
-        <v>24</v>
       </c>
       <c r="J49" t="s">
         <v>459</v>
@@ -5296,46 +5119,46 @@
         <v>30</v>
       </c>
       <c r="P49" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>462</v>
+      </c>
+      <c r="B50" t="s">
         <v>463</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>464</v>
       </c>
-      <c r="C50" t="s">
-        <v>465</v>
-      </c>
       <c r="D50" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="E50" t="s">
         <v>20</v>
       </c>
       <c r="F50" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G50" t="s">
+        <v>465</v>
+      </c>
+      <c r="H50" t="s">
+        <v>466</v>
+      </c>
+      <c r="I50" t="s">
         <v>467</v>
       </c>
-      <c r="H50" t="s">
+      <c r="J50" t="s">
         <v>468</v>
       </c>
-      <c r="I50" t="s">
+      <c r="K50" t="s">
         <v>469</v>
       </c>
-      <c r="J50" t="s">
+      <c r="L50" t="s">
         <v>470</v>
       </c>
-      <c r="K50" t="s">
-        <v>471</v>
-      </c>
-      <c r="L50" t="s">
-        <v>472</v>
-      </c>
       <c r="M50" t="s">
         <v>28</v>
       </c>
@@ -5343,46 +5166,43 @@
         <v>30</v>
       </c>
       <c r="P50" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>471</v>
+      </c>
+      <c r="B51" t="s">
+        <v>472</v>
+      </c>
+      <c r="C51" t="s">
         <v>473</v>
       </c>
-      <c r="B51" t="s">
+      <c r="D51" t="s">
+        <v>455</v>
+      </c>
+      <c r="E51" t="s">
+        <v>74</v>
+      </c>
+      <c r="F51" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51" t="s">
+        <v>465</v>
+      </c>
+      <c r="H51" t="s">
         <v>474</v>
       </c>
-      <c r="C51" t="s">
+      <c r="I51" t="s">
         <v>475</v>
       </c>
-      <c r="D51" t="s">
-        <v>466</v>
-      </c>
-      <c r="E51" t="s">
-        <v>20</v>
-      </c>
-      <c r="F51" t="s">
-        <v>54</v>
-      </c>
-      <c r="G51" t="s">
+      <c r="J51" t="s">
         <v>476</v>
       </c>
-      <c r="H51" t="s">
+      <c r="L51" t="s">
         <v>477</v>
       </c>
-      <c r="I51" t="s">
-        <v>478</v>
-      </c>
-      <c r="J51" t="s">
-        <v>479</v>
-      </c>
-      <c r="K51" t="s">
-        <v>480</v>
-      </c>
-      <c r="L51" t="s">
-        <v>481</v>
-      </c>
       <c r="M51" t="s">
         <v>28</v>
       </c>
@@ -5390,74 +5210,74 @@
         <v>30</v>
       </c>
       <c r="P51" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B52" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C52" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="D52" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="E52" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="F52" t="s">
         <v>54</v>
       </c>
       <c r="G52" t="s">
+        <v>482</v>
+      </c>
+      <c r="H52" t="s">
+        <v>483</v>
+      </c>
+      <c r="I52" t="s">
+        <v>484</v>
+      </c>
+      <c r="J52" t="s">
         <v>485</v>
       </c>
-      <c r="H52" t="s">
+      <c r="L52" t="s">
         <v>486</v>
       </c>
-      <c r="I52" t="s">
-        <v>24</v>
-      </c>
-      <c r="J52" t="s">
-        <v>487</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>488</v>
-      </c>
       <c r="M52" t="s">
-        <v>249</v>
+        <v>28</v>
       </c>
       <c r="O52" t="s">
-        <v>249</v>
+        <v>30</v>
       </c>
       <c r="P52" t="s">
-        <v>251</v>
+        <v>451</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>487</v>
+      </c>
+      <c r="B53" t="s">
+        <v>488</v>
+      </c>
+      <c r="C53" t="s">
         <v>489</v>
       </c>
-      <c r="B53" t="s">
+      <c r="D53" t="s">
         <v>490</v>
       </c>
-      <c r="C53" t="s">
+      <c r="E53" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" t="s">
+        <v>54</v>
+      </c>
+      <c r="G53" t="s">
         <v>491</v>
-      </c>
-      <c r="D53" t="s">
-        <v>466</v>
-      </c>
-      <c r="E53" t="s">
-        <v>74</v>
-      </c>
-      <c r="F53" t="s">
-        <v>21</v>
-      </c>
-      <c r="G53" t="s">
-        <v>476</v>
       </c>
       <c r="H53" t="s">
         <v>492</v>
@@ -5468,8 +5288,11 @@
       <c r="J53" t="s">
         <v>494</v>
       </c>
+      <c r="K53" t="s">
+        <v>495</v>
+      </c>
       <c r="L53" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M53" t="s">
         <v>28</v>
@@ -5478,42 +5301,45 @@
         <v>30</v>
       </c>
       <c r="P53" t="s">
-        <v>462</v>
+        <v>269</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B54" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C54" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D54" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E54" t="s">
         <v>20</v>
       </c>
       <c r="F54" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G54" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H54" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="I54" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="J54" t="s">
         <v>503</v>
       </c>
+      <c r="K54" t="s">
+        <v>504</v>
+      </c>
       <c r="L54" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M54" t="s">
         <v>28</v>
@@ -5522,46 +5348,43 @@
         <v>30</v>
       </c>
       <c r="P54" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B55" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C55" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D55" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E55" t="s">
         <v>20</v>
       </c>
       <c r="F55" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G55" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H55" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I55" t="s">
-        <v>511</v>
+        <v>484</v>
       </c>
       <c r="J55" t="s">
         <v>512</v>
       </c>
-      <c r="K55" t="s">
+      <c r="L55" t="s">
         <v>513</v>
       </c>
-      <c r="L55" t="s">
-        <v>514</v>
-      </c>
       <c r="M55" t="s">
         <v>28</v>
       </c>
@@ -5569,46 +5392,43 @@
         <v>30</v>
       </c>
       <c r="P55" t="s">
-        <v>280</v>
+        <v>451</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>514</v>
+      </c>
+      <c r="B56" t="s">
         <v>515</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>516</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
+        <v>509</v>
+      </c>
+      <c r="E56" t="s">
+        <v>64</v>
+      </c>
+      <c r="F56" t="s">
+        <v>65</v>
+      </c>
+      <c r="G56" t="s">
         <v>517</v>
       </c>
-      <c r="D56" t="s">
+      <c r="H56" t="s">
         <v>518</v>
       </c>
-      <c r="E56" t="s">
-        <v>20</v>
-      </c>
-      <c r="F56" t="s">
-        <v>21</v>
-      </c>
-      <c r="G56" t="s">
+      <c r="I56" t="s">
+        <v>24</v>
+      </c>
+      <c r="J56" t="s">
         <v>519</v>
       </c>
-      <c r="H56" t="s">
+      <c r="L56" t="s">
         <v>520</v>
       </c>
-      <c r="I56" t="s">
-        <v>502</v>
-      </c>
-      <c r="J56" t="s">
-        <v>521</v>
-      </c>
-      <c r="K56" t="s">
-        <v>522</v>
-      </c>
-      <c r="L56" t="s">
-        <v>523</v>
-      </c>
       <c r="M56" t="s">
         <v>28</v>
       </c>
@@ -5616,43 +5436,46 @@
         <v>30</v>
       </c>
       <c r="P56" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>521</v>
+      </c>
+      <c r="B57" t="s">
+        <v>522</v>
+      </c>
+      <c r="C57" t="s">
+        <v>523</v>
+      </c>
+      <c r="D57" t="s">
+        <v>509</v>
+      </c>
+      <c r="E57" t="s">
+        <v>74</v>
+      </c>
+      <c r="F57" t="s">
+        <v>54</v>
+      </c>
+      <c r="G57" t="s">
         <v>524</v>
       </c>
-      <c r="B57" t="s">
+      <c r="H57" t="s">
         <v>525</v>
       </c>
-      <c r="C57" t="s">
+      <c r="I57" t="s">
         <v>526</v>
       </c>
-      <c r="D57" t="s">
+      <c r="J57" t="s">
         <v>527</v>
       </c>
-      <c r="E57" t="s">
-        <v>20</v>
-      </c>
-      <c r="F57" t="s">
-        <v>21</v>
-      </c>
-      <c r="G57" t="s">
+      <c r="K57" t="s">
         <v>528</v>
       </c>
-      <c r="H57" t="s">
+      <c r="L57" t="s">
         <v>529</v>
       </c>
-      <c r="I57" t="s">
-        <v>502</v>
-      </c>
-      <c r="J57" t="s">
-        <v>530</v>
-      </c>
-      <c r="L57" t="s">
-        <v>531</v>
-      </c>
       <c r="M57" t="s">
         <v>28</v>
       </c>
@@ -5660,43 +5483,43 @@
         <v>30</v>
       </c>
       <c r="P57" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>530</v>
+      </c>
+      <c r="B58" t="s">
+        <v>531</v>
+      </c>
+      <c r="C58" t="s">
         <v>532</v>
       </c>
-      <c r="B58" t="s">
+      <c r="D58" t="s">
         <v>533</v>
       </c>
-      <c r="C58" t="s">
+      <c r="E58" t="s">
+        <v>20</v>
+      </c>
+      <c r="F58" t="s">
+        <v>54</v>
+      </c>
+      <c r="G58" t="s">
         <v>534</v>
       </c>
-      <c r="D58" t="s">
-        <v>527</v>
-      </c>
-      <c r="E58" t="s">
-        <v>64</v>
-      </c>
-      <c r="F58" t="s">
-        <v>65</v>
-      </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>535</v>
       </c>
-      <c r="H58" t="s">
+      <c r="I58" t="s">
+        <v>484</v>
+      </c>
+      <c r="J58" t="s">
         <v>536</v>
       </c>
-      <c r="I58" t="s">
-        <v>24</v>
-      </c>
-      <c r="J58" t="s">
+      <c r="L58" t="s">
         <v>537</v>
       </c>
-      <c r="L58" t="s">
-        <v>538</v>
-      </c>
       <c r="M58" t="s">
         <v>28</v>
       </c>
@@ -5704,24 +5527,24 @@
         <v>30</v>
       </c>
       <c r="P58" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>538</v>
+      </c>
+      <c r="B59" t="s">
         <v>539</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>540</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>541</v>
       </c>
-      <c r="D59" t="s">
-        <v>527</v>
-      </c>
       <c r="E59" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="F59" t="s">
         <v>54</v>
@@ -5733,256 +5556,247 @@
         <v>543</v>
       </c>
       <c r="I59" t="s">
+        <v>333</v>
+      </c>
+      <c r="J59" t="s">
         <v>544</v>
       </c>
-      <c r="J59" t="s">
+      <c r="K59" t="s">
         <v>545</v>
       </c>
-      <c r="K59" t="s">
+      <c r="M59" t="s">
         <v>546</v>
       </c>
-      <c r="L59" t="s">
-        <v>547</v>
-      </c>
-      <c r="M59" t="s">
-        <v>28</v>
-      </c>
       <c r="O59" t="s">
-        <v>30</v>
+        <v>327</v>
       </c>
       <c r="P59" t="s">
-        <v>462</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>547</v>
+      </c>
+      <c r="B60" t="s">
         <v>548</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>549</v>
       </c>
-      <c r="C60" t="s">
-        <v>550</v>
-      </c>
       <c r="D60" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="E60" t="s">
         <v>20</v>
       </c>
       <c r="F60" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="G60" t="s">
+        <v>550</v>
+      </c>
+      <c r="H60" t="s">
+        <v>551</v>
+      </c>
+      <c r="I60" t="s">
         <v>552</v>
       </c>
-      <c r="H60" t="s">
+      <c r="J60" t="s">
         <v>553</v>
       </c>
-      <c r="I60" t="s">
-        <v>502</v>
-      </c>
-      <c r="J60" t="s">
-        <v>554</v>
-      </c>
-      <c r="L60" t="s">
-        <v>555</v>
-      </c>
       <c r="M60" t="s">
-        <v>28</v>
+        <v>546</v>
       </c>
       <c r="O60" t="s">
-        <v>30</v>
+        <v>327</v>
       </c>
       <c r="P60" t="s">
-        <v>462</v>
+        <v>328</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>554</v>
+      </c>
+      <c r="B61" t="s">
+        <v>555</v>
+      </c>
+      <c r="C61" t="s">
         <v>556</v>
       </c>
-      <c r="B61" t="s">
+      <c r="D61" t="s">
         <v>557</v>
-      </c>
-      <c r="C61" t="s">
-        <v>558</v>
-      </c>
-      <c r="D61" t="s">
-        <v>559</v>
       </c>
       <c r="E61" t="s">
         <v>20</v>
       </c>
       <c r="F61" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G61" t="s">
+        <v>558</v>
+      </c>
+      <c r="H61" t="s">
+        <v>559</v>
+      </c>
+      <c r="I61" t="s">
         <v>560</v>
       </c>
-      <c r="H61" t="s">
+      <c r="J61" t="s">
         <v>561</v>
       </c>
-      <c r="I61" t="s">
-        <v>344</v>
-      </c>
-      <c r="J61" t="s">
+      <c r="K61" t="s">
         <v>562</v>
       </c>
-      <c r="K61" t="s">
-        <v>563</v>
-      </c>
       <c r="M61" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="O61" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="P61" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>563</v>
+      </c>
+      <c r="B62" t="s">
+        <v>564</v>
+      </c>
+      <c r="C62" t="s">
         <v>565</v>
       </c>
-      <c r="B62" t="s">
-        <v>566</v>
-      </c>
-      <c r="C62" t="s">
-        <v>567</v>
-      </c>
       <c r="D62" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E62" t="s">
         <v>20</v>
       </c>
       <c r="F62" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G62" t="s">
+        <v>566</v>
+      </c>
+      <c r="H62" t="s">
+        <v>567</v>
+      </c>
+      <c r="I62" t="s">
         <v>568</v>
       </c>
-      <c r="H62" t="s">
+      <c r="J62" t="s">
         <v>569</v>
       </c>
-      <c r="I62" t="s">
+      <c r="K62" t="s">
         <v>570</v>
       </c>
-      <c r="J62" t="s">
-        <v>571</v>
-      </c>
       <c r="M62" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="O62" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="P62" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>571</v>
+      </c>
+      <c r="B63" t="s">
         <v>572</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>573</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
+        <v>557</v>
+      </c>
+      <c r="E63" t="s">
+        <v>64</v>
+      </c>
+      <c r="F63" t="s">
+        <v>65</v>
+      </c>
+      <c r="G63" t="s">
         <v>574</v>
       </c>
-      <c r="D63" t="s">
+      <c r="H63" t="s">
         <v>575</v>
       </c>
-      <c r="E63" t="s">
-        <v>20</v>
-      </c>
-      <c r="F63" t="s">
-        <v>21</v>
-      </c>
-      <c r="G63" t="s">
+      <c r="I63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J63" t="s">
         <v>576</v>
       </c>
-      <c r="H63" t="s">
-        <v>577</v>
-      </c>
-      <c r="I63" t="s">
-        <v>578</v>
-      </c>
-      <c r="J63" t="s">
-        <v>579</v>
-      </c>
-      <c r="K63" t="s">
-        <v>580</v>
-      </c>
       <c r="M63" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="O63" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="P63" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>577</v>
+      </c>
+      <c r="B64" t="s">
+        <v>578</v>
+      </c>
+      <c r="C64" t="s">
+        <v>579</v>
+      </c>
+      <c r="D64" t="s">
+        <v>557</v>
+      </c>
+      <c r="E64" t="s">
+        <v>74</v>
+      </c>
+      <c r="F64" t="s">
+        <v>54</v>
+      </c>
+      <c r="G64" t="s">
+        <v>580</v>
+      </c>
+      <c r="H64" t="s">
         <v>581</v>
       </c>
-      <c r="B64" t="s">
+      <c r="I64" t="s">
         <v>582</v>
       </c>
-      <c r="C64" t="s">
+      <c r="J64" t="s">
         <v>583</v>
       </c>
-      <c r="D64" t="s">
-        <v>575</v>
-      </c>
-      <c r="E64" t="s">
-        <v>20</v>
-      </c>
-      <c r="F64" t="s">
-        <v>21</v>
-      </c>
-      <c r="G64" t="s">
-        <v>584</v>
-      </c>
-      <c r="H64" t="s">
-        <v>585</v>
-      </c>
-      <c r="I64" t="s">
-        <v>586</v>
-      </c>
-      <c r="J64" t="s">
-        <v>587</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="M64" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="O64" t="s">
-        <v>588</v>
+        <v>327</v>
       </c>
       <c r="P64" t="s">
-        <v>589</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="B65" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="C65" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="D65" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="E65" t="s">
         <v>20</v>
@@ -5991,168 +5805,174 @@
         <v>54</v>
       </c>
       <c r="G65" t="s">
-        <v>593</v>
+        <v>36</v>
       </c>
       <c r="H65" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="I65" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="J65" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="K65" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="M65" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="O65" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="P65" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>592</v>
+      </c>
+      <c r="B66" t="s">
+        <v>593</v>
+      </c>
+      <c r="C66" t="s">
+        <v>594</v>
+      </c>
+      <c r="D66" t="s">
+        <v>595</v>
+      </c>
+      <c r="E66" t="s">
+        <v>20</v>
+      </c>
+      <c r="F66" t="s">
+        <v>21</v>
+      </c>
+      <c r="G66" t="s">
+        <v>596</v>
+      </c>
+      <c r="H66" t="s">
+        <v>597</v>
+      </c>
+      <c r="I66" t="s">
+        <v>24</v>
+      </c>
+      <c r="J66" t="s">
         <v>598</v>
       </c>
-      <c r="B66" t="s">
+      <c r="K66" t="s">
         <v>599</v>
       </c>
-      <c r="C66" t="s">
-        <v>600</v>
-      </c>
-      <c r="D66" t="s">
-        <v>575</v>
-      </c>
-      <c r="E66" t="s">
-        <v>64</v>
-      </c>
-      <c r="F66" t="s">
-        <v>54</v>
-      </c>
-      <c r="G66" t="s">
-        <v>601</v>
-      </c>
-      <c r="H66" t="s">
-        <v>602</v>
-      </c>
-      <c r="I66" t="s">
-        <v>603</v>
-      </c>
-      <c r="J66" t="s">
-        <v>604</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>605</v>
-      </c>
       <c r="M66" t="s">
-        <v>564</v>
+        <v>28</v>
       </c>
       <c r="O66" t="s">
-        <v>588</v>
+        <v>30</v>
       </c>
       <c r="P66" t="s">
-        <v>589</v>
+        <v>269</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>600</v>
+      </c>
+      <c r="B67" t="s">
+        <v>601</v>
+      </c>
+      <c r="C67" t="s">
+        <v>602</v>
+      </c>
+      <c r="D67" t="s">
+        <v>595</v>
+      </c>
+      <c r="E67" t="s">
+        <v>20</v>
+      </c>
+      <c r="F67" t="s">
+        <v>21</v>
+      </c>
+      <c r="G67" t="s">
+        <v>603</v>
+      </c>
+      <c r="H67" t="s">
+        <v>604</v>
+      </c>
+      <c r="I67" t="s">
+        <v>605</v>
+      </c>
+      <c r="J67" t="s">
         <v>606</v>
       </c>
-      <c r="B67" t="s">
+      <c r="K67" t="s">
         <v>607</v>
       </c>
-      <c r="C67" t="s">
-        <v>608</v>
-      </c>
-      <c r="D67" t="s">
-        <v>575</v>
-      </c>
-      <c r="E67" t="s">
-        <v>64</v>
-      </c>
-      <c r="F67" t="s">
-        <v>65</v>
-      </c>
-      <c r="G67" t="s">
-        <v>609</v>
-      </c>
-      <c r="H67" t="s">
-        <v>610</v>
-      </c>
-      <c r="I67" t="s">
-        <v>24</v>
-      </c>
-      <c r="J67" t="s">
-        <v>611</v>
-      </c>
       <c r="M67" t="s">
-        <v>564</v>
+        <v>28</v>
       </c>
       <c r="O67" t="s">
-        <v>338</v>
+        <v>30</v>
       </c>
       <c r="P67" t="s">
-        <v>339</v>
+        <v>269</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>608</v>
+      </c>
+      <c r="B68" t="s">
+        <v>609</v>
+      </c>
+      <c r="C68" t="s">
+        <v>610</v>
+      </c>
+      <c r="D68" t="s">
+        <v>595</v>
+      </c>
+      <c r="E68" t="s">
+        <v>20</v>
+      </c>
+      <c r="F68" t="s">
+        <v>21</v>
+      </c>
+      <c r="G68" t="s">
+        <v>603</v>
+      </c>
+      <c r="H68" t="s">
+        <v>611</v>
+      </c>
+      <c r="I68" t="s">
         <v>612</v>
       </c>
-      <c r="B68" t="s">
+      <c r="J68" t="s">
         <v>613</v>
       </c>
-      <c r="C68" t="s">
+      <c r="K68" t="s">
         <v>614</v>
       </c>
-      <c r="D68" t="s">
-        <v>575</v>
-      </c>
-      <c r="E68" t="s">
-        <v>74</v>
-      </c>
-      <c r="F68" t="s">
-        <v>54</v>
-      </c>
-      <c r="G68" t="s">
-        <v>615</v>
-      </c>
-      <c r="H68" t="s">
-        <v>616</v>
-      </c>
-      <c r="I68" t="s">
-        <v>617</v>
-      </c>
-      <c r="J68" t="s">
-        <v>618</v>
-      </c>
       <c r="M68" t="s">
-        <v>564</v>
+        <v>28</v>
       </c>
       <c r="O68" t="s">
-        <v>338</v>
+        <v>30</v>
       </c>
       <c r="P68" t="s">
-        <v>339</v>
+        <v>269</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B69" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C69" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="D69" t="s">
-        <v>622</v>
+        <v>595</v>
       </c>
       <c r="E69" t="s">
         <v>20</v>
@@ -6161,63 +5981,57 @@
         <v>54</v>
       </c>
       <c r="G69" t="s">
-        <v>36</v>
+        <v>603</v>
       </c>
       <c r="H69" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="I69" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="J69" t="s">
-        <v>625</v>
-      </c>
-      <c r="K69" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="M69" t="s">
-        <v>564</v>
+        <v>28</v>
       </c>
       <c r="O69" t="s">
-        <v>338</v>
+        <v>30</v>
       </c>
       <c r="P69" t="s">
-        <v>339</v>
+        <v>269</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B70" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="C70" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="D70" t="s">
-        <v>630</v>
+        <v>595</v>
       </c>
       <c r="E70" t="s">
         <v>20</v>
       </c>
       <c r="F70" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="G70" t="s">
-        <v>631</v>
+        <v>603</v>
       </c>
       <c r="H70" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="I70" t="s">
         <v>24</v>
       </c>
       <c r="J70" t="s">
-        <v>633</v>
-      </c>
-      <c r="K70" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="M70" t="s">
         <v>28</v>
@@ -6226,42 +6040,42 @@
         <v>30</v>
       </c>
       <c r="P70" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="B71" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="C71" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="D71" t="s">
+        <v>595</v>
+      </c>
+      <c r="E71" t="s">
+        <v>64</v>
+      </c>
+      <c r="F71" t="s">
+        <v>54</v>
+      </c>
+      <c r="G71" t="s">
+        <v>629</v>
+      </c>
+      <c r="H71" t="s">
         <v>630</v>
       </c>
-      <c r="E71" t="s">
-        <v>20</v>
-      </c>
-      <c r="F71" t="s">
-        <v>21</v>
-      </c>
-      <c r="G71" t="s">
-        <v>638</v>
-      </c>
-      <c r="H71" t="s">
-        <v>639</v>
-      </c>
       <c r="I71" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="J71" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="K71" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="M71" t="s">
         <v>28</v>
@@ -6270,21 +6084,21 @@
         <v>30</v>
       </c>
       <c r="P71" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="B72" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="C72" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="D72" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E72" t="s">
         <v>20</v>
@@ -6296,523 +6110,571 @@
         <v>638</v>
       </c>
       <c r="H72" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="I72" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="J72" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="K72" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="M72" t="s">
-        <v>28</v>
+        <v>546</v>
       </c>
       <c r="O72" t="s">
-        <v>30</v>
+        <v>327</v>
       </c>
       <c r="P72" t="s">
-        <v>280</v>
+        <v>328</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="B73" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="C73" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="D73" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E73" t="s">
         <v>20</v>
       </c>
       <c r="F73" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G73" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="H73" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="I73" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="J73" t="s">
-        <v>655</v>
+        <v>649</v>
+      </c>
+      <c r="K73" t="s">
+        <v>650</v>
       </c>
       <c r="M73" t="s">
-        <v>28</v>
+        <v>546</v>
       </c>
       <c r="O73" t="s">
-        <v>30</v>
+        <v>327</v>
       </c>
       <c r="P73" t="s">
-        <v>280</v>
+        <v>328</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="B74" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="C74" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="D74" t="s">
-        <v>630</v>
+        <v>654</v>
       </c>
       <c r="E74" t="s">
         <v>20</v>
       </c>
       <c r="F74" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G74" t="s">
-        <v>638</v>
+        <v>655</v>
       </c>
       <c r="H74" t="s">
+        <v>656</v>
+      </c>
+      <c r="I74" t="s">
+        <v>657</v>
+      </c>
+      <c r="J74" t="s">
+        <v>658</v>
+      </c>
+      <c r="K74" t="s">
         <v>659</v>
       </c>
-      <c r="I74" t="s">
-        <v>24</v>
-      </c>
-      <c r="J74" t="s">
-        <v>660</v>
-      </c>
       <c r="M74" t="s">
-        <v>28</v>
+        <v>546</v>
       </c>
       <c r="O74" t="s">
-        <v>30</v>
+        <v>327</v>
       </c>
       <c r="P74" t="s">
-        <v>280</v>
+        <v>328</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>660</v>
+      </c>
+      <c r="B75" t="s">
         <v>661</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>662</v>
       </c>
-      <c r="C75" t="s">
-        <v>663</v>
-      </c>
       <c r="D75" t="s">
-        <v>630</v>
+        <v>654</v>
       </c>
       <c r="E75" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="F75" t="s">
         <v>54</v>
       </c>
       <c r="G75" t="s">
+        <v>663</v>
+      </c>
+      <c r="H75" t="s">
         <v>664</v>
       </c>
-      <c r="H75" t="s">
+      <c r="I75" t="s">
         <v>665</v>
       </c>
-      <c r="I75" t="s">
+      <c r="J75" t="s">
         <v>666</v>
       </c>
-      <c r="J75" t="s">
+      <c r="K75" t="s">
         <v>667</v>
       </c>
-      <c r="K75" t="s">
-        <v>668</v>
-      </c>
       <c r="M75" t="s">
-        <v>28</v>
+        <v>546</v>
       </c>
       <c r="O75" t="s">
-        <v>30</v>
+        <v>327</v>
       </c>
       <c r="P75" t="s">
-        <v>280</v>
+        <v>328</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>668</v>
+      </c>
+      <c r="B76" t="s">
         <v>669</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>670</v>
       </c>
-      <c r="C76" t="s">
-        <v>671</v>
-      </c>
       <c r="D76" t="s">
-        <v>672</v>
+        <v>35</v>
       </c>
       <c r="E76" t="s">
         <v>20</v>
       </c>
       <c r="F76" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G76" t="s">
+        <v>671</v>
+      </c>
+      <c r="H76" t="s">
+        <v>672</v>
+      </c>
+      <c r="I76" t="s">
+        <v>24</v>
+      </c>
+      <c r="J76" t="s">
         <v>673</v>
       </c>
-      <c r="H76" t="s">
+      <c r="K76" t="s">
         <v>674</v>
       </c>
-      <c r="I76" t="s">
+      <c r="L76" t="s">
         <v>675</v>
       </c>
-      <c r="J76" t="s">
+      <c r="M76" t="s">
+        <v>28</v>
+      </c>
+      <c r="N76" t="s">
         <v>676</v>
       </c>
-      <c r="K76" t="s">
+      <c r="O76" t="s">
+        <v>30</v>
+      </c>
+      <c r="P76" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
+        <v>83</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="M76" t="s">
-        <v>564</v>
-      </c>
-      <c r="O76" t="s">
-        <v>338</v>
-      </c>
-      <c r="P76" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="C77" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="B77" t="s">
+      <c r="D77" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="C77" t="s">
+      <c r="E77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G77" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="D77" t="s">
-        <v>672</v>
-      </c>
-      <c r="E77" t="s">
+      <c r="H77" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N77" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="O77" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P77" s="3" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
+        <v>84</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N78" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P78" s="3" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
+        <v>85</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F77" t="s">
-        <v>21</v>
-      </c>
-      <c r="G77" t="s">
-        <v>681</v>
-      </c>
-      <c r="H77" t="s">
-        <v>682</v>
-      </c>
-      <c r="I77" t="s">
-        <v>683</v>
-      </c>
-      <c r="J77" t="s">
-        <v>684</v>
-      </c>
-      <c r="K77" t="s">
-        <v>685</v>
-      </c>
-      <c r="M77" t="s">
-        <v>564</v>
-      </c>
-      <c r="O77" t="s">
-        <v>338</v>
-      </c>
-      <c r="P77" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>686</v>
-      </c>
-      <c r="B78" t="s">
-        <v>687</v>
-      </c>
-      <c r="C78" t="s">
-        <v>688</v>
-      </c>
-      <c r="D78" t="s">
-        <v>672</v>
-      </c>
-      <c r="E78" t="s">
-        <v>64</v>
-      </c>
-      <c r="F78" t="s">
+      <c r="F79" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N79" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="O79" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P79" s="3" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
+        <v>86</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F80" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G78" t="s">
-        <v>689</v>
-      </c>
-      <c r="H78" t="s">
-        <v>690</v>
-      </c>
-      <c r="I78" t="s">
-        <v>691</v>
-      </c>
-      <c r="J78" t="s">
-        <v>692</v>
-      </c>
-      <c r="K78" s="3" t="s">
-        <v>693</v>
-      </c>
-      <c r="M78" t="s">
-        <v>564</v>
-      </c>
-      <c r="O78" t="s">
-        <v>588</v>
-      </c>
-      <c r="P78" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>694</v>
-      </c>
-      <c r="B79" t="s">
-        <v>695</v>
-      </c>
-      <c r="C79" t="s">
-        <v>696</v>
-      </c>
-      <c r="D79" t="s">
-        <v>697</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="G80" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="N80" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="P80" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
+        <v>87</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F81" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G79" t="s">
-        <v>698</v>
-      </c>
-      <c r="H79" t="s">
-        <v>699</v>
-      </c>
-      <c r="I79" t="s">
-        <v>700</v>
-      </c>
-      <c r="J79" t="s">
-        <v>701</v>
-      </c>
-      <c r="K79" t="s">
-        <v>702</v>
-      </c>
-      <c r="M79" t="s">
-        <v>564</v>
-      </c>
-      <c r="O79" t="s">
-        <v>338</v>
-      </c>
-      <c r="P79" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>703</v>
-      </c>
-      <c r="B80" t="s">
-        <v>704</v>
-      </c>
-      <c r="C80" t="s">
-        <v>705</v>
-      </c>
-      <c r="D80" t="s">
-        <v>697</v>
-      </c>
-      <c r="E80" t="s">
+      <c r="G81" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
+        <v>88</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F82" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G80" t="s">
-        <v>706</v>
-      </c>
-      <c r="H80" t="s">
-        <v>707</v>
-      </c>
-      <c r="I80" t="s">
-        <v>708</v>
-      </c>
-      <c r="J80" t="s">
-        <v>709</v>
-      </c>
-      <c r="K80" t="s">
-        <v>710</v>
-      </c>
-      <c r="M80" t="s">
-        <v>564</v>
-      </c>
-      <c r="O80" t="s">
-        <v>338</v>
-      </c>
-      <c r="P80" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>711</v>
-      </c>
-      <c r="B81" t="s">
-        <v>712</v>
-      </c>
-      <c r="C81" t="s">
-        <v>713</v>
-      </c>
-      <c r="D81" t="s">
-        <v>697</v>
-      </c>
-      <c r="E81" t="s">
+      <c r="G82" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="L82" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="M82" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N82" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P82" s="3" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="3">
+        <v>89</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F83" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G81" t="s">
-        <v>714</v>
-      </c>
-      <c r="H81" t="s">
-        <v>715</v>
-      </c>
-      <c r="I81" t="s">
-        <v>716</v>
-      </c>
-      <c r="J81" t="s">
-        <v>717</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="M81" t="s">
-        <v>564</v>
-      </c>
-      <c r="O81" t="s">
-        <v>588</v>
-      </c>
-      <c r="P81" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>719</v>
-      </c>
-      <c r="B82" t="s">
-        <v>720</v>
-      </c>
-      <c r="C82" t="s">
-        <v>721</v>
-      </c>
-      <c r="D82" t="s">
-        <v>697</v>
-      </c>
-      <c r="E82" t="s">
-        <v>20</v>
-      </c>
-      <c r="F82" t="s">
-        <v>54</v>
-      </c>
-      <c r="G82" t="s">
-        <v>722</v>
-      </c>
-      <c r="H82" t="s">
-        <v>723</v>
-      </c>
-      <c r="I82" t="s">
-        <v>724</v>
-      </c>
-      <c r="J82" t="s">
-        <v>725</v>
-      </c>
-      <c r="K82" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="M82" t="s">
-        <v>564</v>
-      </c>
-      <c r="O82" t="s">
-        <v>588</v>
-      </c>
-      <c r="P82" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>726</v>
-      </c>
-      <c r="B83" t="s">
-        <v>727</v>
-      </c>
-      <c r="C83" t="s">
-        <v>728</v>
-      </c>
-      <c r="D83" t="s">
-        <v>35</v>
-      </c>
-      <c r="E83" t="s">
-        <v>20</v>
-      </c>
-      <c r="F83" t="s">
-        <v>54</v>
-      </c>
-      <c r="G83" t="s">
-        <v>729</v>
-      </c>
-      <c r="H83" t="s">
-        <v>730</v>
-      </c>
-      <c r="I83" t="s">
-        <v>24</v>
-      </c>
-      <c r="J83" t="s">
-        <v>731</v>
-      </c>
-      <c r="K83" t="s">
-        <v>732</v>
-      </c>
-      <c r="L83" t="s">
-        <v>733</v>
-      </c>
-      <c r="M83" t="s">
-        <v>28</v>
-      </c>
-      <c r="N83" t="s">
-        <v>734</v>
-      </c>
-      <c r="O83" t="s">
-        <v>30</v>
-      </c>
-      <c r="P83" t="s">
-        <v>31</v>
+      <c r="G83" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="84" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>735</v>
+        <v>748</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>20</v>
@@ -6821,484 +6683,134 @@
         <v>54</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>739</v>
+        <v>750</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>741</v>
+        <v>752</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="M84" s="3" t="s">
         <v>28</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>744</v>
+        <v>755</v>
       </c>
       <c r="O84" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P84" s="3" t="s">
-        <v>745</v>
+        <v>756</v>
       </c>
     </row>
     <row r="85" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>746</v>
+        <v>757</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>747</v>
+        <v>758</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>748</v>
+        <v>729</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>54</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>750</v>
+        <v>759</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>751</v>
+        <v>760</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>752</v>
+        <v>761</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>754</v>
+        <v>763</v>
       </c>
       <c r="M85" s="3" t="s">
         <v>28</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>755</v>
+        <v>764</v>
       </c>
       <c r="O85" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>756</v>
+        <v>765</v>
       </c>
     </row>
     <row r="86" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>759</v>
+        <v>729</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="M86" s="3" t="s">
         <v>28</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="O86" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P86" s="3" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="3">
-        <v>86</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>771</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>773</v>
-      </c>
-      <c r="J87" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="K87" s="3" t="s">
         <v>775</v>
-      </c>
-      <c r="L87" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="M87" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="N87" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="O87" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="P87" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="3">
-        <v>87</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="J88" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="K88" s="3" t="s">
-        <v>784</v>
-      </c>
-      <c r="L88" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="M88" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="N88" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="O88" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="P88" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="3">
-        <v>88</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>785</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>788</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>789</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>793</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>794</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="3">
-        <v>89</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>796</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>797</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="I90" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="J90" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="K90" s="3" t="s">
-        <v>802</v>
-      </c>
-      <c r="L90" s="3" t="s">
-        <v>803</v>
-      </c>
-      <c r="M90" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N90" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="O90" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P90" s="3" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="3">
-        <v>90</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>806</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="L91" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="3">
-        <v>91</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>815</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>816</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>817</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>818</v>
-      </c>
-      <c r="J92" s="3" t="s">
-        <v>819</v>
-      </c>
-      <c r="K92" s="3" t="s">
-        <v>820</v>
-      </c>
-      <c r="L92" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="M92" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N92" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="O92" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P92" s="3" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="3">
-        <v>92</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>824</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>825</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>826</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>827</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>828</v>
-      </c>
-      <c r="J93" s="3" t="s">
-        <v>829</v>
-      </c>
-      <c r="K93" s="3" t="s">
-        <v>830</v>
-      </c>
-      <c r="L93" s="3" t="s">
-        <v>831</v>
-      </c>
-      <c r="M93" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N93" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="O93" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P93" s="3" t="s">
-        <v>833</v>
       </c>
     </row>
   </sheetData>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
@@ -2194,7 +2194,7 @@
     <t>Added 2026-09-01 from the other team's TC_CLS_034, which covers weights, add and remove, and the 100% rule. Our TST_CGST_TC_3 only adds a category and TST_CGST_TC_6 only checks the 100% total, so removal was untested. Fits the existing CGST suite, which already creates and tears down its own class - no new fixture needed. Creates and mutates real data on that throwaway class.</t>
   </si>
   <si>
-    <t>TST_CCLS_TC_24</t>
+    <t>TST_BCCF_TC_17</t>
   </si>
   <si>
     <t>Verify the bulk Add teacher toolbar action applies the teacher to every selected class row</t>
@@ -2227,7 +2227,7 @@
     <t>Automated as TST_CCLS_TC_24 | Suite: schoolAdminAddClassBulk | 2026-09-17: Pass</t>
   </si>
   <si>
-    <t>TST_CCLS_TC_25</t>
+    <t>TST_BCCF_TC_18</t>
   </si>
   <si>
     <t>Verify the bulk Add Material toolbar action applies the material to every selected class row</t>
@@ -2257,7 +2257,7 @@
     <t>Automated as TST_CCLS_TC_25 | Suite: schoolAdminAddClassBulk | 2026-09-17: Pass</t>
   </si>
   <si>
-    <t>TST_CCLS_TC_26</t>
+    <t>TST_BCCF_TC_19</t>
   </si>
   <si>
     <t>Verify the bulk Add labels toolbar action applies the label to every selected class row</t>
@@ -2284,7 +2284,7 @@
     <t>Automated as TST_CCLS_TC_26 | Suite: schoolAdminAddClassBulk | 2026-09-17: Pass</t>
   </si>
   <si>
-    <t>TST_CCLS_TC_27</t>
+    <t>TST_BCCF_TC_20</t>
   </si>
   <si>
     <t>Verify the bulk Show student progress toolbar action applies to every selected class row</t>
@@ -2311,7 +2311,7 @@
     <t>Automated as TST_CCLS_TC_27 | Suite: schoolAdminAddClassBulk | 2026-09-17: Pass</t>
   </si>
   <si>
-    <t>TST_CCLS_TC_28</t>
+    <t>TST_BCCF_TC_21</t>
   </si>
   <si>
     <t>Verify the bulk Remove toolbar action deletes exactly the selected class rows</t>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Classes/AdminApp_Classes_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="776">
   <si>
     <t>S.No.</t>
   </si>
@@ -736,39 +736,6 @@
     <t>PASS. A 50-character name was accepted and the category appeared in the list. Confirmed live that #gradingCategoryNameInput carries maxlength=50, so longer input cannot be typed - the [ASSUMED] on this TC is resolved.</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>TST_GCAT_TC_4</t>
-  </si>
-  <si>
-    <t>Verify the maximum-grading-categories limit is enforced</t>
-  </si>
-  <si>
-    <t>School already at the maximum number of grading categories.</t>
-  </si>
-  <si>
-    <t>1. Attempt to create another grading category.</t>
-  </si>
-  <si>
-    <t>Modal: You have reached the maximum number of grading categories for your school. Please remove at least one category to add a new one; no category created. [ASSUMED] exact max count.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. NOT AUTOMATED - BLOCKED. Deliberately absent from the test file, the TC repository and the execution file (not merely skipped), so it cannot run by accident.</t>
-  </si>
-  <si>
-    <t>- (not executed)</t>
-  </si>
-  <si>
-    <t>Blocked</t>
-  </si>
-  <si>
-    <t>BLOCKED (2026-08-18). The precondition is 'school is already at its maximum', so the test must first FILL the school with grading categories. Three problems: (1) the maximum is unknown, so the only way to find it is to keep creating until the app refuses; (2) 3 July Test School 1 (FCN-CHZ-PDA) is SHARED - while it sits at the cap, nobody else can create a grading category and other suites would fail with a misleading error (same cross-suite interference that broke two TST_CLST_TC_7 assertions on 2026-08-17); (3) if a run crashes before cleanup, the school stays full until cleared by hand. TO UNBLOCK, any one of: (a) a DEDICATED school used only by this test (recommended - cheapest and fully safe); (b) product/dev supply the exact maximum, plus agreement to accept the shared-school impact; (c) an environment where no other suite runs. The expected modal copy is already verified live (the modal is pre-rendered in the DOM), so once a school exists this is a short TC.</t>
-  </si>
-  <si>
-    <t>BLOCKED - see Comments for the blocker and its unblock route</t>
-  </si>
-  <si>
     <t>27</t>
   </si>
   <si>
@@ -1459,27 +1426,6 @@
     <t>As expected. '+ Add new grade' inserted a middle band between Highest and Lowest. Note the re-indexing: before the click rows are 0=Highest, 1=Lowest; after, 0=Highest, 1=new middle band, 2=Lowest. The middle band exposes BOTH From and To. Automation creates nothing here - it cancels out.</t>
   </si>
   <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>TST_GSCL_TC_4</t>
-  </si>
-  <si>
-    <t>Verify the maximum-grading-scales limit is enforced</t>
-  </si>
-  <si>
-    <t>School already at the maximum number of grading scales.</t>
-  </si>
-  <si>
-    <t>1. Attempt to create another grading scale.</t>
-  </si>
-  <si>
-    <t>Modal: You have reached the maximum number of grading scales for this school. Please remove at least one grading scale to add a new one; no scale created. [ASSUMED] exact maximum.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. The expected modal copy is now VERIFIED word for word - the modal is pre-rendered in the DOM, so it was captured without filling the school to its cap. Only triggering it is blocked (shared school).</t>
-  </si>
-  <si>
     <t>52</t>
   </si>
   <si>
@@ -1756,33 +1702,6 @@
     <t>Soft delete is restorable.</t>
   </si>
   <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>TST_CMGT_TC_4</t>
-  </si>
-  <si>
-    <t>Verify bulk-deleting multiple classes</t>
-  </si>
-  <si>
-    <t>On the Classes tab with &gt;=2 active classes.</t>
-  </si>
-  <si>
-    <t>1. Select multiple class checkboxes (or select-all). 2. Click Delete class. 3. Confirm Yes, delete N classes.</t>
-  </si>
-  <si>
-    <t>Multiple classes</t>
-  </si>
-  <si>
-    <t>Selected classes are soft-deleted together; confirmation reflects the count (Yes, delete N classes).</t>
-  </si>
-  <si>
-    <t>Excluded - Phase 1</t>
-  </si>
-  <si>
-    <t>Out of Phase 1 automation scope.</t>
-  </si>
-  <si>
     <t>64</t>
   </si>
   <si>
@@ -1807,30 +1726,6 @@
     <t>The 7 conditions (per AdminApp.xlsx) must all be satisfied.</t>
   </si>
   <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>TST_CMGT_TC_6</t>
-  </si>
-  <si>
-    <t>Verify bulk delete supports up to 50 classes</t>
-  </si>
-  <si>
-    <t>On the Classes tab with many classes.</t>
-  </si>
-  <si>
-    <t>1. Select up to 50 classes. 2. Click Delete class and confirm.</t>
-  </si>
-  <si>
-    <t>50 classes</t>
-  </si>
-  <si>
-    <t>Up to 50 classes can be selected and deleted in one action. [ASSUMED] confirm the 50-class maximum.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Scenario title references 50 classes.</t>
-  </si>
-  <si>
     <t>66</t>
   </si>
   <si>
@@ -2071,30 +1966,6 @@
     <t>Requires a seeded source class.</t>
   </si>
   <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>TST_CLON_TC_3</t>
-  </si>
-  <si>
-    <t>Verify components with no items are not selectable when copying</t>
-  </si>
-  <si>
-    <t>A source class that has 0 of one or more components.</t>
-  </si>
-  <si>
-    <t>1. Copy an Existing Class -&gt; select a source with empty components -&gt; Continue.</t>
-  </si>
-  <si>
-    <t>Source: SarthakTestClass1 (0 teachers/materials/assignments/rules)</t>
-  </si>
-  <si>
-    <t>Components with a count of 0 are disabled/unselectable (e.g. Teachers [0] disabled; Class grade settings - Not available).</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Observed live.</t>
-  </si>
-  <si>
     <t>78</t>
   </si>
   <si>
@@ -2146,51 +2017,6 @@
     <t>Expected result strengthened 2026-09-01 from the other team's TC_CLS_030, which gives the concrete assertion this case previously lacked - ours read only "behaves as expected", which nothing could fail. Allow a few minutes after creation: class creation is asynchronous. Depends on TST_BCCF_TC_20 (the bulk Show student progress toolbar action) for the class that produces this state.</t>
   </si>
   <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>TST_CTXC_TC_3</t>
-  </si>
-  <si>
-    <t>Verify the context class appears/behaves correctly in the teacher login</t>
-  </si>
-  <si>
-    <t>A context class exists; a teacher account associated with it.</t>
-  </si>
-  <si>
-    <t>1. Log in as the teacher. 2. Locate/open the context class.</t>
-  </si>
-  <si>
-    <t>Teacher account [ASSUMED]</t>
-  </si>
-  <si>
-    <t>The context class is visible and behaves correctly for the teacher role. [ASSUMED] needs a teacher test account.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Cross-role verification.</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>TST_CTXC_TC_4</t>
-  </si>
-  <si>
-    <t>Verify the context class appears/behaves correctly in the student login</t>
-  </si>
-  <si>
-    <t>A context class exists; a student account enrolled in it.</t>
-  </si>
-  <si>
-    <t>1. Log in as the student. 2. Locate/open the context class.</t>
-  </si>
-  <si>
-    <t>Student account [ASSUMED]</t>
-  </si>
-  <si>
-    <t>The context class is visible and behaves correctly for the student role. [ASSUMED] needs a student test account.</t>
-  </si>
-  <si>
     <t>82</t>
   </si>
   <si>
@@ -2368,7 +2194,7 @@
     <t>Added 2026-09-01 from the other team's TC_CLS_034, which covers weights, add and remove, and the 100% rule. Our TST_CGST_TC_3 only adds a category and TST_CGST_TC_6 only checks the 100% total, so removal was untested. Fits the existing CGST suite, which already creates and tears down its own class - no new fixture needed. Creates and mutates real data on that throwaway class.</t>
   </si>
   <si>
-    <t>TST_CCLS_TC_24</t>
+    <t>TST_BCCF_TC_17</t>
   </si>
   <si>
     <t>Verify the bulk Add teacher toolbar action applies the teacher to every selected class row</t>
@@ -2401,7 +2227,7 @@
     <t>Automated as TST_CCLS_TC_24 | Suite: schoolAdminAddClassBulk | 2026-09-17: Pass</t>
   </si>
   <si>
-    <t>TST_CCLS_TC_25</t>
+    <t>TST_BCCF_TC_18</t>
   </si>
   <si>
     <t>Verify the bulk Add Material toolbar action applies the material to every selected class row</t>
@@ -2431,7 +2257,7 @@
     <t>Automated as TST_CCLS_TC_25 | Suite: schoolAdminAddClassBulk | 2026-09-17: Pass</t>
   </si>
   <si>
-    <t>TST_CCLS_TC_26</t>
+    <t>TST_BCCF_TC_19</t>
   </si>
   <si>
     <t>Verify the bulk Add labels toolbar action applies the label to every selected class row</t>
@@ -2458,7 +2284,7 @@
     <t>Automated as TST_CCLS_TC_26 | Suite: schoolAdminAddClassBulk | 2026-09-17: Pass</t>
   </si>
   <si>
-    <t>TST_CCLS_TC_27</t>
+    <t>TST_BCCF_TC_20</t>
   </si>
   <si>
     <t>Verify the bulk Show student progress toolbar action applies to every selected class row</t>
@@ -2485,7 +2311,7 @@
     <t>Automated as TST_CCLS_TC_27 | Suite: schoolAdminAddClassBulk | 2026-09-17: Pass</t>
   </si>
   <si>
-    <t>TST_CCLS_TC_28</t>
+    <t>TST_BCCF_TC_21</t>
   </si>
   <si>
     <t>Verify the bulk Remove toolbar action deletes exactly the selected class rows</t>
@@ -2873,7 +2699,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P93"/>
+  <dimension ref="A1:P86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -4184,19 +4010,19 @@
         <v>224</v>
       </c>
       <c r="E27" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F27" t="s">
         <v>54</v>
       </c>
       <c r="G27" t="s">
+        <v>235</v>
+      </c>
+      <c r="H27" t="s">
         <v>244</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>245</v>
-      </c>
-      <c r="I27" t="s">
-        <v>24</v>
       </c>
       <c r="J27" t="s">
         <v>246</v>
@@ -4208,60 +4034,57 @@
         <v>248</v>
       </c>
       <c r="M27" t="s">
-        <v>249</v>
+        <v>28</v>
       </c>
       <c r="N27" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="O27" t="s">
-        <v>249</v>
+        <v>30</v>
       </c>
       <c r="P27" t="s">
-        <v>251</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>249</v>
+      </c>
+      <c r="B28" t="s">
+        <v>250</v>
+      </c>
+      <c r="C28" t="s">
+        <v>251</v>
+      </c>
+      <c r="D28" t="s">
         <v>252</v>
       </c>
-      <c r="B28" t="s">
-        <v>253</v>
-      </c>
-      <c r="C28" t="s">
-        <v>254</v>
-      </c>
-      <c r="D28" t="s">
-        <v>224</v>
-      </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="F28" t="s">
         <v>54</v>
       </c>
       <c r="G28" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="H28" t="s">
+        <v>254</v>
+      </c>
+      <c r="I28" t="s">
         <v>255</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>256</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>257</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="L28" t="s">
         <v>258</v>
       </c>
-      <c r="L28" t="s">
-        <v>259</v>
-      </c>
       <c r="M28" t="s">
         <v>28</v>
-      </c>
-      <c r="N28" t="s">
-        <v>231</v>
       </c>
       <c r="O28" t="s">
         <v>30</v>
@@ -4272,16 +4095,16 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>259</v>
+      </c>
+      <c r="B29" t="s">
         <v>260</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>261</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>262</v>
-      </c>
-      <c r="D29" t="s">
-        <v>263</v>
       </c>
       <c r="E29" t="s">
         <v>20</v>
@@ -4290,31 +4113,31 @@
         <v>54</v>
       </c>
       <c r="G29" t="s">
+        <v>263</v>
+      </c>
+      <c r="H29" t="s">
         <v>264</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>265</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>266</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>267</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L29" t="s">
         <v>268</v>
       </c>
-      <c r="L29" t="s">
+      <c r="M29" t="s">
+        <v>28</v>
+      </c>
+      <c r="O29" t="s">
+        <v>30</v>
+      </c>
+      <c r="P29" t="s">
         <v>269</v>
-      </c>
-      <c r="M29" t="s">
-        <v>28</v>
-      </c>
-      <c r="O29" t="s">
-        <v>30</v>
-      </c>
-      <c r="P29" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -4334,7 +4157,7 @@
         <v>20</v>
       </c>
       <c r="F30" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G30" t="s">
         <v>274</v>
@@ -4343,63 +4166,66 @@
         <v>275</v>
       </c>
       <c r="I30" t="s">
+        <v>255</v>
+      </c>
+      <c r="J30" t="s">
         <v>276</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>277</v>
       </c>
-      <c r="K30" t="s">
+      <c r="L30" t="s">
         <v>278</v>
       </c>
-      <c r="L30" t="s">
-        <v>279</v>
-      </c>
       <c r="M30" t="s">
         <v>28</v>
       </c>
+      <c r="N30" t="s">
+        <v>231</v>
+      </c>
       <c r="O30" t="s">
         <v>30</v>
       </c>
       <c r="P30" t="s">
-        <v>280</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>279</v>
+      </c>
+      <c r="B31" t="s">
+        <v>280</v>
+      </c>
+      <c r="C31" t="s">
         <v>281</v>
       </c>
-      <c r="B31" t="s">
+      <c r="D31" t="s">
+        <v>273</v>
+      </c>
+      <c r="E31" t="s">
+        <v>64</v>
+      </c>
+      <c r="F31" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" t="s">
+        <v>253</v>
+      </c>
+      <c r="H31" t="s">
         <v>282</v>
       </c>
-      <c r="C31" t="s">
+      <c r="I31" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" t="s">
         <v>283</v>
       </c>
-      <c r="D31" t="s">
+      <c r="K31" t="s">
         <v>284</v>
       </c>
-      <c r="E31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F31" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="L31" t="s">
         <v>285</v>
-      </c>
-      <c r="H31" t="s">
-        <v>286</v>
-      </c>
-      <c r="I31" t="s">
-        <v>266</v>
-      </c>
-      <c r="J31" t="s">
-        <v>287</v>
-      </c>
-      <c r="K31" t="s">
-        <v>288</v>
-      </c>
-      <c r="L31" t="s">
-        <v>289</v>
       </c>
       <c r="M31" t="s">
         <v>28</v>
@@ -4416,66 +4242,66 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>286</v>
+      </c>
+      <c r="B32" t="s">
+        <v>287</v>
+      </c>
+      <c r="C32" t="s">
+        <v>288</v>
+      </c>
+      <c r="D32" t="s">
+        <v>289</v>
+      </c>
+      <c r="E32" t="s">
+        <v>20</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" t="s">
+        <v>36</v>
+      </c>
+      <c r="H32" t="s">
         <v>290</v>
-      </c>
-      <c r="B32" t="s">
-        <v>291</v>
-      </c>
-      <c r="C32" t="s">
-        <v>292</v>
-      </c>
-      <c r="D32" t="s">
-        <v>284</v>
-      </c>
-      <c r="E32" t="s">
-        <v>64</v>
-      </c>
-      <c r="F32" t="s">
-        <v>65</v>
-      </c>
-      <c r="G32" t="s">
-        <v>264</v>
-      </c>
-      <c r="H32" t="s">
-        <v>293</v>
       </c>
       <c r="I32" t="s">
         <v>24</v>
       </c>
       <c r="J32" t="s">
+        <v>291</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="L32" t="s">
+        <v>293</v>
+      </c>
+      <c r="M32" t="s">
+        <v>28</v>
+      </c>
+      <c r="N32" t="s">
         <v>294</v>
       </c>
-      <c r="K32" t="s">
+      <c r="O32" t="s">
+        <v>30</v>
+      </c>
+      <c r="P32" t="s">
         <v>295</v>
-      </c>
-      <c r="L32" t="s">
-        <v>296</v>
-      </c>
-      <c r="M32" t="s">
-        <v>28</v>
-      </c>
-      <c r="N32" t="s">
-        <v>231</v>
-      </c>
-      <c r="O32" t="s">
-        <v>30</v>
-      </c>
-      <c r="P32" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>296</v>
+      </c>
+      <c r="B33" t="s">
         <v>297</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>298</v>
       </c>
-      <c r="C33" t="s">
-        <v>299</v>
-      </c>
       <c r="D33" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E33" t="s">
         <v>20</v>
@@ -4484,18 +4310,18 @@
         <v>21</v>
       </c>
       <c r="G33" t="s">
-        <v>36</v>
+        <v>299</v>
       </c>
       <c r="H33" t="s">
+        <v>300</v>
+      </c>
+      <c r="I33" t="s">
         <v>301</v>
-      </c>
-      <c r="I33" t="s">
-        <v>24</v>
       </c>
       <c r="J33" t="s">
         <v>302</v>
       </c>
-      <c r="K33" s="3" t="s">
+      <c r="K33" t="s">
         <v>303</v>
       </c>
       <c r="L33" t="s">
@@ -4525,13 +4351,13 @@
         <v>309</v>
       </c>
       <c r="D34" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E34" t="s">
         <v>20</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G34" t="s">
         <v>310</v>
@@ -4575,7 +4401,7 @@
         <v>320</v>
       </c>
       <c r="D35" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E35" t="s">
         <v>20</v>
@@ -4584,31 +4410,31 @@
         <v>54</v>
       </c>
       <c r="G35" t="s">
+        <v>310</v>
+      </c>
+      <c r="H35" t="s">
         <v>321</v>
       </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
         <v>322</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>323</v>
       </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>324</v>
       </c>
-      <c r="K35" t="s">
+      <c r="L35" t="s">
         <v>325</v>
       </c>
-      <c r="L35" t="s">
+      <c r="M35" t="s">
+        <v>28</v>
+      </c>
+      <c r="N35" t="s">
         <v>326</v>
       </c>
-      <c r="M35" t="s">
-        <v>28</v>
-      </c>
-      <c r="N35" t="s">
+      <c r="O35" t="s">
         <v>327</v>
-      </c>
-      <c r="O35" t="s">
-        <v>30</v>
       </c>
       <c r="P35" t="s">
         <v>328</v>
@@ -4625,7 +4451,7 @@
         <v>331</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E36" t="s">
         <v>20</v>
@@ -4634,7 +4460,7 @@
         <v>54</v>
       </c>
       <c r="G36" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="H36" t="s">
         <v>332</v>
@@ -4645,131 +4471,131 @@
       <c r="J36" t="s">
         <v>334</v>
       </c>
-      <c r="K36" t="s">
+      <c r="L36" t="s">
         <v>335</v>
       </c>
-      <c r="L36" t="s">
+      <c r="M36" t="s">
+        <v>28</v>
+      </c>
+      <c r="N36" t="s">
         <v>336</v>
       </c>
-      <c r="M36" t="s">
-        <v>28</v>
-      </c>
-      <c r="N36" t="s">
+      <c r="O36" t="s">
+        <v>30</v>
+      </c>
+      <c r="P36" t="s">
         <v>337</v>
-      </c>
-      <c r="O36" t="s">
-        <v>338</v>
-      </c>
-      <c r="P36" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>338</v>
+      </c>
+      <c r="B37" t="s">
+        <v>339</v>
+      </c>
+      <c r="C37" t="s">
         <v>340</v>
       </c>
-      <c r="B37" t="s">
-        <v>341</v>
-      </c>
-      <c r="C37" t="s">
-        <v>342</v>
-      </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E37" t="s">
         <v>20</v>
       </c>
       <c r="F37" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G37" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="H37" t="s">
+        <v>341</v>
+      </c>
+      <c r="I37" t="s">
+        <v>342</v>
+      </c>
+      <c r="J37" t="s">
         <v>343</v>
       </c>
-      <c r="I37" t="s">
+      <c r="L37" t="s">
         <v>344</v>
       </c>
-      <c r="J37" t="s">
+      <c r="M37" t="s">
+        <v>28</v>
+      </c>
+      <c r="N37" t="s">
         <v>345</v>
       </c>
-      <c r="L37" t="s">
+      <c r="O37" t="s">
+        <v>30</v>
+      </c>
+      <c r="P37" t="s">
         <v>346</v>
-      </c>
-      <c r="M37" t="s">
-        <v>28</v>
-      </c>
-      <c r="N37" t="s">
-        <v>347</v>
-      </c>
-      <c r="O37" t="s">
-        <v>30</v>
-      </c>
-      <c r="P37" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>347</v>
+      </c>
+      <c r="B38" t="s">
+        <v>348</v>
+      </c>
+      <c r="C38" t="s">
         <v>349</v>
       </c>
-      <c r="B38" t="s">
-        <v>350</v>
-      </c>
-      <c r="C38" t="s">
-        <v>351</v>
-      </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E38" t="s">
         <v>20</v>
       </c>
       <c r="F38" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G38" t="s">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="H38" t="s">
+        <v>351</v>
+      </c>
+      <c r="I38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J38" t="s">
         <v>352</v>
       </c>
-      <c r="I38" t="s">
+      <c r="K38" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L38" t="s">
         <v>353</v>
       </c>
-      <c r="J38" t="s">
+      <c r="M38" t="s">
+        <v>28</v>
+      </c>
+      <c r="N38" t="s">
         <v>354</v>
       </c>
-      <c r="L38" t="s">
+      <c r="O38" t="s">
+        <v>30</v>
+      </c>
+      <c r="P38" t="s">
         <v>355</v>
-      </c>
-      <c r="M38" t="s">
-        <v>28</v>
-      </c>
-      <c r="N38" t="s">
-        <v>356</v>
-      </c>
-      <c r="O38" t="s">
-        <v>30</v>
-      </c>
-      <c r="P38" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>356</v>
+      </c>
+      <c r="B39" t="s">
+        <v>357</v>
+      </c>
+      <c r="C39" t="s">
         <v>358</v>
       </c>
-      <c r="B39" t="s">
-        <v>359</v>
-      </c>
-      <c r="C39" t="s">
-        <v>360</v>
-      </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E39" t="s">
         <v>20</v>
@@ -4778,19 +4604,19 @@
         <v>54</v>
       </c>
       <c r="G39" t="s">
+        <v>359</v>
+      </c>
+      <c r="H39" t="s">
+        <v>360</v>
+      </c>
+      <c r="I39" t="s">
         <v>361</v>
       </c>
-      <c r="H39" t="s">
+      <c r="J39" t="s">
         <v>362</v>
       </c>
-      <c r="I39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>363</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="L39" t="s">
         <v>364</v>
@@ -4819,7 +4645,7 @@
         <v>369</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E40" t="s">
         <v>20</v>
@@ -4834,139 +4660,136 @@
         <v>371</v>
       </c>
       <c r="I40" t="s">
+        <v>24</v>
+      </c>
+      <c r="J40" t="s">
         <v>372</v>
       </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
         <v>373</v>
       </c>
-      <c r="K40" t="s">
+      <c r="L40" t="s">
         <v>374</v>
       </c>
-      <c r="L40" t="s">
+      <c r="M40" t="s">
+        <v>28</v>
+      </c>
+      <c r="N40" t="s">
         <v>375</v>
       </c>
-      <c r="M40" t="s">
-        <v>28</v>
-      </c>
-      <c r="N40" t="s">
+      <c r="O40" t="s">
+        <v>30</v>
+      </c>
+      <c r="P40" t="s">
         <v>376</v>
-      </c>
-      <c r="O40" t="s">
-        <v>30</v>
-      </c>
-      <c r="P40" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>377</v>
+      </c>
+      <c r="B41" t="s">
         <v>378</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>379</v>
       </c>
-      <c r="C41" t="s">
-        <v>380</v>
-      </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E41" t="s">
         <v>20</v>
       </c>
       <c r="F41" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="G41" t="s">
-        <v>381</v>
+        <v>299</v>
       </c>
       <c r="H41" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I41" t="s">
         <v>24</v>
       </c>
       <c r="J41" t="s">
+        <v>381</v>
+      </c>
+      <c r="L41" t="s">
+        <v>382</v>
+      </c>
+      <c r="M41" t="s">
+        <v>28</v>
+      </c>
+      <c r="N41" t="s">
         <v>383</v>
       </c>
-      <c r="K41" t="s">
+      <c r="O41" t="s">
+        <v>30</v>
+      </c>
+      <c r="P41" t="s">
         <v>384</v>
-      </c>
-      <c r="L41" t="s">
-        <v>385</v>
-      </c>
-      <c r="M41" t="s">
-        <v>28</v>
-      </c>
-      <c r="N41" t="s">
-        <v>386</v>
-      </c>
-      <c r="O41" t="s">
-        <v>30</v>
-      </c>
-      <c r="P41" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B42" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C42" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D42" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E42" t="s">
         <v>20</v>
       </c>
       <c r="F42" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G42" t="s">
-        <v>310</v>
+        <v>388</v>
       </c>
       <c r="H42" t="s">
+        <v>389</v>
+      </c>
+      <c r="I42" t="s">
+        <v>390</v>
+      </c>
+      <c r="J42" t="s">
         <v>391</v>
       </c>
-      <c r="I42" t="s">
-        <v>24</v>
-      </c>
-      <c r="J42" t="s">
+      <c r="L42" t="s">
         <v>392</v>
       </c>
-      <c r="L42" t="s">
+      <c r="M42" t="s">
+        <v>28</v>
+      </c>
+      <c r="N42" t="s">
         <v>393</v>
       </c>
-      <c r="M42" t="s">
-        <v>28</v>
-      </c>
-      <c r="N42" t="s">
+      <c r="O42" t="s">
+        <v>30</v>
+      </c>
+      <c r="P42" t="s">
         <v>394</v>
-      </c>
-      <c r="O42" t="s">
-        <v>30</v>
-      </c>
-      <c r="P42" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>395</v>
+      </c>
+      <c r="B43" t="s">
         <v>396</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>397</v>
       </c>
-      <c r="C43" t="s">
-        <v>398</v>
-      </c>
       <c r="D43" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E43" t="s">
         <v>20</v>
@@ -4975,116 +4798,119 @@
         <v>54</v>
       </c>
       <c r="G43" t="s">
+        <v>398</v>
+      </c>
+      <c r="H43" t="s">
         <v>399</v>
       </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
+        <v>24</v>
+      </c>
+      <c r="J43" t="s">
         <v>400</v>
       </c>
-      <c r="I43" t="s">
+      <c r="K43" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="J43" t="s">
+      <c r="L43" t="s">
         <v>402</v>
       </c>
-      <c r="L43" t="s">
+      <c r="M43" t="s">
+        <v>28</v>
+      </c>
+      <c r="N43" t="s">
         <v>403</v>
       </c>
-      <c r="M43" t="s">
-        <v>28</v>
-      </c>
-      <c r="N43" t="s">
+      <c r="O43" t="s">
+        <v>30</v>
+      </c>
+      <c r="P43" t="s">
         <v>404</v>
-      </c>
-      <c r="O43" t="s">
-        <v>30</v>
-      </c>
-      <c r="P43" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>405</v>
+      </c>
+      <c r="B44" t="s">
         <v>406</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>407</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
+        <v>289</v>
+      </c>
+      <c r="E44" t="s">
+        <v>64</v>
+      </c>
+      <c r="F44" t="s">
+        <v>65</v>
+      </c>
+      <c r="G44" t="s">
         <v>408</v>
       </c>
-      <c r="D44" t="s">
-        <v>300</v>
-      </c>
-      <c r="E44" t="s">
-        <v>20</v>
-      </c>
-      <c r="F44" t="s">
-        <v>54</v>
-      </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>409</v>
       </c>
-      <c r="H44" t="s">
+      <c r="I44" t="s">
+        <v>237</v>
+      </c>
+      <c r="J44" t="s">
         <v>410</v>
       </c>
-      <c r="I44" t="s">
-        <v>24</v>
-      </c>
-      <c r="J44" t="s">
+      <c r="K44" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L44" t="s">
         <v>411</v>
       </c>
-      <c r="K44" s="3" t="s">
+      <c r="M44" t="s">
+        <v>28</v>
+      </c>
+      <c r="N44" t="s">
         <v>412</v>
       </c>
-      <c r="L44" t="s">
+      <c r="O44" t="s">
+        <v>30</v>
+      </c>
+      <c r="P44" t="s">
         <v>413</v>
-      </c>
-      <c r="M44" t="s">
-        <v>28</v>
-      </c>
-      <c r="N44" t="s">
-        <v>414</v>
-      </c>
-      <c r="O44" t="s">
-        <v>30</v>
-      </c>
-      <c r="P44" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>414</v>
+      </c>
+      <c r="B45" t="s">
+        <v>415</v>
+      </c>
+      <c r="C45" t="s">
         <v>416</v>
       </c>
-      <c r="B45" t="s">
-        <v>417</v>
-      </c>
-      <c r="C45" t="s">
-        <v>418</v>
-      </c>
       <c r="D45" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E45" t="s">
         <v>64</v>
       </c>
       <c r="F45" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G45" t="s">
+        <v>417</v>
+      </c>
+      <c r="H45" t="s">
+        <v>418</v>
+      </c>
+      <c r="I45" t="s">
         <v>419</v>
       </c>
-      <c r="H45" t="s">
+      <c r="J45" t="s">
         <v>420</v>
       </c>
-      <c r="I45" t="s">
-        <v>237</v>
-      </c>
-      <c r="J45" t="s">
+      <c r="K45" t="s">
         <v>421</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="L45" t="s">
         <v>422</v>
@@ -5113,157 +4939,154 @@
         <v>427</v>
       </c>
       <c r="D46" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E46" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F46" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G46" t="s">
+        <v>299</v>
+      </c>
+      <c r="H46" t="s">
         <v>428</v>
       </c>
-      <c r="H46" t="s">
+      <c r="I46" t="s">
         <v>429</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>430</v>
       </c>
-      <c r="J46" t="s">
+      <c r="K46" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L46" t="s">
         <v>431</v>
       </c>
-      <c r="K46" t="s">
+      <c r="M46" t="s">
+        <v>28</v>
+      </c>
+      <c r="N46" t="s">
         <v>432</v>
       </c>
-      <c r="L46" t="s">
+      <c r="O46" t="s">
+        <v>30</v>
+      </c>
+      <c r="P46" t="s">
         <v>433</v>
-      </c>
-      <c r="M46" t="s">
-        <v>28</v>
-      </c>
-      <c r="N46" t="s">
-        <v>434</v>
-      </c>
-      <c r="O46" t="s">
-        <v>30</v>
-      </c>
-      <c r="P46" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>434</v>
+      </c>
+      <c r="B47" t="s">
+        <v>435</v>
+      </c>
+      <c r="C47" t="s">
         <v>436</v>
       </c>
-      <c r="B47" t="s">
-        <v>437</v>
-      </c>
-      <c r="C47" t="s">
-        <v>438</v>
-      </c>
       <c r="D47" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="E47" t="s">
         <v>74</v>
       </c>
       <c r="F47" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G47" t="s">
-        <v>310</v>
+        <v>408</v>
       </c>
       <c r="H47" t="s">
+        <v>437</v>
+      </c>
+      <c r="I47" t="s">
+        <v>438</v>
+      </c>
+      <c r="J47" t="s">
         <v>439</v>
-      </c>
-      <c r="I47" t="s">
-        <v>440</v>
-      </c>
-      <c r="J47" t="s">
-        <v>441</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>69</v>
       </c>
       <c r="L47" t="s">
+        <v>440</v>
+      </c>
+      <c r="M47" t="s">
+        <v>28</v>
+      </c>
+      <c r="N47" t="s">
+        <v>441</v>
+      </c>
+      <c r="O47" t="s">
+        <v>30</v>
+      </c>
+      <c r="P47" t="s">
         <v>442</v>
-      </c>
-      <c r="M47" t="s">
-        <v>28</v>
-      </c>
-      <c r="N47" t="s">
-        <v>443</v>
-      </c>
-      <c r="O47" t="s">
-        <v>30</v>
-      </c>
-      <c r="P47" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>443</v>
+      </c>
+      <c r="B48" t="s">
+        <v>444</v>
+      </c>
+      <c r="C48" t="s">
         <v>445</v>
       </c>
-      <c r="B48" t="s">
+      <c r="D48" t="s">
         <v>446</v>
       </c>
-      <c r="C48" t="s">
+      <c r="E48" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48" t="s">
+        <v>215</v>
+      </c>
+      <c r="H48" t="s">
         <v>447</v>
       </c>
-      <c r="D48" t="s">
-        <v>300</v>
-      </c>
-      <c r="E48" t="s">
-        <v>74</v>
-      </c>
-      <c r="F48" t="s">
-        <v>54</v>
-      </c>
-      <c r="G48" t="s">
-        <v>419</v>
-      </c>
-      <c r="H48" t="s">
+      <c r="I48" t="s">
+        <v>24</v>
+      </c>
+      <c r="J48" t="s">
         <v>448</v>
       </c>
-      <c r="I48" t="s">
+      <c r="K48" t="s">
         <v>449</v>
       </c>
-      <c r="J48" t="s">
+      <c r="L48" t="s">
         <v>450</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L48" t="s">
+      <c r="M48" t="s">
+        <v>28</v>
+      </c>
+      <c r="O48" t="s">
+        <v>30</v>
+      </c>
+      <c r="P48" t="s">
         <v>451</v>
-      </c>
-      <c r="M48" t="s">
-        <v>28</v>
-      </c>
-      <c r="N48" t="s">
-        <v>452</v>
-      </c>
-      <c r="O48" t="s">
-        <v>30</v>
-      </c>
-      <c r="P48" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>452</v>
+      </c>
+      <c r="B49" t="s">
+        <v>453</v>
+      </c>
+      <c r="C49" t="s">
         <v>454</v>
       </c>
-      <c r="B49" t="s">
+      <c r="D49" t="s">
         <v>455</v>
-      </c>
-      <c r="C49" t="s">
-        <v>456</v>
-      </c>
-      <c r="D49" t="s">
-        <v>457</v>
       </c>
       <c r="E49" t="s">
         <v>20</v>
@@ -5272,13 +5095,13 @@
         <v>21</v>
       </c>
       <c r="G49" t="s">
-        <v>215</v>
+        <v>456</v>
       </c>
       <c r="H49" t="s">
+        <v>457</v>
+      </c>
+      <c r="I49" t="s">
         <v>458</v>
-      </c>
-      <c r="I49" t="s">
-        <v>24</v>
       </c>
       <c r="J49" t="s">
         <v>459</v>
@@ -5296,46 +5119,46 @@
         <v>30</v>
       </c>
       <c r="P49" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>462</v>
+      </c>
+      <c r="B50" t="s">
         <v>463</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>464</v>
       </c>
-      <c r="C50" t="s">
-        <v>465</v>
-      </c>
       <c r="D50" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="E50" t="s">
         <v>20</v>
       </c>
       <c r="F50" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G50" t="s">
+        <v>465</v>
+      </c>
+      <c r="H50" t="s">
+        <v>466</v>
+      </c>
+      <c r="I50" t="s">
         <v>467</v>
       </c>
-      <c r="H50" t="s">
+      <c r="J50" t="s">
         <v>468</v>
       </c>
-      <c r="I50" t="s">
+      <c r="K50" t="s">
         <v>469</v>
       </c>
-      <c r="J50" t="s">
+      <c r="L50" t="s">
         <v>470</v>
       </c>
-      <c r="K50" t="s">
-        <v>471</v>
-      </c>
-      <c r="L50" t="s">
-        <v>472</v>
-      </c>
       <c r="M50" t="s">
         <v>28</v>
       </c>
@@ -5343,46 +5166,43 @@
         <v>30</v>
       </c>
       <c r="P50" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>471</v>
+      </c>
+      <c r="B51" t="s">
+        <v>472</v>
+      </c>
+      <c r="C51" t="s">
         <v>473</v>
       </c>
-      <c r="B51" t="s">
+      <c r="D51" t="s">
+        <v>455</v>
+      </c>
+      <c r="E51" t="s">
+        <v>74</v>
+      </c>
+      <c r="F51" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51" t="s">
+        <v>465</v>
+      </c>
+      <c r="H51" t="s">
         <v>474</v>
       </c>
-      <c r="C51" t="s">
+      <c r="I51" t="s">
         <v>475</v>
       </c>
-      <c r="D51" t="s">
-        <v>466</v>
-      </c>
-      <c r="E51" t="s">
-        <v>20</v>
-      </c>
-      <c r="F51" t="s">
-        <v>54</v>
-      </c>
-      <c r="G51" t="s">
+      <c r="J51" t="s">
         <v>476</v>
       </c>
-      <c r="H51" t="s">
+      <c r="L51" t="s">
         <v>477</v>
       </c>
-      <c r="I51" t="s">
-        <v>478</v>
-      </c>
-      <c r="J51" t="s">
-        <v>479</v>
-      </c>
-      <c r="K51" t="s">
-        <v>480</v>
-      </c>
-      <c r="L51" t="s">
-        <v>481</v>
-      </c>
       <c r="M51" t="s">
         <v>28</v>
       </c>
@@ -5390,74 +5210,74 @@
         <v>30</v>
       </c>
       <c r="P51" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B52" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C52" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="D52" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="E52" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="F52" t="s">
         <v>54</v>
       </c>
       <c r="G52" t="s">
+        <v>482</v>
+      </c>
+      <c r="H52" t="s">
+        <v>483</v>
+      </c>
+      <c r="I52" t="s">
+        <v>484</v>
+      </c>
+      <c r="J52" t="s">
         <v>485</v>
       </c>
-      <c r="H52" t="s">
+      <c r="L52" t="s">
         <v>486</v>
       </c>
-      <c r="I52" t="s">
-        <v>24</v>
-      </c>
-      <c r="J52" t="s">
-        <v>487</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>488</v>
-      </c>
       <c r="M52" t="s">
-        <v>249</v>
+        <v>28</v>
       </c>
       <c r="O52" t="s">
-        <v>249</v>
+        <v>30</v>
       </c>
       <c r="P52" t="s">
-        <v>251</v>
+        <v>451</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>487</v>
+      </c>
+      <c r="B53" t="s">
+        <v>488</v>
+      </c>
+      <c r="C53" t="s">
         <v>489</v>
       </c>
-      <c r="B53" t="s">
+      <c r="D53" t="s">
         <v>490</v>
       </c>
-      <c r="C53" t="s">
+      <c r="E53" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" t="s">
+        <v>54</v>
+      </c>
+      <c r="G53" t="s">
         <v>491</v>
-      </c>
-      <c r="D53" t="s">
-        <v>466</v>
-      </c>
-      <c r="E53" t="s">
-        <v>74</v>
-      </c>
-      <c r="F53" t="s">
-        <v>21</v>
-      </c>
-      <c r="G53" t="s">
-        <v>476</v>
       </c>
       <c r="H53" t="s">
         <v>492</v>
@@ -5468,8 +5288,11 @@
       <c r="J53" t="s">
         <v>494</v>
       </c>
+      <c r="K53" t="s">
+        <v>495</v>
+      </c>
       <c r="L53" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M53" t="s">
         <v>28</v>
@@ -5478,42 +5301,45 @@
         <v>30</v>
       </c>
       <c r="P53" t="s">
-        <v>462</v>
+        <v>269</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B54" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C54" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D54" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E54" t="s">
         <v>20</v>
       </c>
       <c r="F54" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G54" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H54" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="I54" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="J54" t="s">
         <v>503</v>
       </c>
+      <c r="K54" t="s">
+        <v>504</v>
+      </c>
       <c r="L54" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M54" t="s">
         <v>28</v>
@@ -5522,46 +5348,43 @@
         <v>30</v>
       </c>
       <c r="P54" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B55" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C55" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D55" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E55" t="s">
         <v>20</v>
       </c>
       <c r="F55" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G55" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H55" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I55" t="s">
-        <v>511</v>
+        <v>484</v>
       </c>
       <c r="J55" t="s">
         <v>512</v>
       </c>
-      <c r="K55" t="s">
+      <c r="L55" t="s">
         <v>513</v>
       </c>
-      <c r="L55" t="s">
-        <v>514</v>
-      </c>
       <c r="M55" t="s">
         <v>28</v>
       </c>
@@ -5569,46 +5392,43 @@
         <v>30</v>
       </c>
       <c r="P55" t="s">
-        <v>280</v>
+        <v>451</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>514</v>
+      </c>
+      <c r="B56" t="s">
         <v>515</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>516</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
+        <v>509</v>
+      </c>
+      <c r="E56" t="s">
+        <v>64</v>
+      </c>
+      <c r="F56" t="s">
+        <v>65</v>
+      </c>
+      <c r="G56" t="s">
         <v>517</v>
       </c>
-      <c r="D56" t="s">
+      <c r="H56" t="s">
         <v>518</v>
       </c>
-      <c r="E56" t="s">
-        <v>20</v>
-      </c>
-      <c r="F56" t="s">
-        <v>21</v>
-      </c>
-      <c r="G56" t="s">
+      <c r="I56" t="s">
+        <v>24</v>
+      </c>
+      <c r="J56" t="s">
         <v>519</v>
       </c>
-      <c r="H56" t="s">
+      <c r="L56" t="s">
         <v>520</v>
       </c>
-      <c r="I56" t="s">
-        <v>502</v>
-      </c>
-      <c r="J56" t="s">
-        <v>521</v>
-      </c>
-      <c r="K56" t="s">
-        <v>522</v>
-      </c>
-      <c r="L56" t="s">
-        <v>523</v>
-      </c>
       <c r="M56" t="s">
         <v>28</v>
       </c>
@@ -5616,43 +5436,46 @@
         <v>30</v>
       </c>
       <c r="P56" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>521</v>
+      </c>
+      <c r="B57" t="s">
+        <v>522</v>
+      </c>
+      <c r="C57" t="s">
+        <v>523</v>
+      </c>
+      <c r="D57" t="s">
+        <v>509</v>
+      </c>
+      <c r="E57" t="s">
+        <v>74</v>
+      </c>
+      <c r="F57" t="s">
+        <v>54</v>
+      </c>
+      <c r="G57" t="s">
         <v>524</v>
       </c>
-      <c r="B57" t="s">
+      <c r="H57" t="s">
         <v>525</v>
       </c>
-      <c r="C57" t="s">
+      <c r="I57" t="s">
         <v>526</v>
       </c>
-      <c r="D57" t="s">
+      <c r="J57" t="s">
         <v>527</v>
       </c>
-      <c r="E57" t="s">
-        <v>20</v>
-      </c>
-      <c r="F57" t="s">
-        <v>21</v>
-      </c>
-      <c r="G57" t="s">
+      <c r="K57" t="s">
         <v>528</v>
       </c>
-      <c r="H57" t="s">
+      <c r="L57" t="s">
         <v>529</v>
       </c>
-      <c r="I57" t="s">
-        <v>502</v>
-      </c>
-      <c r="J57" t="s">
-        <v>530</v>
-      </c>
-      <c r="L57" t="s">
-        <v>531</v>
-      </c>
       <c r="M57" t="s">
         <v>28</v>
       </c>
@@ -5660,43 +5483,43 @@
         <v>30</v>
       </c>
       <c r="P57" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>530</v>
+      </c>
+      <c r="B58" t="s">
+        <v>531</v>
+      </c>
+      <c r="C58" t="s">
         <v>532</v>
       </c>
-      <c r="B58" t="s">
+      <c r="D58" t="s">
         <v>533</v>
       </c>
-      <c r="C58" t="s">
+      <c r="E58" t="s">
+        <v>20</v>
+      </c>
+      <c r="F58" t="s">
+        <v>54</v>
+      </c>
+      <c r="G58" t="s">
         <v>534</v>
       </c>
-      <c r="D58" t="s">
-        <v>527</v>
-      </c>
-      <c r="E58" t="s">
-        <v>64</v>
-      </c>
-      <c r="F58" t="s">
-        <v>65</v>
-      </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>535</v>
       </c>
-      <c r="H58" t="s">
+      <c r="I58" t="s">
+        <v>484</v>
+      </c>
+      <c r="J58" t="s">
         <v>536</v>
       </c>
-      <c r="I58" t="s">
-        <v>24</v>
-      </c>
-      <c r="J58" t="s">
+      <c r="L58" t="s">
         <v>537</v>
       </c>
-      <c r="L58" t="s">
-        <v>538</v>
-      </c>
       <c r="M58" t="s">
         <v>28</v>
       </c>
@@ -5704,24 +5527,24 @@
         <v>30</v>
       </c>
       <c r="P58" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>538</v>
+      </c>
+      <c r="B59" t="s">
         <v>539</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>540</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>541</v>
       </c>
-      <c r="D59" t="s">
-        <v>527</v>
-      </c>
       <c r="E59" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="F59" t="s">
         <v>54</v>
@@ -5733,256 +5556,247 @@
         <v>543</v>
       </c>
       <c r="I59" t="s">
+        <v>333</v>
+      </c>
+      <c r="J59" t="s">
         <v>544</v>
       </c>
-      <c r="J59" t="s">
+      <c r="K59" t="s">
         <v>545</v>
       </c>
-      <c r="K59" t="s">
+      <c r="M59" t="s">
         <v>546</v>
       </c>
-      <c r="L59" t="s">
-        <v>547</v>
-      </c>
-      <c r="M59" t="s">
-        <v>28</v>
-      </c>
       <c r="O59" t="s">
-        <v>30</v>
+        <v>327</v>
       </c>
       <c r="P59" t="s">
-        <v>462</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>547</v>
+      </c>
+      <c r="B60" t="s">
         <v>548</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>549</v>
       </c>
-      <c r="C60" t="s">
-        <v>550</v>
-      </c>
       <c r="D60" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="E60" t="s">
         <v>20</v>
       </c>
       <c r="F60" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="G60" t="s">
+        <v>550</v>
+      </c>
+      <c r="H60" t="s">
+        <v>551</v>
+      </c>
+      <c r="I60" t="s">
         <v>552</v>
       </c>
-      <c r="H60" t="s">
+      <c r="J60" t="s">
         <v>553</v>
       </c>
-      <c r="I60" t="s">
-        <v>502</v>
-      </c>
-      <c r="J60" t="s">
-        <v>554</v>
-      </c>
-      <c r="L60" t="s">
-        <v>555</v>
-      </c>
       <c r="M60" t="s">
-        <v>28</v>
+        <v>546</v>
       </c>
       <c r="O60" t="s">
-        <v>30</v>
+        <v>327</v>
       </c>
       <c r="P60" t="s">
-        <v>462</v>
+        <v>328</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>554</v>
+      </c>
+      <c r="B61" t="s">
+        <v>555</v>
+      </c>
+      <c r="C61" t="s">
         <v>556</v>
       </c>
-      <c r="B61" t="s">
+      <c r="D61" t="s">
         <v>557</v>
-      </c>
-      <c r="C61" t="s">
-        <v>558</v>
-      </c>
-      <c r="D61" t="s">
-        <v>559</v>
       </c>
       <c r="E61" t="s">
         <v>20</v>
       </c>
       <c r="F61" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G61" t="s">
+        <v>558</v>
+      </c>
+      <c r="H61" t="s">
+        <v>559</v>
+      </c>
+      <c r="I61" t="s">
         <v>560</v>
       </c>
-      <c r="H61" t="s">
+      <c r="J61" t="s">
         <v>561</v>
       </c>
-      <c r="I61" t="s">
-        <v>344</v>
-      </c>
-      <c r="J61" t="s">
+      <c r="K61" t="s">
         <v>562</v>
       </c>
-      <c r="K61" t="s">
-        <v>563</v>
-      </c>
       <c r="M61" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="O61" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="P61" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>563</v>
+      </c>
+      <c r="B62" t="s">
+        <v>564</v>
+      </c>
+      <c r="C62" t="s">
         <v>565</v>
       </c>
-      <c r="B62" t="s">
-        <v>566</v>
-      </c>
-      <c r="C62" t="s">
-        <v>567</v>
-      </c>
       <c r="D62" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E62" t="s">
         <v>20</v>
       </c>
       <c r="F62" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G62" t="s">
+        <v>566</v>
+      </c>
+      <c r="H62" t="s">
+        <v>567</v>
+      </c>
+      <c r="I62" t="s">
         <v>568</v>
       </c>
-      <c r="H62" t="s">
+      <c r="J62" t="s">
         <v>569</v>
       </c>
-      <c r="I62" t="s">
+      <c r="K62" t="s">
         <v>570</v>
       </c>
-      <c r="J62" t="s">
-        <v>571</v>
-      </c>
       <c r="M62" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="O62" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="P62" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>571</v>
+      </c>
+      <c r="B63" t="s">
         <v>572</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>573</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
+        <v>557</v>
+      </c>
+      <c r="E63" t="s">
+        <v>64</v>
+      </c>
+      <c r="F63" t="s">
+        <v>65</v>
+      </c>
+      <c r="G63" t="s">
         <v>574</v>
       </c>
-      <c r="D63" t="s">
+      <c r="H63" t="s">
         <v>575</v>
       </c>
-      <c r="E63" t="s">
-        <v>20</v>
-      </c>
-      <c r="F63" t="s">
-        <v>21</v>
-      </c>
-      <c r="G63" t="s">
+      <c r="I63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J63" t="s">
         <v>576</v>
       </c>
-      <c r="H63" t="s">
-        <v>577</v>
-      </c>
-      <c r="I63" t="s">
-        <v>578</v>
-      </c>
-      <c r="J63" t="s">
-        <v>579</v>
-      </c>
-      <c r="K63" t="s">
-        <v>580</v>
-      </c>
       <c r="M63" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="O63" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="P63" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>577</v>
+      </c>
+      <c r="B64" t="s">
+        <v>578</v>
+      </c>
+      <c r="C64" t="s">
+        <v>579</v>
+      </c>
+      <c r="D64" t="s">
+        <v>557</v>
+      </c>
+      <c r="E64" t="s">
+        <v>74</v>
+      </c>
+      <c r="F64" t="s">
+        <v>54</v>
+      </c>
+      <c r="G64" t="s">
+        <v>580</v>
+      </c>
+      <c r="H64" t="s">
         <v>581</v>
       </c>
-      <c r="B64" t="s">
+      <c r="I64" t="s">
         <v>582</v>
       </c>
-      <c r="C64" t="s">
+      <c r="J64" t="s">
         <v>583</v>
       </c>
-      <c r="D64" t="s">
-        <v>575</v>
-      </c>
-      <c r="E64" t="s">
-        <v>20</v>
-      </c>
-      <c r="F64" t="s">
-        <v>21</v>
-      </c>
-      <c r="G64" t="s">
-        <v>584</v>
-      </c>
-      <c r="H64" t="s">
-        <v>585</v>
-      </c>
-      <c r="I64" t="s">
-        <v>586</v>
-      </c>
-      <c r="J64" t="s">
-        <v>587</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="M64" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="O64" t="s">
-        <v>588</v>
+        <v>327</v>
       </c>
       <c r="P64" t="s">
-        <v>589</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="B65" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="C65" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="D65" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="E65" t="s">
         <v>20</v>
@@ -5991,168 +5805,174 @@
         <v>54</v>
       </c>
       <c r="G65" t="s">
-        <v>593</v>
+        <v>36</v>
       </c>
       <c r="H65" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="I65" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="J65" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="K65" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="M65" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="O65" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="P65" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>592</v>
+      </c>
+      <c r="B66" t="s">
+        <v>593</v>
+      </c>
+      <c r="C66" t="s">
+        <v>594</v>
+      </c>
+      <c r="D66" t="s">
+        <v>595</v>
+      </c>
+      <c r="E66" t="s">
+        <v>20</v>
+      </c>
+      <c r="F66" t="s">
+        <v>21</v>
+      </c>
+      <c r="G66" t="s">
+        <v>596</v>
+      </c>
+      <c r="H66" t="s">
+        <v>597</v>
+      </c>
+      <c r="I66" t="s">
+        <v>24</v>
+      </c>
+      <c r="J66" t="s">
         <v>598</v>
       </c>
-      <c r="B66" t="s">
+      <c r="K66" t="s">
         <v>599</v>
       </c>
-      <c r="C66" t="s">
-        <v>600</v>
-      </c>
-      <c r="D66" t="s">
-        <v>575</v>
-      </c>
-      <c r="E66" t="s">
-        <v>64</v>
-      </c>
-      <c r="F66" t="s">
-        <v>54</v>
-      </c>
-      <c r="G66" t="s">
-        <v>601</v>
-      </c>
-      <c r="H66" t="s">
-        <v>602</v>
-      </c>
-      <c r="I66" t="s">
-        <v>603</v>
-      </c>
-      <c r="J66" t="s">
-        <v>604</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>605</v>
-      </c>
       <c r="M66" t="s">
-        <v>564</v>
+        <v>28</v>
       </c>
       <c r="O66" t="s">
-        <v>588</v>
+        <v>30</v>
       </c>
       <c r="P66" t="s">
-        <v>589</v>
+        <v>269</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>600</v>
+      </c>
+      <c r="B67" t="s">
+        <v>601</v>
+      </c>
+      <c r="C67" t="s">
+        <v>602</v>
+      </c>
+      <c r="D67" t="s">
+        <v>595</v>
+      </c>
+      <c r="E67" t="s">
+        <v>20</v>
+      </c>
+      <c r="F67" t="s">
+        <v>21</v>
+      </c>
+      <c r="G67" t="s">
+        <v>603</v>
+      </c>
+      <c r="H67" t="s">
+        <v>604</v>
+      </c>
+      <c r="I67" t="s">
+        <v>605</v>
+      </c>
+      <c r="J67" t="s">
         <v>606</v>
       </c>
-      <c r="B67" t="s">
+      <c r="K67" t="s">
         <v>607</v>
       </c>
-      <c r="C67" t="s">
-        <v>608</v>
-      </c>
-      <c r="D67" t="s">
-        <v>575</v>
-      </c>
-      <c r="E67" t="s">
-        <v>64</v>
-      </c>
-      <c r="F67" t="s">
-        <v>65</v>
-      </c>
-      <c r="G67" t="s">
-        <v>609</v>
-      </c>
-      <c r="H67" t="s">
-        <v>610</v>
-      </c>
-      <c r="I67" t="s">
-        <v>24</v>
-      </c>
-      <c r="J67" t="s">
-        <v>611</v>
-      </c>
       <c r="M67" t="s">
-        <v>564</v>
+        <v>28</v>
       </c>
       <c r="O67" t="s">
-        <v>338</v>
+        <v>30</v>
       </c>
       <c r="P67" t="s">
-        <v>339</v>
+        <v>269</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>608</v>
+      </c>
+      <c r="B68" t="s">
+        <v>609</v>
+      </c>
+      <c r="C68" t="s">
+        <v>610</v>
+      </c>
+      <c r="D68" t="s">
+        <v>595</v>
+      </c>
+      <c r="E68" t="s">
+        <v>20</v>
+      </c>
+      <c r="F68" t="s">
+        <v>21</v>
+      </c>
+      <c r="G68" t="s">
+        <v>603</v>
+      </c>
+      <c r="H68" t="s">
+        <v>611</v>
+      </c>
+      <c r="I68" t="s">
         <v>612</v>
       </c>
-      <c r="B68" t="s">
+      <c r="J68" t="s">
         <v>613</v>
       </c>
-      <c r="C68" t="s">
+      <c r="K68" t="s">
         <v>614</v>
       </c>
-      <c r="D68" t="s">
-        <v>575</v>
-      </c>
-      <c r="E68" t="s">
-        <v>74</v>
-      </c>
-      <c r="F68" t="s">
-        <v>54</v>
-      </c>
-      <c r="G68" t="s">
-        <v>615</v>
-      </c>
-      <c r="H68" t="s">
-        <v>616</v>
-      </c>
-      <c r="I68" t="s">
-        <v>617</v>
-      </c>
-      <c r="J68" t="s">
-        <v>618</v>
-      </c>
       <c r="M68" t="s">
-        <v>564</v>
+        <v>28</v>
       </c>
       <c r="O68" t="s">
-        <v>338</v>
+        <v>30</v>
       </c>
       <c r="P68" t="s">
-        <v>339</v>
+        <v>269</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B69" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C69" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="D69" t="s">
-        <v>622</v>
+        <v>595</v>
       </c>
       <c r="E69" t="s">
         <v>20</v>
@@ -6161,63 +5981,57 @@
         <v>54</v>
       </c>
       <c r="G69" t="s">
-        <v>36</v>
+        <v>603</v>
       </c>
       <c r="H69" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="I69" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="J69" t="s">
-        <v>625</v>
-      </c>
-      <c r="K69" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="M69" t="s">
-        <v>564</v>
+        <v>28</v>
       </c>
       <c r="O69" t="s">
-        <v>338</v>
+        <v>30</v>
       </c>
       <c r="P69" t="s">
-        <v>339</v>
+        <v>269</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B70" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="C70" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="D70" t="s">
-        <v>630</v>
+        <v>595</v>
       </c>
       <c r="E70" t="s">
         <v>20</v>
       </c>
       <c r="F70" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="G70" t="s">
-        <v>631</v>
+        <v>603</v>
       </c>
       <c r="H70" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="I70" t="s">
         <v>24</v>
       </c>
       <c r="J70" t="s">
-        <v>633</v>
-      </c>
-      <c r="K70" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="M70" t="s">
         <v>28</v>
@@ -6226,42 +6040,42 @@
         <v>30</v>
       </c>
       <c r="P70" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="B71" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="C71" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="D71" t="s">
+        <v>595</v>
+      </c>
+      <c r="E71" t="s">
+        <v>64</v>
+      </c>
+      <c r="F71" t="s">
+        <v>54</v>
+      </c>
+      <c r="G71" t="s">
+        <v>629</v>
+      </c>
+      <c r="H71" t="s">
         <v>630</v>
       </c>
-      <c r="E71" t="s">
-        <v>20</v>
-      </c>
-      <c r="F71" t="s">
-        <v>21</v>
-      </c>
-      <c r="G71" t="s">
-        <v>638</v>
-      </c>
-      <c r="H71" t="s">
-        <v>639</v>
-      </c>
       <c r="I71" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="J71" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="K71" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="M71" t="s">
         <v>28</v>
@@ -6270,21 +6084,21 @@
         <v>30</v>
       </c>
       <c r="P71" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="B72" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="C72" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="D72" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E72" t="s">
         <v>20</v>
@@ -6296,523 +6110,571 @@
         <v>638</v>
       </c>
       <c r="H72" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="I72" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="J72" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="K72" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="M72" t="s">
-        <v>28</v>
+        <v>546</v>
       </c>
       <c r="O72" t="s">
-        <v>30</v>
+        <v>327</v>
       </c>
       <c r="P72" t="s">
-        <v>280</v>
+        <v>328</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="B73" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="C73" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="D73" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E73" t="s">
         <v>20</v>
       </c>
       <c r="F73" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G73" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="H73" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="I73" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="J73" t="s">
-        <v>655</v>
+        <v>649</v>
+      </c>
+      <c r="K73" t="s">
+        <v>650</v>
       </c>
       <c r="M73" t="s">
-        <v>28</v>
+        <v>546</v>
       </c>
       <c r="O73" t="s">
-        <v>30</v>
+        <v>327</v>
       </c>
       <c r="P73" t="s">
-        <v>280</v>
+        <v>328</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="B74" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="C74" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="D74" t="s">
-        <v>630</v>
+        <v>654</v>
       </c>
       <c r="E74" t="s">
         <v>20</v>
       </c>
       <c r="F74" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G74" t="s">
-        <v>638</v>
+        <v>655</v>
       </c>
       <c r="H74" t="s">
+        <v>656</v>
+      </c>
+      <c r="I74" t="s">
+        <v>657</v>
+      </c>
+      <c r="J74" t="s">
+        <v>658</v>
+      </c>
+      <c r="K74" t="s">
         <v>659</v>
       </c>
-      <c r="I74" t="s">
-        <v>24</v>
-      </c>
-      <c r="J74" t="s">
-        <v>660</v>
-      </c>
       <c r="M74" t="s">
-        <v>28</v>
+        <v>546</v>
       </c>
       <c r="O74" t="s">
-        <v>30</v>
+        <v>327</v>
       </c>
       <c r="P74" t="s">
-        <v>280</v>
+        <v>328</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>660</v>
+      </c>
+      <c r="B75" t="s">
         <v>661</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>662</v>
       </c>
-      <c r="C75" t="s">
-        <v>663</v>
-      </c>
       <c r="D75" t="s">
-        <v>630</v>
+        <v>654</v>
       </c>
       <c r="E75" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="F75" t="s">
         <v>54</v>
       </c>
       <c r="G75" t="s">
+        <v>663</v>
+      </c>
+      <c r="H75" t="s">
         <v>664</v>
       </c>
-      <c r="H75" t="s">
+      <c r="I75" t="s">
         <v>665</v>
       </c>
-      <c r="I75" t="s">
+      <c r="J75" t="s">
         <v>666</v>
       </c>
-      <c r="J75" t="s">
+      <c r="K75" t="s">
         <v>667</v>
       </c>
-      <c r="K75" t="s">
-        <v>668</v>
-      </c>
       <c r="M75" t="s">
-        <v>28</v>
+        <v>546</v>
       </c>
       <c r="O75" t="s">
-        <v>30</v>
+        <v>327</v>
       </c>
       <c r="P75" t="s">
-        <v>280</v>
+        <v>328</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>668</v>
+      </c>
+      <c r="B76" t="s">
         <v>669</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>670</v>
       </c>
-      <c r="C76" t="s">
-        <v>671</v>
-      </c>
       <c r="D76" t="s">
-        <v>672</v>
+        <v>35</v>
       </c>
       <c r="E76" t="s">
         <v>20</v>
       </c>
       <c r="F76" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G76" t="s">
+        <v>671</v>
+      </c>
+      <c r="H76" t="s">
+        <v>672</v>
+      </c>
+      <c r="I76" t="s">
+        <v>24</v>
+      </c>
+      <c r="J76" t="s">
         <v>673</v>
       </c>
-      <c r="H76" t="s">
+      <c r="K76" t="s">
         <v>674</v>
       </c>
-      <c r="I76" t="s">
+      <c r="L76" t="s">
         <v>675</v>
       </c>
-      <c r="J76" t="s">
+      <c r="M76" t="s">
+        <v>28</v>
+      </c>
+      <c r="N76" t="s">
         <v>676</v>
       </c>
-      <c r="K76" t="s">
+      <c r="O76" t="s">
+        <v>30</v>
+      </c>
+      <c r="P76" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
+        <v>83</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="M76" t="s">
-        <v>564</v>
-      </c>
-      <c r="O76" t="s">
-        <v>338</v>
-      </c>
-      <c r="P76" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="C77" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="B77" t="s">
+      <c r="D77" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="C77" t="s">
+      <c r="E77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G77" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="D77" t="s">
-        <v>672</v>
-      </c>
-      <c r="E77" t="s">
+      <c r="H77" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N77" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="O77" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P77" s="3" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
+        <v>84</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N78" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P78" s="3" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
+        <v>85</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F77" t="s">
-        <v>21</v>
-      </c>
-      <c r="G77" t="s">
-        <v>681</v>
-      </c>
-      <c r="H77" t="s">
-        <v>682</v>
-      </c>
-      <c r="I77" t="s">
-        <v>683</v>
-      </c>
-      <c r="J77" t="s">
-        <v>684</v>
-      </c>
-      <c r="K77" t="s">
-        <v>685</v>
-      </c>
-      <c r="M77" t="s">
-        <v>564</v>
-      </c>
-      <c r="O77" t="s">
-        <v>338</v>
-      </c>
-      <c r="P77" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>686</v>
-      </c>
-      <c r="B78" t="s">
-        <v>687</v>
-      </c>
-      <c r="C78" t="s">
-        <v>688</v>
-      </c>
-      <c r="D78" t="s">
-        <v>672</v>
-      </c>
-      <c r="E78" t="s">
-        <v>64</v>
-      </c>
-      <c r="F78" t="s">
+      <c r="F79" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N79" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="O79" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P79" s="3" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
+        <v>86</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F80" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G78" t="s">
-        <v>689</v>
-      </c>
-      <c r="H78" t="s">
-        <v>690</v>
-      </c>
-      <c r="I78" t="s">
-        <v>691</v>
-      </c>
-      <c r="J78" t="s">
-        <v>692</v>
-      </c>
-      <c r="K78" s="3" t="s">
-        <v>693</v>
-      </c>
-      <c r="M78" t="s">
-        <v>564</v>
-      </c>
-      <c r="O78" t="s">
-        <v>588</v>
-      </c>
-      <c r="P78" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>694</v>
-      </c>
-      <c r="B79" t="s">
-        <v>695</v>
-      </c>
-      <c r="C79" t="s">
-        <v>696</v>
-      </c>
-      <c r="D79" t="s">
-        <v>697</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="G80" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="N80" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="P80" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
+        <v>87</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F81" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G79" t="s">
-        <v>698</v>
-      </c>
-      <c r="H79" t="s">
-        <v>699</v>
-      </c>
-      <c r="I79" t="s">
-        <v>700</v>
-      </c>
-      <c r="J79" t="s">
-        <v>701</v>
-      </c>
-      <c r="K79" t="s">
-        <v>702</v>
-      </c>
-      <c r="M79" t="s">
-        <v>564</v>
-      </c>
-      <c r="O79" t="s">
-        <v>338</v>
-      </c>
-      <c r="P79" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>703</v>
-      </c>
-      <c r="B80" t="s">
-        <v>704</v>
-      </c>
-      <c r="C80" t="s">
-        <v>705</v>
-      </c>
-      <c r="D80" t="s">
-        <v>697</v>
-      </c>
-      <c r="E80" t="s">
+      <c r="G81" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
+        <v>88</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F82" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G80" t="s">
-        <v>706</v>
-      </c>
-      <c r="H80" t="s">
-        <v>707</v>
-      </c>
-      <c r="I80" t="s">
-        <v>708</v>
-      </c>
-      <c r="J80" t="s">
-        <v>709</v>
-      </c>
-      <c r="K80" t="s">
-        <v>710</v>
-      </c>
-      <c r="M80" t="s">
-        <v>564</v>
-      </c>
-      <c r="O80" t="s">
-        <v>338</v>
-      </c>
-      <c r="P80" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>711</v>
-      </c>
-      <c r="B81" t="s">
-        <v>712</v>
-      </c>
-      <c r="C81" t="s">
-        <v>713</v>
-      </c>
-      <c r="D81" t="s">
-        <v>697</v>
-      </c>
-      <c r="E81" t="s">
+      <c r="G82" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="L82" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="M82" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N82" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P82" s="3" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="3">
+        <v>89</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F83" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G81" t="s">
-        <v>714</v>
-      </c>
-      <c r="H81" t="s">
-        <v>715</v>
-      </c>
-      <c r="I81" t="s">
-        <v>716</v>
-      </c>
-      <c r="J81" t="s">
-        <v>717</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="M81" t="s">
-        <v>564</v>
-      </c>
-      <c r="O81" t="s">
-        <v>588</v>
-      </c>
-      <c r="P81" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>719</v>
-      </c>
-      <c r="B82" t="s">
-        <v>720</v>
-      </c>
-      <c r="C82" t="s">
-        <v>721</v>
-      </c>
-      <c r="D82" t="s">
-        <v>697</v>
-      </c>
-      <c r="E82" t="s">
-        <v>20</v>
-      </c>
-      <c r="F82" t="s">
-        <v>54</v>
-      </c>
-      <c r="G82" t="s">
-        <v>722</v>
-      </c>
-      <c r="H82" t="s">
-        <v>723</v>
-      </c>
-      <c r="I82" t="s">
-        <v>724</v>
-      </c>
-      <c r="J82" t="s">
-        <v>725</v>
-      </c>
-      <c r="K82" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="M82" t="s">
-        <v>564</v>
-      </c>
-      <c r="O82" t="s">
-        <v>588</v>
-      </c>
-      <c r="P82" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>726</v>
-      </c>
-      <c r="B83" t="s">
-        <v>727</v>
-      </c>
-      <c r="C83" t="s">
-        <v>728</v>
-      </c>
-      <c r="D83" t="s">
-        <v>35</v>
-      </c>
-      <c r="E83" t="s">
-        <v>20</v>
-      </c>
-      <c r="F83" t="s">
-        <v>54</v>
-      </c>
-      <c r="G83" t="s">
-        <v>729</v>
-      </c>
-      <c r="H83" t="s">
-        <v>730</v>
-      </c>
-      <c r="I83" t="s">
-        <v>24</v>
-      </c>
-      <c r="J83" t="s">
-        <v>731</v>
-      </c>
-      <c r="K83" t="s">
-        <v>732</v>
-      </c>
-      <c r="L83" t="s">
-        <v>733</v>
-      </c>
-      <c r="M83" t="s">
-        <v>28</v>
-      </c>
-      <c r="N83" t="s">
-        <v>734</v>
-      </c>
-      <c r="O83" t="s">
-        <v>30</v>
-      </c>
-      <c r="P83" t="s">
-        <v>31</v>
+      <c r="G83" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="84" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>735</v>
+        <v>748</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>20</v>
@@ -6821,484 +6683,134 @@
         <v>54</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>739</v>
+        <v>750</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>741</v>
+        <v>752</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="M84" s="3" t="s">
         <v>28</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>744</v>
+        <v>755</v>
       </c>
       <c r="O84" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P84" s="3" t="s">
-        <v>745</v>
+        <v>756</v>
       </c>
     </row>
     <row r="85" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>746</v>
+        <v>757</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>747</v>
+        <v>758</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>748</v>
+        <v>729</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>54</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>750</v>
+        <v>759</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>751</v>
+        <v>760</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>752</v>
+        <v>761</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>754</v>
+        <v>763</v>
       </c>
       <c r="M85" s="3" t="s">
         <v>28</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>755</v>
+        <v>764</v>
       </c>
       <c r="O85" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>756</v>
+        <v>765</v>
       </c>
     </row>
     <row r="86" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>759</v>
+        <v>729</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="M86" s="3" t="s">
         <v>28</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="O86" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P86" s="3" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="3">
-        <v>86</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>771</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>773</v>
-      </c>
-      <c r="J87" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="K87" s="3" t="s">
         <v>775</v>
-      </c>
-      <c r="L87" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="M87" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="N87" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="O87" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="P87" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="3">
-        <v>87</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="J88" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="K88" s="3" t="s">
-        <v>784</v>
-      </c>
-      <c r="L88" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="M88" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="N88" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="O88" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="P88" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="3">
-        <v>88</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>785</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>788</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>789</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>793</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>794</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="3">
-        <v>89</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>796</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>797</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="I90" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="J90" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="K90" s="3" t="s">
-        <v>802</v>
-      </c>
-      <c r="L90" s="3" t="s">
-        <v>803</v>
-      </c>
-      <c r="M90" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N90" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="O90" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P90" s="3" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="3">
-        <v>90</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>806</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="L91" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="3">
-        <v>91</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>815</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>816</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>817</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>818</v>
-      </c>
-      <c r="J92" s="3" t="s">
-        <v>819</v>
-      </c>
-      <c r="K92" s="3" t="s">
-        <v>820</v>
-      </c>
-      <c r="L92" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="M92" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N92" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="O92" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P92" s="3" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="3">
-        <v>92</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>824</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>825</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>826</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>827</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>828</v>
-      </c>
-      <c r="J93" s="3" t="s">
-        <v>829</v>
-      </c>
-      <c r="K93" s="3" t="s">
-        <v>830</v>
-      </c>
-      <c r="L93" s="3" t="s">
-        <v>831</v>
-      </c>
-      <c r="M93" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N93" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="O93" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P93" s="3" t="s">
-        <v>833</v>
       </c>
     </row>
   </sheetData>
